--- a/gstdatabase/GSTR-1-2018-2019.xlsx
+++ b/gstdatabase/GSTR-1-2018-2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD75AD1-9B1B-4E05-B29A-7EC2CBF4CE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A19D9D-A354-48BE-9CAF-CC4C207FA8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -377,20 +377,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -400,6 +394,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -715,13 +715,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
       <c r="G1"/>
       <c r="L1"/>
     </row>
@@ -740,10 +740,10 @@
       <c r="L2" s="7"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26"/>
+      <c r="B3" s="24"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -770,14 +770,14 @@
       <c r="L4" s="7"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
     </row>
     <row r="8" spans="1:62" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="23" t="s">
@@ -869,7 +869,7 @@
       <c r="BJ8" s="23"/>
     </row>
     <row r="9" spans="1:62" s="17" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="23"/>
       <c r="C9" s="18" t="s">
         <v>4</v>
@@ -1186,14 +1186,14 @@
       </c>
       <c r="AN10" s="11">
         <f>AO10-AM10</f>
-        <v>18217</v>
+        <v>18218</v>
       </c>
       <c r="AO10" s="6">
-        <v>25968</v>
+        <v>25969</v>
       </c>
       <c r="AP10" s="12">
         <f>AO10/AL10</f>
-        <v>0.66072973385578337</v>
+        <v>0.66075517785354432</v>
       </c>
       <c r="AQ10" s="5">
         <v>84692</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="E11" s="11">
         <f t="shared" ref="E11:E48" si="0">F11-D11</f>
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="F11" s="6">
-        <v>17865</v>
+        <v>17866</v>
       </c>
       <c r="G11" s="12">
         <f t="shared" ref="G11:G48" si="1">F11/C11</f>
-        <v>0.64204851752021563</v>
+        <v>0.64208445642407908</v>
       </c>
       <c r="H11" s="5">
         <v>30075</v>
@@ -1296,14 +1296,14 @@
       </c>
       <c r="J11" s="11">
         <f t="shared" ref="J11:J48" si="2">K11-I11</f>
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="K11" s="6">
-        <v>18203</v>
+        <v>18204</v>
       </c>
       <c r="L11" s="12">
         <f t="shared" ref="L11:L48" si="3">K11/H11</f>
-        <v>0.60525353283458017</v>
+        <v>0.60528678304239403</v>
       </c>
       <c r="M11" s="5">
         <v>75206</v>
@@ -1313,14 +1313,14 @@
       </c>
       <c r="O11" s="11">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>15483</v>
+        <v>15484</v>
       </c>
       <c r="P11" s="6">
-        <v>67178</v>
+        <v>67179</v>
       </c>
       <c r="Q11" s="12">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.89325319788314761</v>
+        <v>0.8932664946945722</v>
       </c>
       <c r="R11" s="5">
         <v>31646</v>
@@ -1330,14 +1330,14 @@
       </c>
       <c r="T11" s="11">
         <f t="shared" ref="T11:T48" si="6">U11-S11</f>
-        <v>3835</v>
+        <v>3836</v>
       </c>
       <c r="U11" s="6">
-        <v>18683</v>
+        <v>18684</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" ref="V11:V48" si="7">U11/R11</f>
-        <v>0.59037477090311574</v>
+        <v>0.59040637047336153</v>
       </c>
       <c r="W11" s="5">
         <v>30728</v>
@@ -1347,14 +1347,14 @@
       </c>
       <c r="Y11" s="11">
         <f t="shared" ref="Y11:Y48" si="8">Z11-X11</f>
-        <v>5034</v>
+        <v>5036</v>
       </c>
       <c r="Z11" s="6">
-        <v>18797</v>
+        <v>18799</v>
       </c>
       <c r="AA11" s="12">
         <f t="shared" ref="AA11:AA48" si="9">Z11/W11</f>
-        <v>0.61172220775839625</v>
+        <v>0.61178729497526685</v>
       </c>
       <c r="AB11" s="5">
         <v>79070</v>
@@ -1432,14 +1432,14 @@
       </c>
       <c r="AX11" s="11">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>10824</v>
+        <v>10825</v>
       </c>
       <c r="AY11" s="6">
-        <v>19506</v>
+        <v>19507</v>
       </c>
       <c r="AZ11" s="12">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.66741942106343666</v>
+        <v>0.66745363717238071</v>
       </c>
       <c r="BA11" s="5">
         <v>28879</v>
@@ -1449,14 +1449,14 @@
       </c>
       <c r="BC11" s="11">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>10977</v>
+        <v>10978</v>
       </c>
       <c r="BD11" s="6">
-        <v>19557</v>
+        <v>19558</v>
       </c>
       <c r="BE11" s="12">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>0.67720488936597523</v>
+        <v>0.67723951660376047</v>
       </c>
       <c r="BF11" s="5">
         <v>86666</v>
@@ -1466,14 +1466,14 @@
       </c>
       <c r="BH11" s="11">
         <f t="shared" ref="BH11:BH48" si="22">BI11-BG11</f>
-        <v>63179</v>
+        <v>63180</v>
       </c>
       <c r="BI11" s="6">
-        <v>75337</v>
+        <v>75338</v>
       </c>
       <c r="BJ11" s="12">
         <f t="shared" ref="BJ11:BJ48" si="23">BI11/BF11</f>
-        <v>0.86927976369048998</v>
+        <v>0.86929130224078643</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="E12" s="11">
         <f t="shared" si="0"/>
-        <v>4907</v>
+        <v>4908</v>
       </c>
       <c r="F12" s="6">
-        <v>75144</v>
+        <v>75145</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" si="1"/>
-        <v>0.75647814444198358</v>
+        <v>0.75648821148851353</v>
       </c>
       <c r="H12" s="5">
         <v>103832</v>
@@ -1508,14 +1508,14 @@
       </c>
       <c r="J12" s="11">
         <f t="shared" si="2"/>
-        <v>5348</v>
+        <v>5349</v>
       </c>
       <c r="K12" s="6">
-        <v>75762</v>
+        <v>75763</v>
       </c>
       <c r="L12" s="12">
         <f t="shared" si="3"/>
-        <v>0.72965944988057629</v>
+        <v>0.72966908082286774</v>
       </c>
       <c r="M12" s="5">
         <v>284602</v>
@@ -1542,14 +1542,14 @@
       </c>
       <c r="T12" s="11">
         <f t="shared" si="6"/>
-        <v>8158</v>
+        <v>8159</v>
       </c>
       <c r="U12" s="6">
-        <v>76379</v>
+        <v>76380</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="7"/>
-        <v>0.73017284233872515</v>
+        <v>0.73018240220259267</v>
       </c>
       <c r="W12" s="5">
         <v>102000</v>
@@ -1559,14 +1559,14 @@
       </c>
       <c r="Y12" s="11">
         <f t="shared" si="8"/>
-        <v>12262</v>
+        <v>12263</v>
       </c>
       <c r="Z12" s="6">
-        <v>76698</v>
+        <v>76699</v>
       </c>
       <c r="AA12" s="12">
         <f t="shared" si="9"/>
-        <v>0.75194117647058822</v>
+        <v>0.75195098039215691</v>
       </c>
       <c r="AB12" s="5">
         <v>289976</v>
@@ -1678,14 +1678,14 @@
       </c>
       <c r="BH12" s="11">
         <f t="shared" si="22"/>
-        <v>218708</v>
+        <v>218710</v>
       </c>
       <c r="BI12" s="6">
-        <v>276497</v>
+        <v>276499</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="23"/>
-        <v>0.91318535056459582</v>
+        <v>0.91319195595525504</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1949,14 +1949,14 @@
       </c>
       <c r="O14" s="11">
         <f t="shared" si="4"/>
-        <v>35300</v>
+        <v>35302</v>
       </c>
       <c r="P14" s="6">
-        <v>98336</v>
+        <v>98338</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="5"/>
-        <v>0.8277023045974109</v>
+        <v>0.82771913876403547</v>
       </c>
       <c r="R14" s="5">
         <v>54910</v>
@@ -1983,14 +1983,14 @@
       </c>
       <c r="Y14" s="11">
         <f t="shared" si="8"/>
-        <v>10192</v>
+        <v>10194</v>
       </c>
       <c r="Z14" s="6">
-        <v>29320</v>
+        <v>29322</v>
       </c>
       <c r="AA14" s="12">
         <f t="shared" si="9"/>
-        <v>0.54841666199053551</v>
+        <v>0.5484540710397845</v>
       </c>
       <c r="AB14" s="5">
         <v>122477</v>
@@ -2000,14 +2000,14 @@
       </c>
       <c r="AD14" s="11">
         <f t="shared" si="10"/>
-        <v>55156</v>
+        <v>55161</v>
       </c>
       <c r="AE14" s="6">
-        <v>102356</v>
+        <v>102361</v>
       </c>
       <c r="AF14" s="12">
         <f t="shared" si="11"/>
-        <v>0.83571609363390675</v>
+        <v>0.83575691762535009</v>
       </c>
       <c r="AG14" s="5">
         <v>49944</v>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="AI14" s="11">
         <f t="shared" si="12"/>
-        <v>22751</v>
+        <v>22753</v>
       </c>
       <c r="AJ14" s="6">
-        <v>29756</v>
+        <v>29758</v>
       </c>
       <c r="AK14" s="12">
         <f t="shared" si="13"/>
-        <v>0.59578728175556628</v>
+        <v>0.59582732660579851</v>
       </c>
       <c r="AL14" s="5">
         <v>48590</v>
@@ -2034,14 +2034,14 @@
       </c>
       <c r="AN14" s="11">
         <f t="shared" si="14"/>
-        <v>19975</v>
+        <v>19976</v>
       </c>
       <c r="AO14" s="6">
-        <v>29771</v>
+        <v>29772</v>
       </c>
       <c r="AP14" s="12">
         <f t="shared" si="15"/>
-        <v>0.61269808602593123</v>
+        <v>0.6127186663922618</v>
       </c>
       <c r="AQ14" s="5">
         <v>123658</v>
@@ -2051,14 +2051,14 @@
       </c>
       <c r="AS14" s="11">
         <f t="shared" si="16"/>
-        <v>87212</v>
+        <v>87218</v>
       </c>
       <c r="AT14" s="6">
-        <v>105102</v>
+        <v>105108</v>
       </c>
       <c r="AU14" s="12">
         <f t="shared" si="17"/>
-        <v>0.84994096621326565</v>
+        <v>0.84998948713386924</v>
       </c>
       <c r="AV14" s="5">
         <v>44859</v>
@@ -2068,14 +2068,14 @@
       </c>
       <c r="AX14" s="11">
         <f t="shared" si="18"/>
-        <v>19901</v>
+        <v>19902</v>
       </c>
       <c r="AY14" s="6">
-        <v>30194</v>
+        <v>30195</v>
       </c>
       <c r="AZ14" s="12">
         <f t="shared" si="19"/>
-        <v>0.67308678303127578</v>
+        <v>0.67310907510198625</v>
       </c>
       <c r="BA14" s="5">
         <v>44209</v>
@@ -2085,14 +2085,14 @@
       </c>
       <c r="BC14" s="11">
         <f t="shared" si="20"/>
-        <v>19907</v>
+        <v>19908</v>
       </c>
       <c r="BD14" s="6">
-        <v>30164</v>
+        <v>30165</v>
       </c>
       <c r="BE14" s="12">
         <f t="shared" si="21"/>
-        <v>0.68230450813182841</v>
+        <v>0.68232712796037009</v>
       </c>
       <c r="BF14" s="5">
         <v>128280</v>
@@ -2102,14 +2102,14 @@
       </c>
       <c r="BH14" s="11">
         <f t="shared" si="22"/>
-        <v>92367</v>
+        <v>92374</v>
       </c>
       <c r="BI14" s="6">
-        <v>108318</v>
+        <v>108325</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="23"/>
-        <v>0.84438727782974743</v>
+        <v>0.84444184596195826</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2424,14 +2424,14 @@
       </c>
       <c r="AD16" s="11">
         <f t="shared" si="10"/>
-        <v>274647</v>
+        <v>274649</v>
       </c>
       <c r="AE16" s="6">
-        <v>585349</v>
+        <v>585351</v>
       </c>
       <c r="AF16" s="12">
         <f t="shared" si="11"/>
-        <v>0.86723895003681717</v>
+        <v>0.86724191318854382</v>
       </c>
       <c r="AG16" s="5">
         <v>255869</v>
@@ -2492,14 +2492,14 @@
       </c>
       <c r="AX16" s="11">
         <f t="shared" si="18"/>
-        <v>83270</v>
+        <v>83271</v>
       </c>
       <c r="AY16" s="6">
-        <v>162686</v>
+        <v>162687</v>
       </c>
       <c r="AZ16" s="12">
         <f t="shared" si="19"/>
-        <v>0.64433416373912322</v>
+        <v>0.64433812433907489</v>
       </c>
       <c r="BA16" s="5">
         <v>250214</v>
@@ -2526,14 +2526,14 @@
       </c>
       <c r="BH16" s="11">
         <f t="shared" si="22"/>
-        <v>501854</v>
+        <v>501855</v>
       </c>
       <c r="BI16" s="6">
-        <v>605896</v>
+        <v>605897</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="23"/>
-        <v>0.82958086652682772</v>
+        <v>0.82958223570712686</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2585,14 +2585,14 @@
       </c>
       <c r="O17" s="11">
         <f t="shared" si="4"/>
-        <v>111626</v>
+        <v>111628</v>
       </c>
       <c r="P17" s="6">
-        <v>448815</v>
+        <v>448817</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="5"/>
-        <v>0.89688200041165667</v>
+        <v>0.89688599707843664</v>
       </c>
       <c r="R17" s="5">
         <v>195360</v>
@@ -2619,14 +2619,14 @@
       </c>
       <c r="Y17" s="11">
         <f t="shared" si="8"/>
-        <v>28945</v>
+        <v>28948</v>
       </c>
       <c r="Z17" s="6">
-        <v>115022</v>
+        <v>115025</v>
       </c>
       <c r="AA17" s="12">
         <f t="shared" si="9"/>
-        <v>0.59585468070887959</v>
+        <v>0.59587022177095583</v>
       </c>
       <c r="AB17" s="5">
         <v>511436</v>
@@ -2636,14 +2636,14 @@
       </c>
       <c r="AD17" s="11">
         <f t="shared" si="10"/>
-        <v>217801</v>
+        <v>217806</v>
       </c>
       <c r="AE17" s="6">
-        <v>464509</v>
+        <v>464514</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="11"/>
-        <v>0.9082446288489664</v>
+        <v>0.90825440524327583</v>
       </c>
       <c r="AG17" s="5">
         <v>180725</v>
@@ -2653,14 +2653,14 @@
       </c>
       <c r="AI17" s="11">
         <f t="shared" si="12"/>
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="AJ17" s="6">
-        <v>116376</v>
+        <v>116377</v>
       </c>
       <c r="AK17" s="12">
         <f t="shared" si="13"/>
-        <v>0.64393968737031404</v>
+        <v>0.64394522063909254</v>
       </c>
       <c r="AL17" s="5">
         <v>176831</v>
@@ -2670,14 +2670,14 @@
       </c>
       <c r="AN17" s="11">
         <f t="shared" si="14"/>
-        <v>59930</v>
+        <v>59931</v>
       </c>
       <c r="AO17" s="6">
-        <v>116289</v>
+        <v>116290</v>
       </c>
       <c r="AP17" s="12">
         <f t="shared" si="15"/>
-        <v>0.65762790460948595</v>
+        <v>0.65763355972651849</v>
       </c>
       <c r="AQ17" s="5">
         <v>530594</v>
@@ -2687,14 +2687,14 @@
       </c>
       <c r="AS17" s="11">
         <f t="shared" si="16"/>
-        <v>374708</v>
+        <v>374710</v>
       </c>
       <c r="AT17" s="6">
-        <v>475234</v>
+        <v>475236</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="17"/>
-        <v>0.89566410475806357</v>
+        <v>0.89566787411844084</v>
       </c>
       <c r="AV17" s="5">
         <v>171569</v>
@@ -2704,14 +2704,14 @@
       </c>
       <c r="AX17" s="11">
         <f t="shared" si="18"/>
-        <v>54946</v>
+        <v>54949</v>
       </c>
       <c r="AY17" s="6">
-        <v>117200</v>
+        <v>117203</v>
       </c>
       <c r="AZ17" s="12">
         <f t="shared" si="19"/>
-        <v>0.68310708811032295</v>
+        <v>0.68312457378663982</v>
       </c>
       <c r="BA17" s="5">
         <v>168653</v>
@@ -2721,14 +2721,14 @@
       </c>
       <c r="BC17" s="11">
         <f t="shared" si="20"/>
-        <v>57283</v>
+        <v>57285</v>
       </c>
       <c r="BD17" s="6">
-        <v>117355</v>
+        <v>117357</v>
       </c>
       <c r="BE17" s="12">
         <f t="shared" si="21"/>
-        <v>0.69583701446164614</v>
+        <v>0.69584887313003618</v>
       </c>
       <c r="BF17" s="5">
         <v>551432</v>
@@ -2738,14 +2738,14 @@
       </c>
       <c r="BH17" s="11">
         <f t="shared" si="22"/>
-        <v>407031</v>
+        <v>407035</v>
       </c>
       <c r="BI17" s="6">
-        <v>486571</v>
+        <v>486575</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="23"/>
-        <v>0.88237715620421009</v>
+        <v>0.88238441004511892</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2763,14 +2763,14 @@
       </c>
       <c r="E18" s="11">
         <f t="shared" si="0"/>
-        <v>44576</v>
+        <v>44578</v>
       </c>
       <c r="F18" s="6">
-        <v>257938</v>
+        <v>257940</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="1"/>
-        <v>0.672840198561654</v>
+        <v>0.67284541563086109</v>
       </c>
       <c r="H18" s="5">
         <v>402114</v>
@@ -2780,14 +2780,14 @@
       </c>
       <c r="J18" s="11">
         <f t="shared" si="2"/>
-        <v>48211</v>
+        <v>48212</v>
       </c>
       <c r="K18" s="6">
-        <v>261684</v>
+        <v>261685</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="3"/>
-        <v>0.65077067697220192</v>
+        <v>0.65077316382916284</v>
       </c>
       <c r="M18" s="5">
         <v>1006440</v>
@@ -2797,14 +2797,14 @@
       </c>
       <c r="O18" s="11">
         <f t="shared" si="4"/>
-        <v>254403</v>
+        <v>254408</v>
       </c>
       <c r="P18" s="6">
-        <v>869025</v>
+        <v>869030</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="5"/>
-        <v>0.86346428997257663</v>
+        <v>0.86346925797861773</v>
       </c>
       <c r="R18" s="5">
         <v>418258</v>
@@ -2814,14 +2814,14 @@
       </c>
       <c r="T18" s="11">
         <f t="shared" si="6"/>
-        <v>64616</v>
+        <v>64618</v>
       </c>
       <c r="U18" s="6">
-        <v>267021</v>
+        <v>267023</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="7"/>
-        <v>0.63841217621659363</v>
+        <v>0.63841695795418141</v>
       </c>
       <c r="W18" s="5">
         <v>414163</v>
@@ -2831,14 +2831,14 @@
       </c>
       <c r="Y18" s="11">
         <f t="shared" si="8"/>
-        <v>80970</v>
+        <v>80971</v>
       </c>
       <c r="Z18" s="6">
-        <v>269023</v>
+        <v>269024</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="9"/>
-        <v>0.64955826570698005</v>
+        <v>0.64956068021527757</v>
       </c>
       <c r="AB18" s="5">
         <v>1050898</v>
@@ -2848,14 +2848,14 @@
       </c>
       <c r="AD18" s="11">
         <f t="shared" si="10"/>
-        <v>436535</v>
+        <v>436537</v>
       </c>
       <c r="AE18" s="6">
-        <v>905330</v>
+        <v>905332</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="11"/>
-        <v>0.86148227515895925</v>
+        <v>0.8614841782932311</v>
       </c>
       <c r="AG18" s="5">
         <v>403018</v>
@@ -2865,14 +2865,14 @@
       </c>
       <c r="AI18" s="11">
         <f t="shared" si="12"/>
-        <v>213040</v>
+        <v>213041</v>
       </c>
       <c r="AJ18" s="6">
-        <v>274048</v>
+        <v>274049</v>
       </c>
       <c r="AK18" s="12">
         <f t="shared" si="13"/>
-        <v>0.67998947937809229</v>
+        <v>0.67999196065684409</v>
       </c>
       <c r="AL18" s="5">
         <v>397911</v>
@@ -2882,14 +2882,14 @@
       </c>
       <c r="AN18" s="11">
         <f t="shared" si="14"/>
-        <v>184322</v>
+        <v>184323</v>
       </c>
       <c r="AO18" s="6">
-        <v>274566</v>
+        <v>274567</v>
       </c>
       <c r="AP18" s="12">
         <f t="shared" si="15"/>
-        <v>0.69001862225472532</v>
+        <v>0.69002113537951959</v>
       </c>
       <c r="AQ18" s="5">
         <v>1080975</v>
@@ -2899,14 +2899,14 @@
       </c>
       <c r="AS18" s="11">
         <f t="shared" si="16"/>
-        <v>781411</v>
+        <v>781413</v>
       </c>
       <c r="AT18" s="6">
-        <v>931157</v>
+        <v>931159</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="17"/>
-        <v>0.86140475034112718</v>
+        <v>0.86140660052267626</v>
       </c>
       <c r="AV18" s="5">
         <v>383854</v>
@@ -2916,14 +2916,14 @@
       </c>
       <c r="AX18" s="11">
         <f t="shared" si="18"/>
-        <v>183987</v>
+        <v>183989</v>
       </c>
       <c r="AY18" s="6">
-        <v>278190</v>
+        <v>278192</v>
       </c>
       <c r="AZ18" s="12">
         <f t="shared" si="19"/>
-        <v>0.72472867288083487</v>
+        <v>0.72473388319517318</v>
       </c>
       <c r="BA18" s="5">
         <v>375418</v>
@@ -2933,14 +2933,14 @@
       </c>
       <c r="BC18" s="11">
         <f t="shared" si="20"/>
-        <v>188046</v>
+        <v>188047</v>
       </c>
       <c r="BD18" s="6">
-        <v>278702</v>
+        <v>278703</v>
       </c>
       <c r="BE18" s="12">
         <f t="shared" si="21"/>
-        <v>0.74237782951270315</v>
+        <v>0.74238049321023503</v>
       </c>
       <c r="BF18" s="5">
         <v>1108438</v>
@@ -2950,14 +2950,14 @@
       </c>
       <c r="BH18" s="11">
         <f t="shared" si="22"/>
-        <v>810024</v>
+        <v>810027</v>
       </c>
       <c r="BI18" s="6">
-        <v>946537</v>
+        <v>946540</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="23"/>
-        <v>0.8539377033266633</v>
+        <v>0.85394040983798825</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3009,14 +3009,14 @@
       </c>
       <c r="O19" s="11">
         <f t="shared" si="4"/>
-        <v>84442</v>
+        <v>84443</v>
       </c>
       <c r="P19" s="6">
-        <v>215876</v>
+        <v>215877</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="5"/>
-        <v>0.83002414604512387</v>
+        <v>0.83002799095676782</v>
       </c>
       <c r="R19" s="5">
         <v>130716</v>
@@ -3043,14 +3043,14 @@
       </c>
       <c r="Y19" s="11">
         <f t="shared" si="8"/>
-        <v>32150</v>
+        <v>32151</v>
       </c>
       <c r="Z19" s="6">
-        <v>71442</v>
+        <v>71443</v>
       </c>
       <c r="AA19" s="12">
         <f t="shared" si="9"/>
-        <v>0.55737858396723228</v>
+        <v>0.55738638580066313</v>
       </c>
       <c r="AB19" s="5">
         <v>274935</v>
@@ -3060,14 +3060,14 @@
       </c>
       <c r="AD19" s="11">
         <f t="shared" si="10"/>
-        <v>121052</v>
+        <v>121054</v>
       </c>
       <c r="AE19" s="6">
-        <v>227898</v>
+        <v>227900</v>
       </c>
       <c r="AF19" s="12">
         <f t="shared" si="11"/>
-        <v>0.82891592558241034</v>
+        <v>0.82892320002909781</v>
       </c>
       <c r="AG19" s="5">
         <v>126876</v>
@@ -3111,14 +3111,14 @@
       </c>
       <c r="AS19" s="11">
         <f t="shared" si="16"/>
-        <v>205893</v>
+        <v>205894</v>
       </c>
       <c r="AT19" s="6">
-        <v>236614</v>
+        <v>236615</v>
       </c>
       <c r="AU19" s="12">
         <f t="shared" si="17"/>
-        <v>0.82340618040089086</v>
+        <v>0.82340966035634744</v>
       </c>
       <c r="AV19" s="5">
         <v>121125</v>
@@ -3162,14 +3162,14 @@
       </c>
       <c r="BH19" s="11">
         <f t="shared" si="22"/>
-        <v>219833</v>
+        <v>219834</v>
       </c>
       <c r="BI19" s="6">
-        <v>245314</v>
+        <v>245315</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="23"/>
-        <v>0.80627762896254784</v>
+        <v>0.80628091567928217</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3586,14 +3586,14 @@
       </c>
       <c r="BH21" s="11">
         <f t="shared" si="22"/>
-        <v>6850</v>
+        <v>6851</v>
       </c>
       <c r="BI21" s="6">
-        <v>7507</v>
+        <v>7508</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="23"/>
-        <v>0.69917109062121641</v>
+        <v>0.69926422650647291</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -4010,14 +4010,14 @@
       </c>
       <c r="BH23" s="11">
         <f t="shared" si="22"/>
-        <v>5927</v>
+        <v>5928</v>
       </c>
       <c r="BI23" s="6">
-        <v>6714</v>
+        <v>6715</v>
       </c>
       <c r="BJ23" s="12">
         <f t="shared" si="23"/>
-        <v>0.61432884984902558</v>
+        <v>0.61442034952877667</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4035,14 +4035,14 @@
       </c>
       <c r="E24" s="11">
         <f t="shared" si="0"/>
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F24" s="6">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="G24" s="12">
         <f t="shared" si="1"/>
-        <v>0.61112729391203024</v>
+        <v>0.61141858432857554</v>
       </c>
       <c r="H24" s="5">
         <v>3586</v>
@@ -4052,14 +4052,14 @@
       </c>
       <c r="J24" s="11">
         <f t="shared" si="2"/>
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="K24" s="6">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="3"/>
-        <v>0.60039040713887337</v>
+        <v>0.6006692693809258</v>
       </c>
       <c r="M24" s="5">
         <v>4577</v>
@@ -4476,14 +4476,14 @@
       </c>
       <c r="J26" s="11">
         <f t="shared" si="2"/>
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="K26" s="6">
-        <v>6584</v>
+        <v>6585</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="3"/>
-        <v>0.53580729166666663</v>
+        <v>0.535888671875</v>
       </c>
       <c r="M26" s="5">
         <v>20216</v>
@@ -4493,14 +4493,14 @@
       </c>
       <c r="O26" s="11">
         <f t="shared" si="4"/>
-        <v>5998</v>
+        <v>6000</v>
       </c>
       <c r="P26" s="6">
-        <v>15202</v>
+        <v>15204</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="5"/>
-        <v>0.75197863078749505</v>
+        <v>0.75207756232686984</v>
       </c>
       <c r="R26" s="5">
         <v>13942</v>
@@ -4510,14 +4510,14 @@
       </c>
       <c r="T26" s="11">
         <f t="shared" si="6"/>
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="U26" s="6">
-        <v>7342</v>
+        <v>7343</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="7"/>
-        <v>0.52661024243293642</v>
+        <v>0.52668196815377999</v>
       </c>
       <c r="W26" s="5">
         <v>13671</v>
@@ -4527,14 +4527,14 @@
       </c>
       <c r="Y26" s="11">
         <f t="shared" si="8"/>
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="Z26" s="6">
-        <v>7480</v>
+        <v>7481</v>
       </c>
       <c r="AA26" s="12">
         <f t="shared" si="9"/>
-        <v>0.54714358861824297</v>
+        <v>0.54721673615682831</v>
       </c>
       <c r="AB26" s="5">
         <v>22408</v>
@@ -4544,14 +4544,14 @@
       </c>
       <c r="AD26" s="11">
         <f t="shared" si="10"/>
-        <v>8963</v>
+        <v>8964</v>
       </c>
       <c r="AE26" s="6">
-        <v>16708</v>
+        <v>16709</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="11"/>
-        <v>0.74562656194216348</v>
+        <v>0.74567118886112105</v>
       </c>
       <c r="AG26" s="5">
         <v>13544</v>
@@ -4595,14 +4595,14 @@
       </c>
       <c r="AS26" s="11">
         <f t="shared" si="16"/>
-        <v>14315</v>
+        <v>14316</v>
       </c>
       <c r="AT26" s="6">
-        <v>16810</v>
+        <v>16811</v>
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="17"/>
-        <v>0.72513156759554831</v>
+        <v>0.72517470451212152</v>
       </c>
       <c r="AV26" s="5">
         <v>13582</v>
@@ -4646,14 +4646,14 @@
       </c>
       <c r="BH26" s="11">
         <f t="shared" si="22"/>
-        <v>14206</v>
+        <v>14209</v>
       </c>
       <c r="BI26" s="6">
-        <v>16850</v>
+        <v>16853</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="23"/>
-        <v>0.71088047926422815</v>
+        <v>0.71100704552166394</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4671,14 +4671,14 @@
       </c>
       <c r="E27" s="11">
         <f t="shared" si="0"/>
-        <v>14850</v>
+        <v>14851</v>
       </c>
       <c r="F27" s="6">
-        <v>42022</v>
+        <v>42023</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="1"/>
-        <v>0.50652716336591896</v>
+        <v>0.50653921722255035</v>
       </c>
       <c r="H27" s="5">
         <v>85929</v>
@@ -4688,14 +4688,14 @@
       </c>
       <c r="J27" s="11">
         <f t="shared" si="2"/>
-        <v>15874</v>
+        <v>15875</v>
       </c>
       <c r="K27" s="6">
-        <v>42825</v>
+        <v>42826</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="3"/>
-        <v>0.49837656670041547</v>
+        <v>0.49838820421510782</v>
       </c>
       <c r="M27" s="5">
         <v>136177</v>
@@ -4705,14 +4705,14 @@
       </c>
       <c r="O27" s="11">
         <f t="shared" si="4"/>
-        <v>47561</v>
+        <v>47562</v>
       </c>
       <c r="P27" s="6">
-        <v>102626</v>
+        <v>102627</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="5"/>
-        <v>0.75362212414724949</v>
+        <v>0.75362946753122773</v>
       </c>
       <c r="R27" s="5">
         <v>89310</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="T27" s="11">
         <f t="shared" si="6"/>
-        <v>19204</v>
+        <v>19205</v>
       </c>
       <c r="U27" s="6">
-        <v>44428</v>
+        <v>44429</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="7"/>
-        <v>0.49745829134475422</v>
+        <v>0.49746948829918264</v>
       </c>
       <c r="W27" s="5">
         <v>88186</v>
@@ -4739,14 +4739,14 @@
       </c>
       <c r="Y27" s="11">
         <f t="shared" si="8"/>
-        <v>22435</v>
+        <v>22436</v>
       </c>
       <c r="Z27" s="6">
-        <v>45016</v>
+        <v>45017</v>
       </c>
       <c r="AA27" s="12">
         <f t="shared" si="9"/>
-        <v>0.51046651395913178</v>
+        <v>0.51047785362755993</v>
       </c>
       <c r="AB27" s="5">
         <v>144015</v>
@@ -4756,14 +4756,14 @@
       </c>
       <c r="AD27" s="11">
         <f t="shared" si="10"/>
-        <v>68769</v>
+        <v>68771</v>
       </c>
       <c r="AE27" s="6">
-        <v>108185</v>
+        <v>108187</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="11"/>
-        <v>0.75120647154810261</v>
+        <v>0.75122035899038297</v>
       </c>
       <c r="AG27" s="5">
         <v>86986</v>
@@ -4773,14 +4773,14 @@
       </c>
       <c r="AI27" s="11">
         <f t="shared" si="12"/>
-        <v>37132</v>
+        <v>37133</v>
       </c>
       <c r="AJ27" s="6">
-        <v>45890</v>
+        <v>45891</v>
       </c>
       <c r="AK27" s="12">
         <f t="shared" si="13"/>
-        <v>0.52755615846228132</v>
+        <v>0.52756765456510246</v>
       </c>
       <c r="AL27" s="5">
         <v>86985</v>
@@ -4790,14 +4790,14 @@
       </c>
       <c r="AN27" s="11">
         <f t="shared" si="14"/>
-        <v>35485</v>
+        <v>35487</v>
       </c>
       <c r="AO27" s="6">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="AP27" s="12">
         <f t="shared" si="15"/>
-        <v>0.52987296660343741</v>
+        <v>0.52989595907340348</v>
       </c>
       <c r="AQ27" s="5">
         <v>150627</v>
@@ -4807,14 +4807,14 @@
       </c>
       <c r="AS27" s="11">
         <f t="shared" si="16"/>
-        <v>94454</v>
+        <v>94458</v>
       </c>
       <c r="AT27" s="6">
-        <v>110496</v>
+        <v>110500</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="17"/>
-        <v>0.73357366209245356</v>
+        <v>0.73360021775644468</v>
       </c>
       <c r="AV27" s="5">
         <v>85745</v>
@@ -4824,14 +4824,14 @@
       </c>
       <c r="AX27" s="11">
         <f t="shared" si="18"/>
-        <v>35998</v>
+        <v>35999</v>
       </c>
       <c r="AY27" s="6">
-        <v>46695</v>
+        <v>46696</v>
       </c>
       <c r="AZ27" s="12">
         <f t="shared" si="19"/>
-        <v>0.54457985888389993</v>
+        <v>0.54459152137150857</v>
       </c>
       <c r="BA27" s="5">
         <v>85438</v>
@@ -4841,14 +4841,14 @@
       </c>
       <c r="BC27" s="11">
         <f t="shared" si="20"/>
-        <v>36464</v>
+        <v>36465</v>
       </c>
       <c r="BD27" s="6">
-        <v>46867</v>
+        <v>46868</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="21"/>
-        <v>0.54854982560453192</v>
+        <v>0.54856152999836139</v>
       </c>
       <c r="BF27" s="5">
         <v>157244</v>
@@ -4858,14 +4858,14 @@
       </c>
       <c r="BH27" s="11">
         <f t="shared" si="22"/>
-        <v>99073</v>
+        <v>99076</v>
       </c>
       <c r="BI27" s="6">
-        <v>112441</v>
+        <v>112444</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="23"/>
-        <v>0.71507338912772511</v>
+        <v>0.71509246775711632</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4883,14 +4883,14 @@
       </c>
       <c r="E28" s="11">
         <f t="shared" si="0"/>
-        <v>29616</v>
+        <v>29618</v>
       </c>
       <c r="F28" s="6">
-        <v>149451</v>
+        <v>149453</v>
       </c>
       <c r="G28" s="12">
         <f t="shared" si="1"/>
-        <v>0.68061279789419038</v>
+        <v>0.68062190606740958</v>
       </c>
       <c r="H28" s="5">
         <v>233184</v>
@@ -4900,14 +4900,14 @@
       </c>
       <c r="J28" s="11">
         <f t="shared" si="2"/>
-        <v>32196</v>
+        <v>32199</v>
       </c>
       <c r="K28" s="6">
-        <v>151280</v>
+        <v>151283</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="3"/>
-        <v>0.64875806230273092</v>
+        <v>0.64877092767942912</v>
       </c>
       <c r="M28" s="5">
         <v>511502</v>
@@ -4917,14 +4917,14 @@
       </c>
       <c r="O28" s="11">
         <f t="shared" si="4"/>
-        <v>123073</v>
+        <v>123076</v>
       </c>
       <c r="P28" s="6">
-        <v>452702</v>
+        <v>452705</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="5"/>
-        <v>0.88504443775390906</v>
+        <v>0.88505030283361552</v>
       </c>
       <c r="R28" s="5">
         <v>239310</v>
@@ -4934,14 +4934,14 @@
       </c>
       <c r="T28" s="11">
         <f t="shared" si="6"/>
-        <v>41973</v>
+        <v>41975</v>
       </c>
       <c r="U28" s="6">
-        <v>154814</v>
+        <v>154816</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="7"/>
-        <v>0.6469182232251055</v>
+        <v>0.64692658058585095</v>
       </c>
       <c r="W28" s="5">
         <v>235824</v>
@@ -4951,14 +4951,14 @@
       </c>
       <c r="Y28" s="11">
         <f t="shared" si="8"/>
-        <v>52204</v>
+        <v>52206</v>
       </c>
       <c r="Z28" s="6">
-        <v>156282</v>
+        <v>156284</v>
       </c>
       <c r="AA28" s="12">
         <f t="shared" si="9"/>
-        <v>0.66270608589456548</v>
+        <v>0.66271456679557639</v>
       </c>
       <c r="AB28" s="5">
         <v>536002</v>
@@ -4968,14 +4968,14 @@
       </c>
       <c r="AD28" s="11">
         <f t="shared" si="10"/>
-        <v>216570</v>
+        <v>216573</v>
       </c>
       <c r="AE28" s="6">
-        <v>472343</v>
+        <v>472346</v>
       </c>
       <c r="AF28" s="12">
         <f t="shared" si="11"/>
-        <v>0.88123365211323834</v>
+        <v>0.88123924910727947</v>
       </c>
       <c r="AG28" s="5">
         <v>231591</v>
@@ -4985,14 +4985,14 @@
       </c>
       <c r="AI28" s="11">
         <f t="shared" si="12"/>
-        <v>114025</v>
+        <v>114028</v>
       </c>
       <c r="AJ28" s="6">
-        <v>158893</v>
+        <v>158896</v>
       </c>
       <c r="AK28" s="12">
         <f t="shared" si="13"/>
-        <v>0.68609315560621964</v>
+        <v>0.68610610947748396</v>
       </c>
       <c r="AL28" s="5">
         <v>231682</v>
@@ -5002,14 +5002,14 @@
       </c>
       <c r="AN28" s="11">
         <f t="shared" si="14"/>
-        <v>103641</v>
+        <v>103644</v>
       </c>
       <c r="AO28" s="6">
-        <v>159642</v>
+        <v>159645</v>
       </c>
       <c r="AP28" s="12">
         <f t="shared" si="15"/>
-        <v>0.68905655165269641</v>
+        <v>0.68906950043594239</v>
       </c>
       <c r="AQ28" s="5">
         <v>558638</v>
@@ -5019,14 +5019,14 @@
       </c>
       <c r="AS28" s="11">
         <f t="shared" si="16"/>
-        <v>396306</v>
+        <v>396311</v>
       </c>
       <c r="AT28" s="6">
-        <v>485716</v>
+        <v>485721</v>
       </c>
       <c r="AU28" s="12">
         <f t="shared" si="17"/>
-        <v>0.86946466226787289</v>
+        <v>0.86947361260780687</v>
       </c>
       <c r="AV28" s="5">
         <v>229686</v>
@@ -5036,14 +5036,14 @@
       </c>
       <c r="AX28" s="11">
         <f t="shared" si="18"/>
-        <v>104959</v>
+        <v>104962</v>
       </c>
       <c r="AY28" s="6">
-        <v>162526</v>
+        <v>162529</v>
       </c>
       <c r="AZ28" s="12">
         <f t="shared" si="19"/>
-        <v>0.70760081154271481</v>
+        <v>0.70761387285250299</v>
       </c>
       <c r="BA28" s="5">
         <v>227810</v>
@@ -5053,14 +5053,14 @@
       </c>
       <c r="BC28" s="11">
         <f t="shared" si="20"/>
-        <v>106634</v>
+        <v>106638</v>
       </c>
       <c r="BD28" s="6">
-        <v>163298</v>
+        <v>163302</v>
       </c>
       <c r="BE28" s="12">
         <f t="shared" si="21"/>
-        <v>0.71681664545015589</v>
+        <v>0.71683420394188135</v>
       </c>
       <c r="BF28" s="5">
         <v>582519</v>
@@ -5070,14 +5070,14 @@
       </c>
       <c r="BH28" s="11">
         <f t="shared" si="22"/>
-        <v>415949</v>
+        <v>415952</v>
       </c>
       <c r="BI28" s="6">
-        <v>496931</v>
+        <v>496934</v>
       </c>
       <c r="BJ28" s="12">
         <f t="shared" si="23"/>
-        <v>0.85307260364039628</v>
+        <v>0.85307775368700423</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="O29" s="11">
         <f t="shared" si="4"/>
-        <v>37090</v>
+        <v>37092</v>
       </c>
       <c r="P29" s="6">
-        <v>109705</v>
+        <v>109707</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="5"/>
-        <v>0.86237933528283495</v>
+        <v>0.86239505707008768</v>
       </c>
       <c r="R29" s="5">
         <v>67228</v>
@@ -5180,14 +5180,14 @@
       </c>
       <c r="AD29" s="11">
         <f t="shared" si="10"/>
-        <v>61312</v>
+        <v>61313</v>
       </c>
       <c r="AE29" s="6">
-        <v>114337</v>
+        <v>114338</v>
       </c>
       <c r="AF29" s="12">
         <f t="shared" si="11"/>
-        <v>0.85833433427421779</v>
+        <v>0.85834184133085101</v>
       </c>
       <c r="AG29" s="5">
         <v>65284</v>
@@ -5282,14 +5282,14 @@
       </c>
       <c r="BH29" s="11">
         <f t="shared" si="22"/>
-        <v>104776</v>
+        <v>104777</v>
       </c>
       <c r="BI29" s="6">
-        <v>121523</v>
+        <v>121524</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="23"/>
-        <v>0.83198460948625264</v>
+        <v>0.83199145580019718</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5307,14 +5307,14 @@
       </c>
       <c r="E30" s="11">
         <f t="shared" si="0"/>
-        <v>14586</v>
+        <v>14591</v>
       </c>
       <c r="F30" s="6">
-        <v>53373</v>
+        <v>53378</v>
       </c>
       <c r="G30" s="12">
         <f t="shared" si="1"/>
-        <v>0.56272733982097478</v>
+        <v>0.56278005630120087</v>
       </c>
       <c r="H30" s="5">
         <v>100711</v>
@@ -5324,14 +5324,14 @@
       </c>
       <c r="J30" s="11">
         <f t="shared" si="2"/>
-        <v>15755</v>
+        <v>15760</v>
       </c>
       <c r="K30" s="6">
-        <v>54309</v>
+        <v>54314</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="3"/>
-        <v>0.53925589061770807</v>
+        <v>0.53930553762746869</v>
       </c>
       <c r="M30" s="5">
         <v>200801</v>
@@ -5341,14 +5341,14 @@
       </c>
       <c r="O30" s="11">
         <f t="shared" si="4"/>
-        <v>62184</v>
+        <v>62192</v>
       </c>
       <c r="P30" s="6">
-        <v>161700</v>
+        <v>161708</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="5"/>
-        <v>0.80527487412911292</v>
+        <v>0.80531471456815451</v>
       </c>
       <c r="R30" s="5">
         <v>104405</v>
@@ -5358,14 +5358,14 @@
       </c>
       <c r="T30" s="11">
         <f t="shared" si="6"/>
-        <v>19546</v>
+        <v>19552</v>
       </c>
       <c r="U30" s="6">
-        <v>55987</v>
+        <v>55993</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="7"/>
-        <v>0.53624826397203196</v>
+        <v>0.53630573248407643</v>
       </c>
       <c r="W30" s="5">
         <v>103393</v>
@@ -5375,14 +5375,14 @@
       </c>
       <c r="Y30" s="11">
         <f t="shared" si="8"/>
-        <v>23192</v>
+        <v>23196</v>
       </c>
       <c r="Z30" s="6">
-        <v>56645</v>
+        <v>56649</v>
       </c>
       <c r="AA30" s="12">
         <f t="shared" si="9"/>
-        <v>0.54786107376708293</v>
+        <v>0.54789976110568417</v>
       </c>
       <c r="AB30" s="5">
         <v>214949</v>
@@ -5392,14 +5392,14 @@
       </c>
       <c r="AD30" s="11">
         <f t="shared" si="10"/>
-        <v>93511</v>
+        <v>93516</v>
       </c>
       <c r="AE30" s="6">
-        <v>170802</v>
+        <v>170807</v>
       </c>
       <c r="AF30" s="12">
         <f t="shared" si="11"/>
-        <v>0.79461639737798273</v>
+        <v>0.7946396587097404</v>
       </c>
       <c r="AG30" s="5">
         <v>102459</v>
@@ -5409,14 +5409,14 @@
       </c>
       <c r="AI30" s="11">
         <f t="shared" si="12"/>
-        <v>44351</v>
+        <v>44355</v>
       </c>
       <c r="AJ30" s="6">
-        <v>57984</v>
+        <v>57988</v>
       </c>
       <c r="AK30" s="12">
         <f t="shared" si="13"/>
-        <v>0.56592393054782886</v>
+        <v>0.5659629705540753</v>
       </c>
       <c r="AL30" s="5">
         <v>101956</v>
@@ -5426,14 +5426,14 @@
       </c>
       <c r="AN30" s="11">
         <f t="shared" si="14"/>
-        <v>42720</v>
+        <v>42725</v>
       </c>
       <c r="AO30" s="6">
-        <v>58389</v>
+        <v>58394</v>
       </c>
       <c r="AP30" s="12">
         <f t="shared" si="15"/>
-        <v>0.57268821844717333</v>
+        <v>0.57273725920985519</v>
       </c>
       <c r="AQ30" s="5">
         <v>223141</v>
@@ -5443,14 +5443,14 @@
       </c>
       <c r="AS30" s="11">
         <f t="shared" si="16"/>
-        <v>150084</v>
+        <v>150090</v>
       </c>
       <c r="AT30" s="6">
-        <v>176537</v>
+        <v>176543</v>
       </c>
       <c r="AU30" s="12">
         <f t="shared" si="17"/>
-        <v>0.7911455088934799</v>
+        <v>0.79117239772161996</v>
       </c>
       <c r="AV30" s="5">
         <v>91341</v>
@@ -5460,14 +5460,14 @@
       </c>
       <c r="AX30" s="11">
         <f t="shared" si="18"/>
-        <v>44042</v>
+        <v>44047</v>
       </c>
       <c r="AY30" s="6">
-        <v>59889</v>
+        <v>59894</v>
       </c>
       <c r="AZ30" s="12">
         <f t="shared" si="19"/>
-        <v>0.65566394061812328</v>
+        <v>0.65571868054871307</v>
       </c>
       <c r="BA30" s="5">
         <v>85107</v>
@@ -5477,14 +5477,14 @@
       </c>
       <c r="BC30" s="11">
         <f t="shared" si="20"/>
-        <v>44785</v>
+        <v>44790</v>
       </c>
       <c r="BD30" s="6">
-        <v>60062</v>
+        <v>60067</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="21"/>
-        <v>0.70572338350546959</v>
+        <v>0.70578213307953519</v>
       </c>
       <c r="BF30" s="5">
         <v>218115</v>
@@ -5494,14 +5494,14 @@
       </c>
       <c r="BH30" s="11">
         <f t="shared" si="22"/>
-        <v>155284</v>
+        <v>155291</v>
       </c>
       <c r="BI30" s="6">
-        <v>180134</v>
+        <v>180141</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="23"/>
-        <v>0.82586708846250834</v>
+        <v>0.82589918162437248</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="E31" s="11">
         <f t="shared" si="0"/>
-        <v>9391</v>
+        <v>9392</v>
       </c>
       <c r="F31" s="6">
-        <v>32554</v>
+        <v>32555</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="1"/>
-        <v>0.64479965139540873</v>
+        <v>0.64481945847445876</v>
       </c>
       <c r="H31" s="5">
         <v>53177</v>
@@ -5536,14 +5536,14 @@
       </c>
       <c r="J31" s="11">
         <f t="shared" si="2"/>
-        <v>9913</v>
+        <v>9914</v>
       </c>
       <c r="K31" s="6">
-        <v>32872</v>
+        <v>32873</v>
       </c>
       <c r="L31" s="12">
         <f t="shared" si="3"/>
-        <v>0.61816198732534744</v>
+        <v>0.61818079244786284</v>
       </c>
       <c r="M31" s="5">
         <v>98284</v>
@@ -5553,14 +5553,14 @@
       </c>
       <c r="O31" s="11">
         <f t="shared" si="4"/>
-        <v>34885</v>
+        <v>34888</v>
       </c>
       <c r="P31" s="6">
-        <v>85283</v>
+        <v>85286</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="5"/>
-        <v>0.86772007651296246</v>
+        <v>0.86775060030116802</v>
       </c>
       <c r="R31" s="5">
         <v>50949</v>
@@ -5570,14 +5570,14 @@
       </c>
       <c r="T31" s="11">
         <f t="shared" si="6"/>
-        <v>12247</v>
+        <v>12248</v>
       </c>
       <c r="U31" s="6">
-        <v>33428</v>
+        <v>33429</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="7"/>
-        <v>0.65610708747963653</v>
+        <v>0.65612671495024433</v>
       </c>
       <c r="W31" s="5">
         <v>49380</v>
@@ -5587,14 +5587,14 @@
       </c>
       <c r="Y31" s="11">
         <f t="shared" si="8"/>
-        <v>14455</v>
+        <v>14456</v>
       </c>
       <c r="Z31" s="6">
-        <v>33558</v>
+        <v>33559</v>
       </c>
       <c r="AA31" s="12">
         <f t="shared" si="9"/>
-        <v>0.67958687727825029</v>
+        <v>0.67960712839206161</v>
       </c>
       <c r="AB31" s="5">
         <v>101382</v>
@@ -5604,14 +5604,14 @@
       </c>
       <c r="AD31" s="11">
         <f t="shared" si="10"/>
-        <v>52662</v>
+        <v>52667</v>
       </c>
       <c r="AE31" s="6">
-        <v>88428</v>
+        <v>88433</v>
       </c>
       <c r="AF31" s="12">
         <f t="shared" si="11"/>
-        <v>0.87222583890631478</v>
+        <v>0.872275157325758</v>
       </c>
       <c r="AG31" s="5">
         <v>47462</v>
@@ -5621,14 +5621,14 @@
       </c>
       <c r="AI31" s="11">
         <f t="shared" si="12"/>
-        <v>28046</v>
+        <v>28047</v>
       </c>
       <c r="AJ31" s="6">
-        <v>34091</v>
+        <v>34092</v>
       </c>
       <c r="AK31" s="12">
         <f t="shared" si="13"/>
-        <v>0.71827988706754875</v>
+        <v>0.71830095655471748</v>
       </c>
       <c r="AL31" s="5">
         <v>45806</v>
@@ -5638,14 +5638,14 @@
       </c>
       <c r="AN31" s="11">
         <f t="shared" si="14"/>
-        <v>24273</v>
+        <v>24274</v>
       </c>
       <c r="AO31" s="6">
-        <v>34138</v>
+        <v>34139</v>
       </c>
       <c r="AP31" s="12">
         <f t="shared" si="15"/>
-        <v>0.74527354495044318</v>
+        <v>0.74529537615159591</v>
       </c>
       <c r="AQ31" s="5">
         <v>101564</v>
@@ -5655,14 +5655,14 @@
       </c>
       <c r="AS31" s="11">
         <f t="shared" si="16"/>
-        <v>75025</v>
+        <v>75029</v>
       </c>
       <c r="AT31" s="6">
-        <v>90037</v>
+        <v>90041</v>
       </c>
       <c r="AU31" s="12">
         <f t="shared" si="17"/>
-        <v>0.88650506084833214</v>
+        <v>0.88654444488204487</v>
       </c>
       <c r="AV31" s="5">
         <v>42627</v>
@@ -5706,14 +5706,14 @@
       </c>
       <c r="BH31" s="11">
         <f t="shared" si="22"/>
-        <v>79942</v>
+        <v>79948</v>
       </c>
       <c r="BI31" s="6">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="23"/>
-        <v>0.89384147593394669</v>
+        <v>0.8939001378555157</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5765,14 +5765,14 @@
       </c>
       <c r="O32" s="11">
         <f t="shared" si="4"/>
-        <v>92598</v>
+        <v>92602</v>
       </c>
       <c r="P32" s="6">
-        <v>287429</v>
+        <v>287433</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="5"/>
-        <v>0.8920714826631575</v>
+        <v>0.89208389715832204</v>
       </c>
       <c r="R32" s="5">
         <v>141043</v>
@@ -5799,14 +5799,14 @@
       </c>
       <c r="Y32" s="11">
         <f t="shared" si="8"/>
-        <v>33866</v>
+        <v>33867</v>
       </c>
       <c r="Z32" s="6">
-        <v>94380</v>
+        <v>94381</v>
       </c>
       <c r="AA32" s="12">
         <f t="shared" si="9"/>
-        <v>0.69402161923670858</v>
+        <v>0.69402897271858222</v>
       </c>
       <c r="AB32" s="5">
         <v>328946</v>
@@ -5816,14 +5816,14 @@
       </c>
       <c r="AD32" s="11">
         <f t="shared" si="10"/>
-        <v>164666</v>
+        <v>164670</v>
       </c>
       <c r="AE32" s="6">
-        <v>297961</v>
+        <v>297965</v>
       </c>
       <c r="AF32" s="12">
         <f t="shared" si="11"/>
-        <v>0.90580520814966592</v>
+        <v>0.90581736820025172</v>
       </c>
       <c r="AG32" s="5">
         <v>131546</v>
@@ -5833,14 +5833,14 @@
       </c>
       <c r="AI32" s="11">
         <f t="shared" si="12"/>
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="AJ32" s="6">
-        <v>95691</v>
+        <v>95693</v>
       </c>
       <c r="AK32" s="12">
         <f t="shared" si="13"/>
-        <v>0.72743374941085248</v>
+        <v>0.72744895321788572</v>
       </c>
       <c r="AL32" s="5">
         <v>128868</v>
@@ -5850,14 +5850,14 @@
       </c>
       <c r="AN32" s="11">
         <f t="shared" si="14"/>
-        <v>63817</v>
+        <v>63819</v>
       </c>
       <c r="AO32" s="6">
-        <v>95808</v>
+        <v>95810</v>
       </c>
       <c r="AP32" s="12">
         <f t="shared" si="15"/>
-        <v>0.74345842257193406</v>
+        <v>0.74347394232858433</v>
       </c>
       <c r="AQ32" s="5">
         <v>335747</v>
@@ -5867,14 +5867,14 @@
       </c>
       <c r="AS32" s="11">
         <f t="shared" si="16"/>
-        <v>253836</v>
+        <v>253841</v>
       </c>
       <c r="AT32" s="6">
-        <v>306056</v>
+        <v>306061</v>
       </c>
       <c r="AU32" s="12">
         <f t="shared" si="17"/>
-        <v>0.91156734088465419</v>
+        <v>0.91158223305048147</v>
       </c>
       <c r="AV32" s="5">
         <v>125246</v>
@@ -5884,14 +5884,14 @@
       </c>
       <c r="AX32" s="11">
         <f t="shared" si="18"/>
-        <v>63832</v>
+        <v>63833</v>
       </c>
       <c r="AY32" s="6">
-        <v>96808</v>
+        <v>96809</v>
       </c>
       <c r="AZ32" s="12">
         <f t="shared" si="19"/>
-        <v>0.7729428484742028</v>
+        <v>0.77295083276112608</v>
       </c>
       <c r="BA32" s="5">
         <v>123206</v>
@@ -5901,14 +5901,14 @@
       </c>
       <c r="BC32" s="11">
         <f t="shared" si="20"/>
-        <v>65717</v>
+        <v>65718</v>
       </c>
       <c r="BD32" s="6">
-        <v>96990</v>
+        <v>96991</v>
       </c>
       <c r="BE32" s="12">
         <f t="shared" si="21"/>
-        <v>0.78721815495998571</v>
+        <v>0.78722627144781909</v>
       </c>
       <c r="BF32" s="5">
         <v>346732</v>
@@ -5918,14 +5918,14 @@
       </c>
       <c r="BH32" s="11">
         <f t="shared" si="22"/>
-        <v>274365</v>
+        <v>274369</v>
       </c>
       <c r="BI32" s="6">
-        <v>312737</v>
+        <v>312741</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="23"/>
-        <v>0.90195597752731216</v>
+        <v>0.90196751381470419</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5943,14 +5943,14 @@
       </c>
       <c r="E33" s="11">
         <f t="shared" si="0"/>
-        <v>22114</v>
+        <v>22116</v>
       </c>
       <c r="F33" s="6">
-        <v>227287</v>
+        <v>227289</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="1"/>
-        <v>0.72391772409927124</v>
+        <v>0.72392409417520254</v>
       </c>
       <c r="H33" s="5">
         <v>329706</v>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J33" s="11">
         <f t="shared" si="2"/>
-        <v>23700</v>
+        <v>23704</v>
       </c>
       <c r="K33" s="6">
-        <v>228998</v>
+        <v>229002</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="3"/>
-        <v>0.69455211612770162</v>
+        <v>0.69456424814835038</v>
       </c>
       <c r="M33" s="5">
         <v>801034</v>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="O33" s="11">
         <f t="shared" si="4"/>
-        <v>145319</v>
+        <v>145324</v>
       </c>
       <c r="P33" s="6">
-        <v>736130</v>
+        <v>736135</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="5"/>
-        <v>0.91897472516772072</v>
+        <v>0.91898096710002319</v>
       </c>
       <c r="R33" s="5">
         <v>331018</v>
@@ -5994,14 +5994,14 @@
       </c>
       <c r="T33" s="11">
         <f t="shared" si="6"/>
-        <v>34425</v>
+        <v>34430</v>
       </c>
       <c r="U33" s="6">
-        <v>231857</v>
+        <v>231862</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="7"/>
-        <v>0.70043623005395472</v>
+        <v>0.7004513349727205</v>
       </c>
       <c r="W33" s="5">
         <v>322207</v>
@@ -6011,14 +6011,14 @@
       </c>
       <c r="Y33" s="11">
         <f t="shared" si="8"/>
-        <v>46974</v>
+        <v>46978</v>
       </c>
       <c r="Z33" s="6">
-        <v>233018</v>
+        <v>233022</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="9"/>
-        <v>0.72319347500209497</v>
+        <v>0.72320588938167074</v>
       </c>
       <c r="AB33" s="5">
         <v>823883</v>
@@ -6028,14 +6028,14 @@
       </c>
       <c r="AD33" s="11">
         <f t="shared" si="10"/>
-        <v>298870</v>
+        <v>298877</v>
       </c>
       <c r="AE33" s="6">
-        <v>758695</v>
+        <v>758702</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="11"/>
-        <v>0.92087711483305279</v>
+        <v>0.92088561118508327</v>
       </c>
       <c r="AG33" s="5">
         <v>309633</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="AI33" s="11">
         <f t="shared" si="12"/>
-        <v>165945</v>
+        <v>165949</v>
       </c>
       <c r="AJ33" s="6">
-        <v>235458</v>
+        <v>235462</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="13"/>
-        <v>0.76044220092819559</v>
+        <v>0.76045511944786248</v>
       </c>
       <c r="AL33" s="5">
         <v>305879</v>
@@ -6062,14 +6062,14 @@
       </c>
       <c r="AN33" s="11">
         <f t="shared" si="14"/>
-        <v>116944</v>
+        <v>116949</v>
       </c>
       <c r="AO33" s="6">
-        <v>235811</v>
+        <v>235816</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="15"/>
-        <v>0.77092902749126291</v>
+        <v>0.77094537382428996</v>
       </c>
       <c r="AQ33" s="5">
         <v>838229</v>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="AS33" s="11">
         <f t="shared" si="16"/>
-        <v>575949</v>
+        <v>575958</v>
       </c>
       <c r="AT33" s="6">
-        <v>775894</v>
+        <v>775903</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="17"/>
-        <v>0.92563488020576712</v>
+        <v>0.92564561712849358</v>
       </c>
       <c r="AV33" s="5">
         <v>298136</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="AX33" s="11">
         <f t="shared" si="18"/>
-        <v>108165</v>
+        <v>108169</v>
       </c>
       <c r="AY33" s="6">
-        <v>237497</v>
+        <v>237501</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="19"/>
-        <v>0.79660624681353476</v>
+        <v>0.79661966350927094</v>
       </c>
       <c r="BA33" s="5">
         <v>294597</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="BC33" s="11">
         <f t="shared" si="20"/>
-        <v>112361</v>
+        <v>112364</v>
       </c>
       <c r="BD33" s="6">
-        <v>237889</v>
+        <v>237892</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="21"/>
-        <v>0.80750652586414662</v>
+        <v>0.80751670926723629</v>
       </c>
       <c r="BF33" s="5">
         <v>864165</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="BH33" s="11">
         <f t="shared" si="22"/>
-        <v>636683</v>
+        <v>636690</v>
       </c>
       <c r="BI33" s="6">
-        <v>791648</v>
+        <v>791655</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="23"/>
-        <v>0.91608431260233869</v>
+        <v>0.91609241290725729</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6554,14 +6554,14 @@
       </c>
       <c r="BH35" s="11">
         <f t="shared" si="22"/>
-        <v>5190</v>
+        <v>5191</v>
       </c>
       <c r="BI35" s="6">
-        <v>7331</v>
+        <v>7332</v>
       </c>
       <c r="BJ35" s="12">
         <f t="shared" si="23"/>
-        <v>0.89708761625061184</v>
+        <v>0.89720998531571217</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6579,14 +6579,14 @@
       </c>
       <c r="E36" s="11">
         <f t="shared" si="0"/>
-        <v>57010</v>
+        <v>57013</v>
       </c>
       <c r="F36" s="6">
-        <v>323157</v>
+        <v>323160</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="1"/>
-        <v>0.58149791626179526</v>
+        <v>0.58150331454729975</v>
       </c>
       <c r="H36" s="5">
         <v>576385</v>
@@ -6596,14 +6596,14 @@
       </c>
       <c r="J36" s="11">
         <f t="shared" si="2"/>
-        <v>61324</v>
+        <v>61330</v>
       </c>
       <c r="K36" s="6">
-        <v>325763</v>
+        <v>325769</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="3"/>
-        <v>0.56518299400574268</v>
+        <v>0.56519340371453108</v>
       </c>
       <c r="M36" s="5">
         <v>1291465</v>
@@ -6613,14 +6613,14 @@
       </c>
       <c r="O36" s="11">
         <f t="shared" si="4"/>
-        <v>325469</v>
+        <v>325474</v>
       </c>
       <c r="P36" s="6">
-        <v>1125061</v>
+        <v>1125066</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>0.87115097970134692</v>
+        <v>0.87115485127355363</v>
       </c>
       <c r="R36" s="5">
         <v>567427</v>
@@ -6630,14 +6630,14 @@
       </c>
       <c r="T36" s="11">
         <f t="shared" si="6"/>
-        <v>80868</v>
+        <v>80873</v>
       </c>
       <c r="U36" s="6">
-        <v>330313</v>
+        <v>330318</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="7"/>
-        <v>0.58212422038429612</v>
+        <v>0.58213303209047151</v>
       </c>
       <c r="W36" s="5">
         <v>554725</v>
@@ -6647,14 +6647,14 @@
       </c>
       <c r="Y36" s="11">
         <f t="shared" si="8"/>
-        <v>102836</v>
+        <v>102842</v>
       </c>
       <c r="Z36" s="6">
-        <v>331904</v>
+        <v>331910</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="9"/>
-        <v>0.5983216909279373</v>
+        <v>0.5983325070981117</v>
       </c>
       <c r="AB36" s="5">
         <v>1322160</v>
@@ -6664,14 +6664,14 @@
       </c>
       <c r="AD36" s="11">
         <f t="shared" si="10"/>
-        <v>585398</v>
+        <v>585408</v>
       </c>
       <c r="AE36" s="6">
-        <v>1156214</v>
+        <v>1156224</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="11"/>
-        <v>0.87448871543534823</v>
+        <v>0.87449627881648218</v>
       </c>
       <c r="AG36" s="5">
         <v>528657</v>
@@ -6681,14 +6681,14 @@
       </c>
       <c r="AI36" s="11">
         <f t="shared" si="12"/>
-        <v>239150</v>
+        <v>239156</v>
       </c>
       <c r="AJ36" s="6">
-        <v>336430</v>
+        <v>336436</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="13"/>
-        <v>0.63638616342921783</v>
+        <v>0.63639751294317493</v>
       </c>
       <c r="AL36" s="5">
         <v>520551</v>
@@ -6698,14 +6698,14 @@
       </c>
       <c r="AN36" s="11">
         <f t="shared" si="14"/>
-        <v>188244</v>
+        <v>188252</v>
       </c>
       <c r="AO36" s="6">
-        <v>336820</v>
+        <v>336828</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="15"/>
-        <v>0.64704515023503939</v>
+        <v>0.64706051856590419</v>
       </c>
       <c r="AQ36" s="5">
         <v>1349417</v>
@@ -6715,14 +6715,14 @@
       </c>
       <c r="AS36" s="11">
         <f t="shared" si="16"/>
-        <v>963160</v>
+        <v>963175</v>
       </c>
       <c r="AT36" s="6">
-        <v>1181457</v>
+        <v>1181472</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="17"/>
-        <v>0.87553143320411708</v>
+        <v>0.8755425491156551</v>
       </c>
       <c r="AV36" s="5">
         <v>479560</v>
@@ -6732,14 +6732,14 @@
       </c>
       <c r="AX36" s="11">
         <f t="shared" si="18"/>
-        <v>182761</v>
+        <v>182772</v>
       </c>
       <c r="AY36" s="6">
-        <v>340640</v>
+        <v>340651</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="19"/>
-        <v>0.71031779130869965</v>
+        <v>0.71034072900158474</v>
       </c>
       <c r="BA36" s="5">
         <v>474262</v>
@@ -6749,14 +6749,14 @@
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="20"/>
-        <v>186121</v>
+        <v>186134</v>
       </c>
       <c r="BD36" s="6">
-        <v>341565</v>
+        <v>341578</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="21"/>
-        <v>0.72020317883364049</v>
+        <v>0.72023058984274513</v>
       </c>
       <c r="BF36" s="5">
         <v>1384075</v>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="BH36" s="11">
         <f t="shared" si="22"/>
-        <v>1004941</v>
+        <v>1004960</v>
       </c>
       <c r="BI36" s="6">
-        <v>1200520</v>
+        <v>1200539</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="23"/>
-        <v>0.86738074165056089</v>
+        <v>0.86739446923035235</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6791,14 +6791,14 @@
       </c>
       <c r="E37" s="11">
         <f t="shared" si="0"/>
-        <v>66170</v>
+        <v>66175</v>
       </c>
       <c r="F37" s="6">
-        <v>317994</v>
+        <v>317999</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="1"/>
-        <v>0.74979663151044429</v>
+        <v>0.74980842098809974</v>
       </c>
       <c r="H37" s="5">
         <v>438161</v>
@@ -6808,14 +6808,14 @@
       </c>
       <c r="J37" s="11">
         <f t="shared" si="2"/>
-        <v>71247</v>
+        <v>71254</v>
       </c>
       <c r="K37" s="6">
-        <v>321966</v>
+        <v>321973</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="3"/>
-        <v>0.73481208962002553</v>
+        <v>0.73482806548277912</v>
       </c>
       <c r="M37" s="5">
         <v>650458</v>
@@ -6825,14 +6825,14 @@
       </c>
       <c r="O37" s="11">
         <f t="shared" si="4"/>
-        <v>156062</v>
+        <v>156069</v>
       </c>
       <c r="P37" s="6">
-        <v>542377</v>
+        <v>542384</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>0.83383861832739392</v>
+        <v>0.83384937997534048</v>
       </c>
       <c r="R37" s="5">
         <v>451955</v>
@@ -6842,14 +6842,14 @@
       </c>
       <c r="T37" s="11">
         <f t="shared" si="6"/>
-        <v>89260</v>
+        <v>89265</v>
       </c>
       <c r="U37" s="6">
-        <v>330053</v>
+        <v>330058</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="7"/>
-        <v>0.73027845692602145</v>
+        <v>0.73028951997433378</v>
       </c>
       <c r="W37" s="5">
         <v>454656</v>
@@ -6859,14 +6859,14 @@
       </c>
       <c r="Y37" s="11">
         <f t="shared" si="8"/>
-        <v>110083</v>
+        <v>110088</v>
       </c>
       <c r="Z37" s="6">
-        <v>333648</v>
+        <v>333653</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="9"/>
-        <v>0.7338471283783784</v>
+        <v>0.7338581257038288</v>
       </c>
       <c r="AB37" s="5">
         <v>682420</v>
@@ -6876,14 +6876,14 @@
       </c>
       <c r="AD37" s="11">
         <f t="shared" si="10"/>
-        <v>263192</v>
+        <v>263199</v>
       </c>
       <c r="AE37" s="6">
-        <v>566098</v>
+        <v>566105</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="11"/>
-        <v>0.82954485507458753</v>
+        <v>0.82955511268720139</v>
       </c>
       <c r="AG37" s="5">
         <v>455096</v>
@@ -6893,14 +6893,14 @@
       </c>
       <c r="AI37" s="11">
         <f t="shared" si="12"/>
-        <v>253283</v>
+        <v>253288</v>
       </c>
       <c r="AJ37" s="6">
-        <v>341035</v>
+        <v>341040</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="13"/>
-        <v>0.7493693638265333</v>
+        <v>0.74938035051945084</v>
       </c>
       <c r="AL37" s="5">
         <v>455153</v>
@@ -6910,14 +6910,14 @@
       </c>
       <c r="AN37" s="11">
         <f t="shared" si="14"/>
-        <v>230805</v>
+        <v>230810</v>
       </c>
       <c r="AO37" s="6">
-        <v>342545</v>
+        <v>342550</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="15"/>
-        <v>0.75259308408381353</v>
+        <v>0.75260406940083879</v>
       </c>
       <c r="AQ37" s="5">
         <v>700400</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="AS37" s="11">
         <f t="shared" si="16"/>
-        <v>433723</v>
+        <v>433734</v>
       </c>
       <c r="AT37" s="6">
-        <v>584968</v>
+        <v>584979</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="17"/>
-        <v>0.83519131924614509</v>
+        <v>0.83520702455739582</v>
       </c>
       <c r="AV37" s="5">
         <v>439004</v>
@@ -6944,14 +6944,14 @@
       </c>
       <c r="AX37" s="11">
         <f t="shared" si="18"/>
-        <v>227670</v>
+        <v>227674</v>
       </c>
       <c r="AY37" s="6">
-        <v>349500</v>
+        <v>349504</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="19"/>
-        <v>0.79612030869878181</v>
+        <v>0.79612942023307309</v>
       </c>
       <c r="BA37" s="5">
         <v>433985</v>
@@ -6961,14 +6961,14 @@
       </c>
       <c r="BC37" s="11">
         <f t="shared" si="20"/>
-        <v>235047</v>
+        <v>235054</v>
       </c>
       <c r="BD37" s="6">
-        <v>351501</v>
+        <v>351508</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="21"/>
-        <v>0.80993813150224081</v>
+        <v>0.80995426109197322</v>
       </c>
       <c r="BF37" s="5">
         <v>706472</v>
@@ -6978,14 +6978,14 @@
       </c>
       <c r="BH37" s="11">
         <f t="shared" si="22"/>
-        <v>460572</v>
+        <v>460586</v>
       </c>
       <c r="BI37" s="6">
-        <v>599304</v>
+        <v>599318</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="23"/>
-        <v>0.84830538223737106</v>
+        <v>0.84832519901708769</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="O38" s="11">
         <f t="shared" si="4"/>
-        <v>7699</v>
+        <v>7700</v>
       </c>
       <c r="P38" s="6">
-        <v>25930</v>
+        <v>25931</v>
       </c>
       <c r="Q38" s="12">
         <f t="shared" si="5"/>
-        <v>0.8835957200299871</v>
+        <v>0.88362979622435767</v>
       </c>
       <c r="R38" s="5">
         <v>16933</v>
@@ -7427,14 +7427,14 @@
       </c>
       <c r="E40" s="11">
         <f t="shared" si="0"/>
-        <v>26500</v>
+        <v>26501</v>
       </c>
       <c r="F40" s="6">
-        <v>135019</v>
+        <v>135020</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="1"/>
-        <v>0.8212235116658152</v>
+        <v>0.82122959394691386</v>
       </c>
       <c r="H40" s="5">
         <v>169073</v>
@@ -7461,14 +7461,14 @@
       </c>
       <c r="O40" s="11">
         <f t="shared" si="4"/>
-        <v>67951</v>
+        <v>67953</v>
       </c>
       <c r="P40" s="6">
-        <v>241228</v>
+        <v>241230</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>0.91456692017803931</v>
+        <v>0.91457450277143792</v>
       </c>
       <c r="R40" s="5">
         <v>173127</v>
@@ -7478,14 +7478,14 @@
       </c>
       <c r="T40" s="11">
         <f t="shared" si="6"/>
-        <v>40604</v>
+        <v>40605</v>
       </c>
       <c r="U40" s="6">
-        <v>139964</v>
+        <v>139965</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="7"/>
-        <v>0.80844697822985434</v>
+        <v>0.80845275433641195</v>
       </c>
       <c r="W40" s="5">
         <v>173204</v>
@@ -7495,14 +7495,14 @@
       </c>
       <c r="Y40" s="11">
         <f t="shared" si="8"/>
-        <v>53698</v>
+        <v>53699</v>
       </c>
       <c r="Z40" s="6">
-        <v>140988</v>
+        <v>140989</v>
       </c>
       <c r="AA40" s="12">
         <f t="shared" si="9"/>
-        <v>0.81399967668183182</v>
+        <v>0.81400545022054915</v>
       </c>
       <c r="AB40" s="5">
         <v>273181</v>
@@ -7512,14 +7512,14 @@
       </c>
       <c r="AD40" s="11">
         <f t="shared" si="10"/>
-        <v>145545</v>
+        <v>145548</v>
       </c>
       <c r="AE40" s="6">
-        <v>249066</v>
+        <v>249069</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="11"/>
-        <v>0.91172519318693468</v>
+        <v>0.91173617491699643</v>
       </c>
       <c r="AG40" s="5">
         <v>172895</v>
@@ -7529,14 +7529,14 @@
       </c>
       <c r="AI40" s="11">
         <f t="shared" si="12"/>
-        <v>112318</v>
+        <v>112319</v>
       </c>
       <c r="AJ40" s="6">
-        <v>143494</v>
+        <v>143495</v>
       </c>
       <c r="AK40" s="12">
         <f t="shared" si="13"/>
-        <v>0.82994881286329858</v>
+        <v>0.82995459672055294</v>
       </c>
       <c r="AL40" s="5">
         <v>173328</v>
@@ -7546,14 +7546,14 @@
       </c>
       <c r="AN40" s="11">
         <f t="shared" si="14"/>
-        <v>107533</v>
+        <v>107534</v>
       </c>
       <c r="AO40" s="6">
-        <v>144479</v>
+        <v>144480</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="15"/>
-        <v>0.83355834025662323</v>
+        <v>0.83356410966491279</v>
       </c>
       <c r="AQ40" s="5">
         <v>281909</v>
@@ -7563,14 +7563,14 @@
       </c>
       <c r="AS40" s="11">
         <f t="shared" si="16"/>
-        <v>206375</v>
+        <v>206376</v>
       </c>
       <c r="AT40" s="6">
-        <v>255762</v>
+        <v>255763</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="17"/>
-        <v>0.90725021194782718</v>
+        <v>0.90725375919179596</v>
       </c>
       <c r="AV40" s="5">
         <v>172382</v>
@@ -7580,14 +7580,14 @@
       </c>
       <c r="AX40" s="11">
         <f t="shared" si="18"/>
-        <v>103189</v>
+        <v>103190</v>
       </c>
       <c r="AY40" s="6">
-        <v>146398</v>
+        <v>146399</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="19"/>
-        <v>0.84926500446682374</v>
+        <v>0.84927080553654088</v>
       </c>
       <c r="BA40" s="5">
         <v>172548</v>
@@ -7597,14 +7597,14 @@
       </c>
       <c r="BC40" s="11">
         <f t="shared" si="20"/>
-        <v>105620</v>
+        <v>105621</v>
       </c>
       <c r="BD40" s="6">
-        <v>146856</v>
+        <v>146857</v>
       </c>
       <c r="BE40" s="12">
         <f t="shared" si="21"/>
-        <v>0.85110230196814796</v>
+        <v>0.85110809745693949</v>
       </c>
       <c r="BF40" s="5">
         <v>291194</v>
@@ -7614,14 +7614,14 @@
       </c>
       <c r="BH40" s="11">
         <f t="shared" si="22"/>
-        <v>208587</v>
+        <v>208596</v>
       </c>
       <c r="BI40" s="6">
-        <v>260549</v>
+        <v>260558</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="23"/>
-        <v>0.89476088106210983</v>
+        <v>0.89479178829234118</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7639,14 +7639,14 @@
       </c>
       <c r="E41" s="11">
         <f t="shared" si="0"/>
-        <v>77266</v>
+        <v>77307</v>
       </c>
       <c r="F41" s="6">
-        <v>452018</v>
+        <v>452059</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="1"/>
-        <v>0.73701510983859686</v>
+        <v>0.73708196031690387</v>
       </c>
       <c r="H41" s="5">
         <v>630477</v>
@@ -7656,14 +7656,14 @@
       </c>
       <c r="J41" s="11">
         <f t="shared" si="2"/>
-        <v>82412</v>
+        <v>82452</v>
       </c>
       <c r="K41" s="6">
-        <v>458481</v>
+        <v>458521</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="3"/>
-        <v>0.72719702701288069</v>
+        <v>0.72726047104018066</v>
       </c>
       <c r="M41" s="5">
         <v>852643</v>
@@ -7673,14 +7673,14 @@
       </c>
       <c r="O41" s="11">
         <f t="shared" si="4"/>
-        <v>165614</v>
+        <v>165674</v>
       </c>
       <c r="P41" s="6">
-        <v>685132</v>
+        <v>685192</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>0.80353911308718884</v>
+        <v>0.80360948251495645</v>
       </c>
       <c r="R41" s="5">
         <v>651946</v>
@@ -7690,14 +7690,14 @@
       </c>
       <c r="T41" s="11">
         <f t="shared" si="6"/>
-        <v>104674</v>
+        <v>104714</v>
       </c>
       <c r="U41" s="6">
-        <v>468796</v>
+        <v>468836</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="7"/>
-        <v>0.71907182496709854</v>
+        <v>0.71913317974188051</v>
       </c>
       <c r="W41" s="5">
         <v>654087</v>
@@ -7707,14 +7707,14 @@
       </c>
       <c r="Y41" s="11">
         <f t="shared" si="8"/>
-        <v>129198</v>
+        <v>129248</v>
       </c>
       <c r="Z41" s="6">
-        <v>472825</v>
+        <v>472875</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="9"/>
-        <v>0.72287784346730632</v>
+        <v>0.72295428589774757</v>
       </c>
       <c r="AB41" s="5">
         <v>882248</v>
@@ -7724,14 +7724,14 @@
       </c>
       <c r="AD41" s="11">
         <f t="shared" si="10"/>
-        <v>296793</v>
+        <v>296867</v>
       </c>
       <c r="AE41" s="6">
-        <v>708641</v>
+        <v>708715</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="11"/>
-        <v>0.80322199653612136</v>
+        <v>0.80330587317851665</v>
       </c>
       <c r="AG41" s="5">
         <v>638043</v>
@@ -7741,14 +7741,14 @@
       </c>
       <c r="AI41" s="11">
         <f t="shared" si="12"/>
-        <v>359813</v>
+        <v>359863</v>
       </c>
       <c r="AJ41" s="6">
-        <v>481340</v>
+        <v>481390</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="13"/>
-        <v>0.75440056547912915</v>
+        <v>0.75447893010345701</v>
       </c>
       <c r="AL41" s="5">
         <v>632207</v>
@@ -7758,14 +7758,14 @@
       </c>
       <c r="AN41" s="11">
         <f t="shared" si="14"/>
-        <v>319856</v>
+        <v>319909</v>
       </c>
       <c r="AO41" s="6">
-        <v>482961</v>
+        <v>483014</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="15"/>
-        <v>0.76392858668126107</v>
+        <v>0.76401241998269553</v>
       </c>
       <c r="AQ41" s="5">
         <v>865402</v>
@@ -7775,14 +7775,14 @@
       </c>
       <c r="AS41" s="11">
         <f t="shared" si="16"/>
-        <v>516733</v>
+        <v>516817</v>
       </c>
       <c r="AT41" s="6">
-        <v>724106</v>
+        <v>724190</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="17"/>
-        <v>0.83672790217725401</v>
+        <v>0.83682496689399843</v>
       </c>
       <c r="AV41" s="5">
         <v>609881</v>
@@ -7792,14 +7792,14 @@
       </c>
       <c r="AX41" s="11">
         <f t="shared" si="18"/>
-        <v>321701</v>
+        <v>321754</v>
       </c>
       <c r="AY41" s="6">
-        <v>489896</v>
+        <v>489949</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="19"/>
-        <v>0.80326489921804423</v>
+        <v>0.80335180141699769</v>
       </c>
       <c r="BA41" s="5">
         <v>594974</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="20"/>
-        <v>336256</v>
+        <v>336313</v>
       </c>
       <c r="BD41" s="6">
-        <v>492265</v>
+        <v>492322</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="21"/>
-        <v>0.82737228853697808</v>
+        <v>0.82746809104263375</v>
       </c>
       <c r="BF41" s="5">
         <v>867754</v>
@@ -7826,14 +7826,14 @@
       </c>
       <c r="BH41" s="11">
         <f t="shared" si="22"/>
-        <v>556438</v>
+        <v>556540</v>
       </c>
       <c r="BI41" s="6">
-        <v>737550</v>
+        <v>737652</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="23"/>
-        <v>0.84995286682631255</v>
+        <v>0.8500704116604475</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8021,14 +8021,14 @@
       </c>
       <c r="BC42" s="11">
         <f t="shared" si="20"/>
-        <v>7321</v>
+        <v>7322</v>
       </c>
       <c r="BD42" s="6">
-        <v>10999</v>
+        <v>11000</v>
       </c>
       <c r="BE42" s="12">
         <f t="shared" si="21"/>
-        <v>0.77880053812929262</v>
+        <v>0.77887134461516672</v>
       </c>
       <c r="BF42" s="5">
         <v>20839</v>
@@ -8038,14 +8038,14 @@
       </c>
       <c r="BH42" s="11">
         <f t="shared" si="22"/>
-        <v>12528</v>
+        <v>12529</v>
       </c>
       <c r="BI42" s="6">
-        <v>16740</v>
+        <v>16741</v>
       </c>
       <c r="BJ42" s="12">
         <f t="shared" si="23"/>
-        <v>0.80330150199145833</v>
+        <v>0.80334948893900859</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8275,14 +8275,14 @@
       </c>
       <c r="E44" s="11">
         <f t="shared" si="0"/>
-        <v>32797</v>
+        <v>32798</v>
       </c>
       <c r="F44" s="6">
-        <v>145309</v>
+        <v>145310</v>
       </c>
       <c r="G44" s="12">
         <f t="shared" si="1"/>
-        <v>0.74958344725126769</v>
+        <v>0.74958860579923958</v>
       </c>
       <c r="H44" s="5">
         <v>201424</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="J44" s="11">
         <f t="shared" si="2"/>
-        <v>35582</v>
+        <v>35583</v>
       </c>
       <c r="K44" s="6">
-        <v>147750</v>
+        <v>147751</v>
       </c>
       <c r="L44" s="12">
         <f t="shared" si="3"/>
-        <v>0.73352728572563353</v>
+        <v>0.73353225037731351</v>
       </c>
       <c r="M44" s="5">
         <v>282140</v>
@@ -8309,14 +8309,14 @@
       </c>
       <c r="O44" s="11">
         <f t="shared" si="4"/>
-        <v>72458</v>
+        <v>72461</v>
       </c>
       <c r="P44" s="6">
-        <v>233289</v>
+        <v>233292</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="5"/>
-        <v>0.8268554618274615</v>
+        <v>0.82686609484653006</v>
       </c>
       <c r="R44" s="5">
         <v>209233</v>
@@ -8326,14 +8326,14 @@
       </c>
       <c r="T44" s="11">
         <f t="shared" si="6"/>
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="U44" s="6">
-        <v>152237</v>
+        <v>152238</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="7"/>
-        <v>0.72759555137095966</v>
+        <v>0.72760033073176789</v>
       </c>
       <c r="W44" s="5">
         <v>210486</v>
@@ -8343,14 +8343,14 @@
       </c>
       <c r="Y44" s="11">
         <f t="shared" si="8"/>
-        <v>56666</v>
+        <v>56667</v>
       </c>
       <c r="Z44" s="6">
-        <v>154136</v>
+        <v>154137</v>
       </c>
       <c r="AA44" s="12">
         <f t="shared" si="9"/>
-        <v>0.73228623281358385</v>
+        <v>0.73229098372338308</v>
       </c>
       <c r="AB44" s="5">
         <v>298180</v>
@@ -8360,14 +8360,14 @@
       </c>
       <c r="AD44" s="11">
         <f t="shared" si="10"/>
-        <v>127292</v>
+        <v>127294</v>
       </c>
       <c r="AE44" s="6">
-        <v>244437</v>
+        <v>244439</v>
       </c>
       <c r="AF44" s="12">
         <f t="shared" si="11"/>
-        <v>0.81976323026359921</v>
+        <v>0.81976993762157091</v>
       </c>
       <c r="AG44" s="5">
         <v>213000</v>
@@ -8377,14 +8377,14 @@
       </c>
       <c r="AI44" s="11">
         <f t="shared" si="12"/>
-        <v>121608</v>
+        <v>121609</v>
       </c>
       <c r="AJ44" s="6">
-        <v>157881</v>
+        <v>157882</v>
       </c>
       <c r="AK44" s="12">
         <f t="shared" si="13"/>
-        <v>0.74122535211267604</v>
+        <v>0.74123004694835681</v>
       </c>
       <c r="AL44" s="5">
         <v>211412</v>
@@ -8394,14 +8394,14 @@
       </c>
       <c r="AN44" s="11">
         <f t="shared" si="14"/>
-        <v>115545</v>
+        <v>115547</v>
       </c>
       <c r="AO44" s="6">
-        <v>158897</v>
+        <v>158899</v>
       </c>
       <c r="AP44" s="12">
         <f t="shared" si="15"/>
-        <v>0.75159877395795882</v>
+        <v>0.75160823415889355</v>
       </c>
       <c r="AQ44" s="5">
         <v>305678</v>
@@ -8411,14 +8411,14 @@
       </c>
       <c r="AS44" s="11">
         <f t="shared" si="16"/>
-        <v>186776</v>
+        <v>186778</v>
       </c>
       <c r="AT44" s="6">
-        <v>252326</v>
+        <v>252328</v>
       </c>
       <c r="AU44" s="12">
         <f t="shared" si="17"/>
-        <v>0.82546339612271735</v>
+        <v>0.82546993895537135</v>
       </c>
       <c r="AV44" s="5">
         <v>207845</v>
@@ -8428,14 +8428,14 @@
       </c>
       <c r="AX44" s="11">
         <f t="shared" si="18"/>
-        <v>111101</v>
+        <v>111102</v>
       </c>
       <c r="AY44" s="6">
-        <v>161564</v>
+        <v>161565</v>
       </c>
       <c r="AZ44" s="12">
         <f t="shared" si="19"/>
-        <v>0.77732925978493594</v>
+        <v>0.77733407106257069</v>
       </c>
       <c r="BA44" s="5">
         <v>209739</v>
@@ -8445,14 +8445,14 @@
       </c>
       <c r="BC44" s="11">
         <f t="shared" si="20"/>
-        <v>115059</v>
+        <v>115060</v>
       </c>
       <c r="BD44" s="6">
-        <v>162521</v>
+        <v>162522</v>
       </c>
       <c r="BE44" s="12">
         <f t="shared" si="21"/>
-        <v>0.77487257973004542</v>
+        <v>0.7748773475605395</v>
       </c>
       <c r="BF44" s="5">
         <v>319463</v>
@@ -8462,14 +8462,14 @@
       </c>
       <c r="BH44" s="11">
         <f t="shared" si="22"/>
-        <v>207901</v>
+        <v>207907</v>
       </c>
       <c r="BI44" s="6">
-        <v>257924</v>
+        <v>257930</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="23"/>
-        <v>0.80736736335663284</v>
+        <v>0.80738614487436733</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8487,14 +8487,14 @@
       </c>
       <c r="E45" s="11">
         <f t="shared" si="0"/>
-        <v>22309</v>
+        <v>22310</v>
       </c>
       <c r="F45" s="6">
-        <v>132667</v>
+        <v>132668</v>
       </c>
       <c r="G45" s="12">
         <f t="shared" si="1"/>
-        <v>0.77306815996643574</v>
+        <v>0.7730739870987291</v>
       </c>
       <c r="H45" s="5">
         <v>177364</v>
@@ -8504,14 +8504,14 @@
       </c>
       <c r="J45" s="11">
         <f t="shared" si="2"/>
-        <v>23857</v>
+        <v>23859</v>
       </c>
       <c r="K45" s="6">
-        <v>134613</v>
+        <v>134615</v>
       </c>
       <c r="L45" s="12">
         <f t="shared" si="3"/>
-        <v>0.7589646151417424</v>
+        <v>0.75897589138720367</v>
       </c>
       <c r="M45" s="5">
         <v>252576</v>
@@ -8521,14 +8521,14 @@
       </c>
       <c r="O45" s="11">
         <f t="shared" si="4"/>
-        <v>53660</v>
+        <v>53663</v>
       </c>
       <c r="P45" s="6">
-        <v>209799</v>
+        <v>209802</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="5"/>
-        <v>0.83063711516533634</v>
+        <v>0.8306489927784112</v>
       </c>
       <c r="R45" s="5">
         <v>182214</v>
@@ -8538,14 +8538,14 @@
       </c>
       <c r="T45" s="11">
         <f t="shared" si="6"/>
-        <v>32047</v>
+        <v>32048</v>
       </c>
       <c r="U45" s="6">
-        <v>137698</v>
+        <v>137699</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="7"/>
-        <v>0.75569385447879966</v>
+        <v>0.75569934253130933</v>
       </c>
       <c r="W45" s="5">
         <v>179895</v>
@@ -8555,14 +8555,14 @@
       </c>
       <c r="Y45" s="11">
         <f t="shared" si="8"/>
-        <v>43450</v>
+        <v>43451</v>
       </c>
       <c r="Z45" s="6">
-        <v>139029</v>
+        <v>139030</v>
       </c>
       <c r="AA45" s="12">
         <f t="shared" si="9"/>
-        <v>0.77283415325606608</v>
+        <v>0.77283971205425384</v>
       </c>
       <c r="AB45" s="5">
         <v>256988</v>
@@ -8572,14 +8572,14 @@
       </c>
       <c r="AD45" s="11">
         <f t="shared" si="10"/>
-        <v>108355</v>
+        <v>108357</v>
       </c>
       <c r="AE45" s="6">
-        <v>218421</v>
+        <v>218423</v>
       </c>
       <c r="AF45" s="12">
         <f t="shared" si="11"/>
-        <v>0.84992684483322178</v>
+        <v>0.84993462729777269</v>
       </c>
       <c r="AG45" s="5">
         <v>177277</v>
@@ -8589,14 +8589,14 @@
       </c>
       <c r="AI45" s="11">
         <f t="shared" si="12"/>
-        <v>104875</v>
+        <v>104877</v>
       </c>
       <c r="AJ45" s="6">
-        <v>142405</v>
+        <v>142407</v>
       </c>
       <c r="AK45" s="12">
         <f t="shared" si="13"/>
-        <v>0.80329089503996576</v>
+        <v>0.80330217681932792</v>
       </c>
       <c r="AL45" s="5">
         <v>180013</v>
@@ -8606,14 +8606,14 @@
       </c>
       <c r="AN45" s="11">
         <f t="shared" si="14"/>
-        <v>98529</v>
+        <v>98531</v>
       </c>
       <c r="AO45" s="6">
-        <v>144249</v>
+        <v>144251</v>
       </c>
       <c r="AP45" s="12">
         <f t="shared" si="15"/>
-        <v>0.80132545982790127</v>
+        <v>0.8013365701366012</v>
       </c>
       <c r="AQ45" s="5">
         <v>268317</v>
@@ -8623,14 +8623,14 @@
       </c>
       <c r="AS45" s="11">
         <f t="shared" si="16"/>
-        <v>162520</v>
+        <v>162524</v>
       </c>
       <c r="AT45" s="6">
-        <v>228543</v>
+        <v>228547</v>
       </c>
       <c r="AU45" s="12">
         <f t="shared" si="17"/>
-        <v>0.85176489003678479</v>
+        <v>0.85177979777651058</v>
       </c>
       <c r="AV45" s="5">
         <v>180726</v>
@@ -8640,14 +8640,14 @@
       </c>
       <c r="AX45" s="11">
         <f t="shared" si="18"/>
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="AY45" s="6">
-        <v>147194</v>
+        <v>147196</v>
       </c>
       <c r="AZ45" s="12">
         <f t="shared" si="19"/>
-        <v>0.81445945796398966</v>
+        <v>0.81447052444031298</v>
       </c>
       <c r="BA45" s="5">
         <v>181857</v>
@@ -8657,14 +8657,14 @@
       </c>
       <c r="BC45" s="11">
         <f t="shared" si="20"/>
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="BD45" s="6">
-        <v>147932</v>
+        <v>147935</v>
       </c>
       <c r="BE45" s="12">
         <f t="shared" si="21"/>
-        <v>0.81345232792798738</v>
+        <v>0.81346882440598933</v>
       </c>
       <c r="BF45" s="5">
         <v>279089</v>
@@ -8674,14 +8674,14 @@
       </c>
       <c r="BH45" s="11">
         <f t="shared" si="22"/>
-        <v>189799</v>
+        <v>189804</v>
       </c>
       <c r="BI45" s="6">
-        <v>233077</v>
+        <v>233082</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="23"/>
-        <v>0.83513502861094491</v>
+        <v>0.83515294404293972</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9085,10 +9085,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+      <c r="A48" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="24"/>
+      <c r="B48" s="28"/>
       <c r="C48" s="15">
         <f>SUM(C10:C47)</f>
         <v>4496316</v>
@@ -9099,15 +9099,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" si="0"/>
-        <v>546805</v>
+        <v>546873</v>
       </c>
       <c r="F48" s="15">
         <f>SUM(F10:F47)</f>
-        <v>3051508</v>
+        <v>3051576</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" si="1"/>
-        <v>0.67866849216113811</v>
+        <v>0.67868361565334823</v>
       </c>
       <c r="H48" s="15">
         <f>SUM(H10:H47)</f>
@@ -9119,15 +9119,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" si="2"/>
-        <v>589200</v>
+        <v>589275</v>
       </c>
       <c r="K48" s="15">
         <f>SUM(K10:K47)</f>
-        <v>3089517</v>
+        <v>3089592</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" si="3"/>
-        <v>0.65982258889509426</v>
+        <v>0.65983860651019943</v>
       </c>
       <c r="M48" s="15">
         <f>SUM(M10:M47)</f>
@@ -9139,15 +9139,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2192163</v>
+        <v>2192283</v>
       </c>
       <c r="P48" s="15">
         <f>SUM(P10:P47)</f>
-        <v>8044814</v>
+        <v>8044934</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.86348228076220035</v>
+        <v>0.86349516084540567</v>
       </c>
       <c r="R48" s="15">
         <f>SUM(R10:R47)</f>
@@ -9159,15 +9159,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>772833</v>
+        <v>772906</v>
       </c>
       <c r="U48" s="15">
         <f>SUM(U10:U47)</f>
-        <v>3153473</v>
+        <v>3153546</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.66032662524242891</v>
+        <v>0.6603419111965636</v>
       </c>
       <c r="W48" s="15">
         <f>SUM(W10:W47)</f>
@@ -9179,15 +9179,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" si="8"/>
-        <v>978160</v>
+        <v>978248</v>
       </c>
       <c r="Z48" s="15">
         <f>SUM(Z10:Z47)</f>
-        <v>3178113</v>
+        <v>3178201</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" si="9"/>
-        <v>0.67234742667008818</v>
+        <v>0.67236604355801732</v>
       </c>
       <c r="AB48" s="15">
         <f>SUM(AB10:AB47)</f>
@@ -9199,15 +9199,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>3987840</v>
+        <v>3987982</v>
       </c>
       <c r="AE48" s="15">
         <f>SUM(AE10:AE47)</f>
-        <v>8342020</v>
+        <v>8342162</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.86381003928762667</v>
+        <v>0.8638247432832511</v>
       </c>
       <c r="AG48" s="15">
         <f>SUM(AG10:AG47)</f>
@@ -9219,15 +9219,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>2361749</v>
+        <v>2361833</v>
       </c>
       <c r="AJ48" s="15">
         <f>SUM(AJ10:AJ47)</f>
-        <v>3233091</v>
+        <v>3233175</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.70140585285340273</v>
+        <v>0.70142407630942039</v>
       </c>
       <c r="AL48" s="15">
         <f>SUM(AL10:AL47)</f>
@@ -9239,15 +9239,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>2046698</v>
+        <v>2046791</v>
       </c>
       <c r="AO48" s="15">
         <f>SUM(AO10:AO47)</f>
-        <v>3245008</v>
+        <v>3245101</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.7097384625681139</v>
+        <v>0.70975880325048479</v>
       </c>
       <c r="AQ48" s="15">
         <f>SUM(AQ10:AQ47)</f>
@@ -9259,15 +9259,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>6759794</v>
+        <v>6759956</v>
       </c>
       <c r="AT48" s="15">
         <f>SUM(AT10:AT47)</f>
-        <v>8562727</v>
+        <v>8562889</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.86474748477504082</v>
+        <v>0.86476384511124371</v>
       </c>
       <c r="AV48" s="15">
         <f>SUM(AV10:AV47)</f>
@@ -9279,15 +9279,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>2013105</v>
+        <v>2013199</v>
       </c>
       <c r="AY48" s="15">
         <f>SUM(AY10:AY47)</f>
-        <v>3290642</v>
+        <v>3290736</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.74409201062148056</v>
+        <v>0.74411326624545859</v>
       </c>
       <c r="BA48" s="15">
         <f>SUM(BA10:BA47)</f>
@@ -9299,15 +9299,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>2072121</v>
+        <v>2072223</v>
       </c>
       <c r="BD48" s="15">
         <f>SUM(BD10:BD47)</f>
-        <v>3302118</v>
+        <v>3302220</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.75708104558739775</v>
+        <v>0.75710443126490834</v>
       </c>
       <c r="BF48" s="15">
         <f>SUM(BF10:BF47)</f>
@@ -9319,15 +9319,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>7183395</v>
+        <v>7183607</v>
       </c>
       <c r="BI48" s="15">
         <f>SUM(BI10:BI47)</f>
-        <v>8730865</v>
+        <v>8731077</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.85807212556135259</v>
+        <v>0.85809296098723753</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
@@ -9471,13 +9471,13 @@
       <c r="BJ58"/>
     </row>
     <row r="59" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A59" s="25" t="s">
+      <c r="A59" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
     </row>
     <row r="62" spans="1:62" x14ac:dyDescent="0.3">
       <c r="C62" s="3"/>
@@ -9510,14 +9510,6 @@
     <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A48:B48"/>
@@ -9529,6 +9521,14 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="H8:L8"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-1-2018-2019.xlsx
+++ b/gstdatabase/GSTR-1-2018-2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A19D9D-A354-48BE-9CAF-CC4C207FA8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA037FF-BAFB-4934-9FE7-E72588326D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -1067,14 +1067,14 @@
       </c>
       <c r="E10" s="11">
         <f>F10-D10</f>
-        <v>5947</v>
+        <v>5948</v>
       </c>
       <c r="F10" s="6">
-        <v>24279</v>
+        <v>24280</v>
       </c>
       <c r="G10" s="12">
         <f>F10/C10</f>
-        <v>0.64325455701568457</v>
+        <v>0.64328105129292068</v>
       </c>
       <c r="H10" s="5">
         <v>39310</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="J10" s="11">
         <f>K10-I10</f>
-        <v>6441</v>
+        <v>6442</v>
       </c>
       <c r="K10" s="6">
-        <v>24653</v>
+        <v>24654</v>
       </c>
       <c r="L10" s="12">
         <f>K10/H10</f>
-        <v>0.62714322055456628</v>
+        <v>0.62716865937420507</v>
       </c>
       <c r="M10" s="5">
         <v>77492</v>
@@ -1101,14 +1101,14 @@
       </c>
       <c r="O10" s="11">
         <f>P10-N10</f>
-        <v>22479</v>
+        <v>22480</v>
       </c>
       <c r="P10" s="6">
-        <v>66449</v>
+        <v>66450</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/M10</f>
-        <v>0.85749496722242291</v>
+        <v>0.85750787178031285</v>
       </c>
       <c r="R10" s="5">
         <v>40446</v>
@@ -1915,14 +1915,14 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" si="0"/>
-        <v>5958</v>
+        <v>5960</v>
       </c>
       <c r="F14" s="6">
-        <v>28299</v>
+        <v>28301</v>
       </c>
       <c r="G14" s="12">
         <f t="shared" si="1"/>
-        <v>0.54046982429335366</v>
+        <v>0.54050802139037435</v>
       </c>
       <c r="H14" s="5">
         <v>53901</v>
@@ -1932,14 +1932,14 @@
       </c>
       <c r="J14" s="11">
         <f t="shared" si="2"/>
-        <v>6566</v>
+        <v>6568</v>
       </c>
       <c r="K14" s="6">
-        <v>28615</v>
+        <v>28617</v>
       </c>
       <c r="L14" s="12">
         <f t="shared" si="3"/>
-        <v>0.53088068866996907</v>
+        <v>0.53091779373295489</v>
       </c>
       <c r="M14" s="5">
         <v>118806</v>
@@ -1949,14 +1949,14 @@
       </c>
       <c r="O14" s="11">
         <f t="shared" si="4"/>
-        <v>35302</v>
+        <v>35305</v>
       </c>
       <c r="P14" s="6">
-        <v>98338</v>
+        <v>98341</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="5"/>
-        <v>0.82771913876403547</v>
+        <v>0.82774439001397238</v>
       </c>
       <c r="R14" s="5">
         <v>54910</v>
@@ -1966,14 +1966,14 @@
       </c>
       <c r="T14" s="11">
         <f t="shared" si="6"/>
-        <v>8469</v>
+        <v>8470</v>
       </c>
       <c r="U14" s="6">
-        <v>29179</v>
+        <v>29180</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="7"/>
-        <v>0.53139683117829173</v>
+        <v>0.53141504279730467</v>
       </c>
       <c r="W14" s="5">
         <v>53463</v>
@@ -1983,14 +1983,14 @@
       </c>
       <c r="Y14" s="11">
         <f t="shared" si="8"/>
-        <v>10194</v>
+        <v>10196</v>
       </c>
       <c r="Z14" s="6">
-        <v>29322</v>
+        <v>29324</v>
       </c>
       <c r="AA14" s="12">
         <f t="shared" si="9"/>
-        <v>0.5484540710397845</v>
+        <v>0.54849148008903359</v>
       </c>
       <c r="AB14" s="5">
         <v>122477</v>
@@ -2000,14 +2000,14 @@
       </c>
       <c r="AD14" s="11">
         <f t="shared" si="10"/>
-        <v>55161</v>
+        <v>55164</v>
       </c>
       <c r="AE14" s="6">
-        <v>102361</v>
+        <v>102364</v>
       </c>
       <c r="AF14" s="12">
         <f t="shared" si="11"/>
-        <v>0.83575691762535009</v>
+        <v>0.83578141202021605</v>
       </c>
       <c r="AG14" s="5">
         <v>49944</v>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="AI14" s="11">
         <f t="shared" si="12"/>
-        <v>22753</v>
+        <v>22755</v>
       </c>
       <c r="AJ14" s="6">
-        <v>29758</v>
+        <v>29760</v>
       </c>
       <c r="AK14" s="12">
         <f t="shared" si="13"/>
-        <v>0.59582732660579851</v>
+        <v>0.59586737145603075</v>
       </c>
       <c r="AL14" s="5">
         <v>48590</v>
@@ -2034,14 +2034,14 @@
       </c>
       <c r="AN14" s="11">
         <f t="shared" si="14"/>
-        <v>19976</v>
+        <v>19978</v>
       </c>
       <c r="AO14" s="6">
-        <v>29772</v>
+        <v>29774</v>
       </c>
       <c r="AP14" s="12">
         <f t="shared" si="15"/>
-        <v>0.6127186663922618</v>
+        <v>0.61275982712492283</v>
       </c>
       <c r="AQ14" s="5">
         <v>123658</v>
@@ -2051,14 +2051,14 @@
       </c>
       <c r="AS14" s="11">
         <f t="shared" si="16"/>
-        <v>87218</v>
+        <v>87220</v>
       </c>
       <c r="AT14" s="6">
-        <v>105108</v>
+        <v>105110</v>
       </c>
       <c r="AU14" s="12">
         <f t="shared" si="17"/>
-        <v>0.84998948713386924</v>
+        <v>0.85000566077407047</v>
       </c>
       <c r="AV14" s="5">
         <v>44859</v>
@@ -2068,14 +2068,14 @@
       </c>
       <c r="AX14" s="11">
         <f t="shared" si="18"/>
-        <v>19902</v>
+        <v>19903</v>
       </c>
       <c r="AY14" s="6">
-        <v>30195</v>
+        <v>30196</v>
       </c>
       <c r="AZ14" s="12">
         <f t="shared" si="19"/>
-        <v>0.67310907510198625</v>
+        <v>0.67313136717269673</v>
       </c>
       <c r="BA14" s="5">
         <v>44209</v>
@@ -2085,14 +2085,14 @@
       </c>
       <c r="BC14" s="11">
         <f t="shared" si="20"/>
-        <v>19908</v>
+        <v>19910</v>
       </c>
       <c r="BD14" s="6">
-        <v>30165</v>
+        <v>30167</v>
       </c>
       <c r="BE14" s="12">
         <f t="shared" si="21"/>
-        <v>0.68232712796037009</v>
+        <v>0.68237236761745346</v>
       </c>
       <c r="BF14" s="5">
         <v>128280</v>
@@ -2102,14 +2102,14 @@
       </c>
       <c r="BH14" s="11">
         <f t="shared" si="22"/>
-        <v>92374</v>
+        <v>92377</v>
       </c>
       <c r="BI14" s="6">
-        <v>108325</v>
+        <v>108328</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="23"/>
-        <v>0.84444184596195826</v>
+        <v>0.84446523230433423</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2424,14 +2424,14 @@
       </c>
       <c r="AD16" s="11">
         <f t="shared" si="10"/>
-        <v>274649</v>
+        <v>274651</v>
       </c>
       <c r="AE16" s="6">
-        <v>585351</v>
+        <v>585353</v>
       </c>
       <c r="AF16" s="12">
         <f t="shared" si="11"/>
-        <v>0.86724191318854382</v>
+        <v>0.86724487634027059</v>
       </c>
       <c r="AG16" s="5">
         <v>255869</v>
@@ -2475,14 +2475,14 @@
       </c>
       <c r="AS16" s="11">
         <f t="shared" si="16"/>
-        <v>481536</v>
+        <v>481537</v>
       </c>
       <c r="AT16" s="6">
-        <v>596767</v>
+        <v>596768</v>
       </c>
       <c r="AU16" s="12">
         <f t="shared" si="17"/>
-        <v>0.85210432001370751</v>
+        <v>0.85210574788140125</v>
       </c>
       <c r="AV16" s="5">
         <v>252487</v>
@@ -2526,14 +2526,14 @@
       </c>
       <c r="BH16" s="11">
         <f t="shared" si="22"/>
-        <v>501855</v>
+        <v>501856</v>
       </c>
       <c r="BI16" s="6">
-        <v>605897</v>
+        <v>605898</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="23"/>
-        <v>0.82958223570712686</v>
+        <v>0.829583604887426</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2551,14 +2551,14 @@
       </c>
       <c r="E17" s="11">
         <f t="shared" si="0"/>
-        <v>14038</v>
+        <v>14039</v>
       </c>
       <c r="F17" s="6">
-        <v>112559</v>
+        <v>112560</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="1"/>
-        <v>0.61948397891005957</v>
+        <v>0.61948948254796421</v>
       </c>
       <c r="H17" s="5">
         <v>194250</v>
@@ -2568,14 +2568,14 @@
       </c>
       <c r="J17" s="11">
         <f t="shared" si="2"/>
-        <v>14912</v>
+        <v>14913</v>
       </c>
       <c r="K17" s="6">
-        <v>113273</v>
+        <v>113274</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="3"/>
-        <v>0.58312998712998709</v>
+        <v>0.58313513513513515</v>
       </c>
       <c r="M17" s="5">
         <v>500417</v>
@@ -2670,14 +2670,14 @@
       </c>
       <c r="AN17" s="11">
         <f t="shared" si="14"/>
-        <v>59931</v>
+        <v>59932</v>
       </c>
       <c r="AO17" s="6">
-        <v>116290</v>
+        <v>116291</v>
       </c>
       <c r="AP17" s="12">
         <f t="shared" si="15"/>
-        <v>0.65763355972651849</v>
+        <v>0.65763921484355115</v>
       </c>
       <c r="AQ17" s="5">
         <v>530594</v>
@@ -2687,14 +2687,14 @@
       </c>
       <c r="AS17" s="11">
         <f t="shared" si="16"/>
-        <v>374710</v>
+        <v>374714</v>
       </c>
       <c r="AT17" s="6">
-        <v>475236</v>
+        <v>475240</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="17"/>
-        <v>0.89566787411844084</v>
+        <v>0.89567541283919527</v>
       </c>
       <c r="AV17" s="5">
         <v>171569</v>
@@ -2738,14 +2738,14 @@
       </c>
       <c r="BH17" s="11">
         <f t="shared" si="22"/>
-        <v>407035</v>
+        <v>407039</v>
       </c>
       <c r="BI17" s="6">
-        <v>486575</v>
+        <v>486579</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="23"/>
-        <v>0.88238441004511892</v>
+        <v>0.88239166388602763</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2797,14 +2797,14 @@
       </c>
       <c r="O18" s="11">
         <f t="shared" si="4"/>
-        <v>254408</v>
+        <v>254410</v>
       </c>
       <c r="P18" s="6">
-        <v>869030</v>
+        <v>869032</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="5"/>
-        <v>0.86346925797861773</v>
+        <v>0.86347124518103413</v>
       </c>
       <c r="R18" s="5">
         <v>418258</v>
@@ -2848,14 +2848,14 @@
       </c>
       <c r="AD18" s="11">
         <f t="shared" si="10"/>
-        <v>436537</v>
+        <v>436539</v>
       </c>
       <c r="AE18" s="6">
-        <v>905332</v>
+        <v>905334</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="11"/>
-        <v>0.8614841782932311</v>
+        <v>0.86148608142750294</v>
       </c>
       <c r="AG18" s="5">
         <v>403018</v>
@@ -2899,14 +2899,14 @@
       </c>
       <c r="AS18" s="11">
         <f t="shared" si="16"/>
-        <v>781413</v>
+        <v>781416</v>
       </c>
       <c r="AT18" s="6">
-        <v>931159</v>
+        <v>931162</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="17"/>
-        <v>0.86140660052267626</v>
+        <v>0.86140937579499988</v>
       </c>
       <c r="AV18" s="5">
         <v>383854</v>
@@ -2916,14 +2916,14 @@
       </c>
       <c r="AX18" s="11">
         <f t="shared" si="18"/>
-        <v>183989</v>
+        <v>183990</v>
       </c>
       <c r="AY18" s="6">
-        <v>278192</v>
+        <v>278193</v>
       </c>
       <c r="AZ18" s="12">
         <f t="shared" si="19"/>
-        <v>0.72473388319517318</v>
+        <v>0.72473648835234228</v>
       </c>
       <c r="BA18" s="5">
         <v>375418</v>
@@ -2933,14 +2933,14 @@
       </c>
       <c r="BC18" s="11">
         <f t="shared" si="20"/>
-        <v>188047</v>
+        <v>188048</v>
       </c>
       <c r="BD18" s="6">
-        <v>278703</v>
+        <v>278704</v>
       </c>
       <c r="BE18" s="12">
         <f t="shared" si="21"/>
-        <v>0.74238049321023503</v>
+        <v>0.74238315690776679</v>
       </c>
       <c r="BF18" s="5">
         <v>1108438</v>
@@ -2950,14 +2950,14 @@
       </c>
       <c r="BH18" s="11">
         <f t="shared" si="22"/>
-        <v>810027</v>
+        <v>810031</v>
       </c>
       <c r="BI18" s="6">
-        <v>946540</v>
+        <v>946544</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="23"/>
-        <v>0.85394040983798825</v>
+        <v>0.85394401851975488</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3399,14 +3399,14 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" si="0"/>
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F21" s="6">
-        <v>2821</v>
+        <v>2822</v>
       </c>
       <c r="G21" s="12">
         <f t="shared" si="1"/>
-        <v>0.46132461161079313</v>
+        <v>0.46148814390842191</v>
       </c>
       <c r="H21" s="5">
         <v>6221</v>
@@ -3416,14 +3416,14 @@
       </c>
       <c r="J21" s="11">
         <f t="shared" si="2"/>
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="K21" s="6">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="L21" s="12">
         <f t="shared" si="3"/>
-        <v>0.46423404597331619</v>
+        <v>0.46439479183411025</v>
       </c>
       <c r="M21" s="5">
         <v>9000</v>
@@ -3535,14 +3535,14 @@
       </c>
       <c r="AS21" s="11">
         <f t="shared" si="16"/>
-        <v>6453</v>
+        <v>6454</v>
       </c>
       <c r="AT21" s="6">
-        <v>7247</v>
+        <v>7248</v>
       </c>
       <c r="AU21" s="12">
         <f t="shared" si="17"/>
-        <v>0.71441246056782337</v>
+        <v>0.71451104100946372</v>
       </c>
       <c r="AV21" s="5">
         <v>6030</v>
@@ -3586,14 +3586,14 @@
       </c>
       <c r="BH21" s="11">
         <f t="shared" si="22"/>
-        <v>6851</v>
+        <v>6852</v>
       </c>
       <c r="BI21" s="6">
-        <v>7508</v>
+        <v>7509</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="23"/>
-        <v>0.69926422650647291</v>
+        <v>0.69935736239172952</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" si="0"/>
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F22" s="6">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="G22" s="12">
         <f t="shared" si="1"/>
-        <v>0.6010981141083791</v>
+        <v>0.60133683456672238</v>
       </c>
       <c r="H22" s="5">
         <v>4295</v>
@@ -3628,14 +3628,14 @@
       </c>
       <c r="J22" s="11">
         <f t="shared" si="2"/>
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="K22" s="6">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="L22" s="12">
         <f t="shared" si="3"/>
-        <v>0.60838183934807921</v>
+        <v>0.60861466821885912</v>
       </c>
       <c r="M22" s="5">
         <v>5450</v>
@@ -3679,14 +3679,14 @@
       </c>
       <c r="Y22" s="11">
         <f t="shared" si="8"/>
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="Z22" s="6">
-        <v>2794</v>
+        <v>2795</v>
       </c>
       <c r="AA22" s="12">
         <f t="shared" si="9"/>
-        <v>0.62435754189944137</v>
+        <v>0.62458100558659213</v>
       </c>
       <c r="AB22" s="5">
         <v>5857</v>
@@ -4069,14 +4069,14 @@
       </c>
       <c r="O24" s="11">
         <f t="shared" si="4"/>
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="P24" s="6">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="5"/>
-        <v>0.71750054620930737</v>
+        <v>0.71771902993226999</v>
       </c>
       <c r="R24" s="5">
         <v>3714</v>
@@ -4527,14 +4527,14 @@
       </c>
       <c r="Y26" s="11">
         <f t="shared" si="8"/>
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="Z26" s="6">
-        <v>7481</v>
+        <v>7482</v>
       </c>
       <c r="AA26" s="12">
         <f t="shared" si="9"/>
-        <v>0.54721673615682831</v>
+        <v>0.54728988369541365</v>
       </c>
       <c r="AB26" s="5">
         <v>22408</v>
@@ -4544,14 +4544,14 @@
       </c>
       <c r="AD26" s="11">
         <f t="shared" si="10"/>
-        <v>8964</v>
+        <v>8965</v>
       </c>
       <c r="AE26" s="6">
-        <v>16709</v>
+        <v>16710</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="11"/>
-        <v>0.74567118886112105</v>
+        <v>0.74571581578007851</v>
       </c>
       <c r="AG26" s="5">
         <v>13544</v>
@@ -4561,14 +4561,14 @@
       </c>
       <c r="AI26" s="11">
         <f t="shared" si="12"/>
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="AJ26" s="6">
-        <v>7609</v>
+        <v>7610</v>
       </c>
       <c r="AK26" s="12">
         <f t="shared" si="13"/>
-        <v>0.56179858239810987</v>
+        <v>0.56187241582988778</v>
       </c>
       <c r="AL26" s="5">
         <v>13664</v>
@@ -4578,14 +4578,14 @@
       </c>
       <c r="AN26" s="11">
         <f t="shared" si="14"/>
-        <v>6171</v>
+        <v>6172</v>
       </c>
       <c r="AO26" s="6">
-        <v>7605</v>
+        <v>7606</v>
       </c>
       <c r="AP26" s="12">
         <f t="shared" si="15"/>
-        <v>0.55657201405152223</v>
+        <v>0.55664519906323184</v>
       </c>
       <c r="AQ26" s="5">
         <v>23182</v>
@@ -4595,14 +4595,14 @@
       </c>
       <c r="AS26" s="11">
         <f t="shared" si="16"/>
-        <v>14316</v>
+        <v>14317</v>
       </c>
       <c r="AT26" s="6">
-        <v>16811</v>
+        <v>16812</v>
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="17"/>
-        <v>0.72517470451212152</v>
+        <v>0.72521784142869472</v>
       </c>
       <c r="AV26" s="5">
         <v>13582</v>
@@ -4612,14 +4612,14 @@
       </c>
       <c r="AX26" s="11">
         <f t="shared" si="18"/>
-        <v>6375</v>
+        <v>6376</v>
       </c>
       <c r="AY26" s="6">
-        <v>7670</v>
+        <v>7671</v>
       </c>
       <c r="AZ26" s="12">
         <f t="shared" si="19"/>
-        <v>0.56471800912973058</v>
+        <v>0.56479163598880877</v>
       </c>
       <c r="BA26" s="5">
         <v>13478</v>
@@ -4629,14 +4629,14 @@
       </c>
       <c r="BC26" s="11">
         <f t="shared" si="20"/>
-        <v>6134</v>
+        <v>6135</v>
       </c>
       <c r="BD26" s="6">
-        <v>7643</v>
+        <v>7644</v>
       </c>
       <c r="BE26" s="12">
         <f t="shared" si="21"/>
-        <v>0.56707226591482418</v>
+        <v>0.56714646089924325</v>
       </c>
       <c r="BF26" s="5">
         <v>23703</v>
@@ -4646,14 +4646,14 @@
       </c>
       <c r="BH26" s="11">
         <f t="shared" si="22"/>
-        <v>14209</v>
+        <v>14210</v>
       </c>
       <c r="BI26" s="6">
-        <v>16853</v>
+        <v>16854</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="23"/>
-        <v>0.71100704552166394</v>
+        <v>0.71104923427414246</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4917,14 +4917,14 @@
       </c>
       <c r="O28" s="11">
         <f t="shared" si="4"/>
-        <v>123076</v>
+        <v>123077</v>
       </c>
       <c r="P28" s="6">
-        <v>452705</v>
+        <v>452706</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="5"/>
-        <v>0.88505030283361552</v>
+        <v>0.88505225786018427</v>
       </c>
       <c r="R28" s="5">
         <v>239310</v>
@@ -4968,14 +4968,14 @@
       </c>
       <c r="AD28" s="11">
         <f t="shared" si="10"/>
-        <v>216573</v>
+        <v>216574</v>
       </c>
       <c r="AE28" s="6">
-        <v>472346</v>
+        <v>472347</v>
       </c>
       <c r="AF28" s="12">
         <f t="shared" si="11"/>
-        <v>0.88123924910727947</v>
+        <v>0.88124111477195977</v>
       </c>
       <c r="AG28" s="5">
         <v>231591</v>
@@ -5053,14 +5053,14 @@
       </c>
       <c r="BC28" s="11">
         <f t="shared" si="20"/>
-        <v>106638</v>
+        <v>106639</v>
       </c>
       <c r="BD28" s="6">
-        <v>163302</v>
+        <v>163303</v>
       </c>
       <c r="BE28" s="12">
         <f t="shared" si="21"/>
-        <v>0.71683420394188135</v>
+        <v>0.71683859356481283</v>
       </c>
       <c r="BF28" s="5">
         <v>582519</v>
@@ -5129,14 +5129,14 @@
       </c>
       <c r="O29" s="11">
         <f t="shared" si="4"/>
-        <v>37092</v>
+        <v>37093</v>
       </c>
       <c r="P29" s="6">
-        <v>109707</v>
+        <v>109708</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="5"/>
-        <v>0.86239505707008768</v>
+        <v>0.86240291796371416</v>
       </c>
       <c r="R29" s="5">
         <v>67228</v>
@@ -5180,14 +5180,14 @@
       </c>
       <c r="AD29" s="11">
         <f t="shared" si="10"/>
-        <v>61313</v>
+        <v>61315</v>
       </c>
       <c r="AE29" s="6">
-        <v>114338</v>
+        <v>114340</v>
       </c>
       <c r="AF29" s="12">
         <f t="shared" si="11"/>
-        <v>0.85834184133085101</v>
+        <v>0.85835685544411744</v>
       </c>
       <c r="AG29" s="5">
         <v>65284</v>
@@ -5197,14 +5197,14 @@
       </c>
       <c r="AI29" s="11">
         <f t="shared" si="12"/>
-        <v>36097</v>
+        <v>36098</v>
       </c>
       <c r="AJ29" s="6">
-        <v>46506</v>
+        <v>46507</v>
       </c>
       <c r="AK29" s="12">
         <f t="shared" si="13"/>
-        <v>0.71236443845352615</v>
+        <v>0.71237975614239324</v>
       </c>
       <c r="AL29" s="5">
         <v>65226</v>
@@ -5214,14 +5214,14 @@
       </c>
       <c r="AN29" s="11">
         <f t="shared" si="14"/>
-        <v>33100</v>
+        <v>33101</v>
       </c>
       <c r="AO29" s="6">
-        <v>46752</v>
+        <v>46753</v>
       </c>
       <c r="AP29" s="12">
         <f t="shared" si="15"/>
-        <v>0.71676938644098975</v>
+        <v>0.71678471775059027</v>
       </c>
       <c r="AQ29" s="5">
         <v>139370</v>
@@ -5231,14 +5231,14 @@
       </c>
       <c r="AS29" s="11">
         <f t="shared" si="16"/>
-        <v>95974</v>
+        <v>95976</v>
       </c>
       <c r="AT29" s="6">
-        <v>118326</v>
+        <v>118328</v>
       </c>
       <c r="AU29" s="12">
         <f t="shared" si="17"/>
-        <v>0.84900624237640809</v>
+        <v>0.84902059266700147</v>
       </c>
       <c r="AV29" s="5">
         <v>64786</v>
@@ -5282,14 +5282,14 @@
       </c>
       <c r="BH29" s="11">
         <f t="shared" si="22"/>
-        <v>104777</v>
+        <v>104778</v>
       </c>
       <c r="BI29" s="6">
-        <v>121524</v>
+        <v>121525</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="23"/>
-        <v>0.83199145580019718</v>
+        <v>0.83199830211414172</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="O30" s="11">
         <f t="shared" si="4"/>
-        <v>62192</v>
+        <v>62193</v>
       </c>
       <c r="P30" s="6">
-        <v>161708</v>
+        <v>161709</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="5"/>
-        <v>0.80531471456815451</v>
+        <v>0.80531969462303477</v>
       </c>
       <c r="R30" s="5">
         <v>104405</v>
@@ -5392,14 +5392,14 @@
       </c>
       <c r="AD30" s="11">
         <f t="shared" si="10"/>
-        <v>93516</v>
+        <v>93518</v>
       </c>
       <c r="AE30" s="6">
-        <v>170807</v>
+        <v>170809</v>
       </c>
       <c r="AF30" s="12">
         <f t="shared" si="11"/>
-        <v>0.7946396587097404</v>
+        <v>0.79464896324244361</v>
       </c>
       <c r="AG30" s="5">
         <v>102459</v>
@@ -5443,14 +5443,14 @@
       </c>
       <c r="AS30" s="11">
         <f t="shared" si="16"/>
-        <v>150090</v>
+        <v>150093</v>
       </c>
       <c r="AT30" s="6">
-        <v>176543</v>
+        <v>176546</v>
       </c>
       <c r="AU30" s="12">
         <f t="shared" si="17"/>
-        <v>0.79117239772161996</v>
+        <v>0.79118584213568999</v>
       </c>
       <c r="AV30" s="5">
         <v>91341</v>
@@ -5494,14 +5494,14 @@
       </c>
       <c r="BH30" s="11">
         <f t="shared" si="22"/>
-        <v>155291</v>
+        <v>155293</v>
       </c>
       <c r="BI30" s="6">
-        <v>180141</v>
+        <v>180143</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="23"/>
-        <v>0.82589918162437248</v>
+        <v>0.82590835109919081</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5553,14 +5553,14 @@
       </c>
       <c r="O31" s="11">
         <f t="shared" si="4"/>
-        <v>34888</v>
+        <v>34889</v>
       </c>
       <c r="P31" s="6">
-        <v>85286</v>
+        <v>85287</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="5"/>
-        <v>0.86775060030116802</v>
+        <v>0.86776077489723658</v>
       </c>
       <c r="R31" s="5">
         <v>50949</v>
@@ -5604,14 +5604,14 @@
       </c>
       <c r="AD31" s="11">
         <f t="shared" si="10"/>
-        <v>52667</v>
+        <v>52668</v>
       </c>
       <c r="AE31" s="6">
-        <v>88433</v>
+        <v>88434</v>
       </c>
       <c r="AF31" s="12">
         <f t="shared" si="11"/>
-        <v>0.872275157325758</v>
+        <v>0.87228502100964667</v>
       </c>
       <c r="AG31" s="5">
         <v>47462</v>
@@ -5655,14 +5655,14 @@
       </c>
       <c r="AS31" s="11">
         <f t="shared" si="16"/>
-        <v>75029</v>
+        <v>75030</v>
       </c>
       <c r="AT31" s="6">
-        <v>90041</v>
+        <v>90042</v>
       </c>
       <c r="AU31" s="12">
         <f t="shared" si="17"/>
-        <v>0.88654444488204487</v>
+        <v>0.886554290890473</v>
       </c>
       <c r="AV31" s="5">
         <v>42627</v>
@@ -5706,14 +5706,14 @@
       </c>
       <c r="BH31" s="11">
         <f t="shared" si="22"/>
-        <v>79948</v>
+        <v>79949</v>
       </c>
       <c r="BI31" s="6">
-        <v>91429</v>
+        <v>91430</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="23"/>
-        <v>0.8939001378555157</v>
+        <v>0.89390991484244386</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5918,14 +5918,14 @@
       </c>
       <c r="BH32" s="11">
         <f t="shared" si="22"/>
-        <v>274369</v>
+        <v>274371</v>
       </c>
       <c r="BI32" s="6">
-        <v>312741</v>
+        <v>312743</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="23"/>
-        <v>0.90196751381470419</v>
+        <v>0.9019732819584001</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5943,14 +5943,14 @@
       </c>
       <c r="E33" s="11">
         <f t="shared" si="0"/>
-        <v>22116</v>
+        <v>22117</v>
       </c>
       <c r="F33" s="6">
-        <v>227289</v>
+        <v>227290</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="1"/>
-        <v>0.72392409417520254</v>
+        <v>0.72392727921316824</v>
       </c>
       <c r="H33" s="5">
         <v>329706</v>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J33" s="11">
         <f t="shared" si="2"/>
-        <v>23704</v>
+        <v>23705</v>
       </c>
       <c r="K33" s="6">
-        <v>229002</v>
+        <v>229003</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="3"/>
-        <v>0.69456424814835038</v>
+        <v>0.69456728115351252</v>
       </c>
       <c r="M33" s="5">
         <v>801034</v>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="O33" s="11">
         <f t="shared" si="4"/>
-        <v>145324</v>
+        <v>145326</v>
       </c>
       <c r="P33" s="6">
-        <v>736135</v>
+        <v>736137</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="5"/>
-        <v>0.91898096710002319</v>
+        <v>0.91898346387294427</v>
       </c>
       <c r="R33" s="5">
         <v>331018</v>
@@ -5994,14 +5994,14 @@
       </c>
       <c r="T33" s="11">
         <f t="shared" si="6"/>
-        <v>34430</v>
+        <v>34432</v>
       </c>
       <c r="U33" s="6">
-        <v>231862</v>
+        <v>231864</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="7"/>
-        <v>0.7004513349727205</v>
+        <v>0.70045737694022681</v>
       </c>
       <c r="W33" s="5">
         <v>322207</v>
@@ -6011,14 +6011,14 @@
       </c>
       <c r="Y33" s="11">
         <f t="shared" si="8"/>
-        <v>46978</v>
+        <v>46982</v>
       </c>
       <c r="Z33" s="6">
-        <v>233022</v>
+        <v>233026</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="9"/>
-        <v>0.72320588938167074</v>
+        <v>0.72321830376124663</v>
       </c>
       <c r="AB33" s="5">
         <v>823883</v>
@@ -6028,14 +6028,14 @@
       </c>
       <c r="AD33" s="11">
         <f t="shared" si="10"/>
-        <v>298877</v>
+        <v>298880</v>
       </c>
       <c r="AE33" s="6">
-        <v>758702</v>
+        <v>758705</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="11"/>
-        <v>0.92088561118508327</v>
+        <v>0.9208892524788107</v>
       </c>
       <c r="AG33" s="5">
         <v>309633</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="AI33" s="11">
         <f t="shared" si="12"/>
-        <v>165949</v>
+        <v>165951</v>
       </c>
       <c r="AJ33" s="6">
-        <v>235462</v>
+        <v>235464</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="13"/>
-        <v>0.76045511944786248</v>
+        <v>0.76046157870769593</v>
       </c>
       <c r="AL33" s="5">
         <v>305879</v>
@@ -6062,14 +6062,14 @@
       </c>
       <c r="AN33" s="11">
         <f t="shared" si="14"/>
-        <v>116949</v>
+        <v>116953</v>
       </c>
       <c r="AO33" s="6">
-        <v>235816</v>
+        <v>235820</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="15"/>
-        <v>0.77094537382428996</v>
+        <v>0.77095845089071169</v>
       </c>
       <c r="AQ33" s="5">
         <v>838229</v>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="AS33" s="11">
         <f t="shared" si="16"/>
-        <v>575958</v>
+        <v>575961</v>
       </c>
       <c r="AT33" s="6">
-        <v>775903</v>
+        <v>775906</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="17"/>
-        <v>0.92564561712849358</v>
+        <v>0.92564919610273566</v>
       </c>
       <c r="AV33" s="5">
         <v>298136</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="AX33" s="11">
         <f t="shared" si="18"/>
-        <v>108169</v>
+        <v>108170</v>
       </c>
       <c r="AY33" s="6">
-        <v>237501</v>
+        <v>237502</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="19"/>
-        <v>0.79661966350927094</v>
+        <v>0.79662301768320498</v>
       </c>
       <c r="BA33" s="5">
         <v>294597</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="BC33" s="11">
         <f t="shared" si="20"/>
-        <v>112364</v>
+        <v>112365</v>
       </c>
       <c r="BD33" s="6">
-        <v>237892</v>
+        <v>237893</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="21"/>
-        <v>0.80751670926723629</v>
+        <v>0.80752010373493277</v>
       </c>
       <c r="BF33" s="5">
         <v>864165</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="BH33" s="11">
         <f t="shared" si="22"/>
-        <v>636690</v>
+        <v>636696</v>
       </c>
       <c r="BI33" s="6">
-        <v>791655</v>
+        <v>791661</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="23"/>
-        <v>0.91609241290725729</v>
+        <v>0.91609935602575898</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6579,14 +6579,14 @@
       </c>
       <c r="E36" s="11">
         <f t="shared" si="0"/>
-        <v>57013</v>
+        <v>57014</v>
       </c>
       <c r="F36" s="6">
-        <v>323160</v>
+        <v>323161</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="1"/>
-        <v>0.58150331454729975</v>
+        <v>0.58150511397580129</v>
       </c>
       <c r="H36" s="5">
         <v>576385</v>
@@ -6596,14 +6596,14 @@
       </c>
       <c r="J36" s="11">
         <f t="shared" si="2"/>
-        <v>61330</v>
+        <v>61332</v>
       </c>
       <c r="K36" s="6">
-        <v>325769</v>
+        <v>325771</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="3"/>
-        <v>0.56519340371453108</v>
+        <v>0.56519687361746052</v>
       </c>
       <c r="M36" s="5">
         <v>1291465</v>
@@ -6613,14 +6613,14 @@
       </c>
       <c r="O36" s="11">
         <f t="shared" si="4"/>
-        <v>325474</v>
+        <v>325475</v>
       </c>
       <c r="P36" s="6">
-        <v>1125066</v>
+        <v>1125067</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>0.87115485127355363</v>
+        <v>0.87115562558799498</v>
       </c>
       <c r="R36" s="5">
         <v>567427</v>
@@ -6630,14 +6630,14 @@
       </c>
       <c r="T36" s="11">
         <f t="shared" si="6"/>
-        <v>80873</v>
+        <v>80874</v>
       </c>
       <c r="U36" s="6">
-        <v>330318</v>
+        <v>330319</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="7"/>
-        <v>0.58213303209047151</v>
+        <v>0.58213479443170668</v>
       </c>
       <c r="W36" s="5">
         <v>554725</v>
@@ -6664,14 +6664,14 @@
       </c>
       <c r="AD36" s="11">
         <f t="shared" si="10"/>
-        <v>585408</v>
+        <v>585410</v>
       </c>
       <c r="AE36" s="6">
-        <v>1156224</v>
+        <v>1156226</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="11"/>
-        <v>0.87449627881648218</v>
+        <v>0.8744977914927089</v>
       </c>
       <c r="AG36" s="5">
         <v>528657</v>
@@ -6681,14 +6681,14 @@
       </c>
       <c r="AI36" s="11">
         <f t="shared" si="12"/>
-        <v>239156</v>
+        <v>239157</v>
       </c>
       <c r="AJ36" s="6">
-        <v>336436</v>
+        <v>336437</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="13"/>
-        <v>0.63639751294317493</v>
+        <v>0.63639940452883437</v>
       </c>
       <c r="AL36" s="5">
         <v>520551</v>
@@ -6698,14 +6698,14 @@
       </c>
       <c r="AN36" s="11">
         <f t="shared" si="14"/>
-        <v>188252</v>
+        <v>188253</v>
       </c>
       <c r="AO36" s="6">
-        <v>336828</v>
+        <v>336829</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="15"/>
-        <v>0.64706051856590419</v>
+        <v>0.64706243960726229</v>
       </c>
       <c r="AQ36" s="5">
         <v>1349417</v>
@@ -6715,14 +6715,14 @@
       </c>
       <c r="AS36" s="11">
         <f t="shared" si="16"/>
-        <v>963175</v>
+        <v>963176</v>
       </c>
       <c r="AT36" s="6">
-        <v>1181472</v>
+        <v>1181473</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="17"/>
-        <v>0.8755425491156551</v>
+        <v>0.87554329017642429</v>
       </c>
       <c r="AV36" s="5">
         <v>479560</v>
@@ -6732,14 +6732,14 @@
       </c>
       <c r="AX36" s="11">
         <f t="shared" si="18"/>
-        <v>182772</v>
+        <v>182774</v>
       </c>
       <c r="AY36" s="6">
-        <v>340651</v>
+        <v>340653</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="19"/>
-        <v>0.71034072900158474</v>
+        <v>0.71034489949120028</v>
       </c>
       <c r="BA36" s="5">
         <v>474262</v>
@@ -6749,14 +6749,14 @@
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="20"/>
-        <v>186134</v>
+        <v>186135</v>
       </c>
       <c r="BD36" s="6">
-        <v>341578</v>
+        <v>341579</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="21"/>
-        <v>0.72023058984274513</v>
+        <v>0.72023269838190707</v>
       </c>
       <c r="BF36" s="5">
         <v>1384075</v>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="BH36" s="11">
         <f t="shared" si="22"/>
-        <v>1004960</v>
+        <v>1004962</v>
       </c>
       <c r="BI36" s="6">
-        <v>1200539</v>
+        <v>1200541</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="23"/>
-        <v>0.86739446923035235</v>
+        <v>0.86739591423875151</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6791,14 +6791,14 @@
       </c>
       <c r="E37" s="11">
         <f t="shared" si="0"/>
-        <v>66175</v>
+        <v>66179</v>
       </c>
       <c r="F37" s="6">
-        <v>317999</v>
+        <v>318003</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="1"/>
-        <v>0.74980842098809974</v>
+        <v>0.74981785257022404</v>
       </c>
       <c r="H37" s="5">
         <v>438161</v>
@@ -6808,14 +6808,14 @@
       </c>
       <c r="J37" s="11">
         <f t="shared" si="2"/>
-        <v>71254</v>
+        <v>71258</v>
       </c>
       <c r="K37" s="6">
-        <v>321973</v>
+        <v>321977</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="3"/>
-        <v>0.73482806548277912</v>
+        <v>0.73483719454720986</v>
       </c>
       <c r="M37" s="5">
         <v>650458</v>
@@ -6825,14 +6825,14 @@
       </c>
       <c r="O37" s="11">
         <f t="shared" si="4"/>
-        <v>156069</v>
+        <v>156074</v>
       </c>
       <c r="P37" s="6">
-        <v>542384</v>
+        <v>542389</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>0.83384937997534048</v>
+        <v>0.83385706686673078</v>
       </c>
       <c r="R37" s="5">
         <v>451955</v>
@@ -6842,14 +6842,14 @@
       </c>
       <c r="T37" s="11">
         <f t="shared" si="6"/>
-        <v>89265</v>
+        <v>89267</v>
       </c>
       <c r="U37" s="6">
-        <v>330058</v>
+        <v>330060</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="7"/>
-        <v>0.73028951997433378</v>
+        <v>0.73029394519365864</v>
       </c>
       <c r="W37" s="5">
         <v>454656</v>
@@ -6859,14 +6859,14 @@
       </c>
       <c r="Y37" s="11">
         <f t="shared" si="8"/>
-        <v>110088</v>
+        <v>110089</v>
       </c>
       <c r="Z37" s="6">
-        <v>333653</v>
+        <v>333654</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="9"/>
-        <v>0.7338581257038288</v>
+        <v>0.73386032516891897</v>
       </c>
       <c r="AB37" s="5">
         <v>682420</v>
@@ -6876,14 +6876,14 @@
       </c>
       <c r="AD37" s="11">
         <f t="shared" si="10"/>
-        <v>263199</v>
+        <v>263204</v>
       </c>
       <c r="AE37" s="6">
-        <v>566105</v>
+        <v>566110</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="11"/>
-        <v>0.82955511268720139</v>
+        <v>0.82956243955335429</v>
       </c>
       <c r="AG37" s="5">
         <v>455096</v>
@@ -6893,14 +6893,14 @@
       </c>
       <c r="AI37" s="11">
         <f t="shared" si="12"/>
-        <v>253288</v>
+        <v>253291</v>
       </c>
       <c r="AJ37" s="6">
-        <v>341040</v>
+        <v>341043</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="13"/>
-        <v>0.74938035051945084</v>
+        <v>0.74938694253520133</v>
       </c>
       <c r="AL37" s="5">
         <v>455153</v>
@@ -6910,14 +6910,14 @@
       </c>
       <c r="AN37" s="11">
         <f t="shared" si="14"/>
-        <v>230810</v>
+        <v>230814</v>
       </c>
       <c r="AO37" s="6">
-        <v>342550</v>
+        <v>342554</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="15"/>
-        <v>0.75260406940083879</v>
+        <v>0.75261285765445907</v>
       </c>
       <c r="AQ37" s="5">
         <v>700400</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="AS37" s="11">
         <f t="shared" si="16"/>
-        <v>433734</v>
+        <v>433741</v>
       </c>
       <c r="AT37" s="6">
-        <v>584979</v>
+        <v>584986</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="17"/>
-        <v>0.83520702455739582</v>
+        <v>0.83521701884637345</v>
       </c>
       <c r="AV37" s="5">
         <v>439004</v>
@@ -6944,14 +6944,14 @@
       </c>
       <c r="AX37" s="11">
         <f t="shared" si="18"/>
-        <v>227674</v>
+        <v>227679</v>
       </c>
       <c r="AY37" s="6">
-        <v>349504</v>
+        <v>349509</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="19"/>
-        <v>0.79612942023307309</v>
+        <v>0.79614080965093714</v>
       </c>
       <c r="BA37" s="5">
         <v>433985</v>
@@ -6961,14 +6961,14 @@
       </c>
       <c r="BC37" s="11">
         <f t="shared" si="20"/>
-        <v>235054</v>
+        <v>235056</v>
       </c>
       <c r="BD37" s="6">
-        <v>351508</v>
+        <v>351510</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="21"/>
-        <v>0.80995426109197322</v>
+        <v>0.80995886954618246</v>
       </c>
       <c r="BF37" s="5">
         <v>706472</v>
@@ -6978,14 +6978,14 @@
       </c>
       <c r="BH37" s="11">
         <f t="shared" si="22"/>
-        <v>460586</v>
+        <v>460594</v>
       </c>
       <c r="BI37" s="6">
-        <v>599318</v>
+        <v>599326</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="23"/>
-        <v>0.84832519901708769</v>
+        <v>0.84833652289121153</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7037,14 +7037,14 @@
       </c>
       <c r="O38" s="11">
         <f t="shared" si="4"/>
-        <v>7700</v>
+        <v>7701</v>
       </c>
       <c r="P38" s="6">
-        <v>25931</v>
+        <v>25932</v>
       </c>
       <c r="Q38" s="12">
         <f t="shared" si="5"/>
-        <v>0.88362979622435767</v>
+        <v>0.88366387241872824</v>
       </c>
       <c r="R38" s="5">
         <v>16933</v>
@@ -7088,14 +7088,14 @@
       </c>
       <c r="AD38" s="11">
         <f t="shared" si="10"/>
-        <v>12648</v>
+        <v>12649</v>
       </c>
       <c r="AE38" s="6">
-        <v>26840</v>
+        <v>26841</v>
       </c>
       <c r="AF38" s="12">
         <f t="shared" si="11"/>
-        <v>0.8778126635269492</v>
+        <v>0.87784536891679754</v>
       </c>
       <c r="AG38" s="5">
         <v>16399</v>
@@ -7427,14 +7427,14 @@
       </c>
       <c r="E40" s="11">
         <f t="shared" si="0"/>
-        <v>26501</v>
+        <v>26503</v>
       </c>
       <c r="F40" s="6">
-        <v>135020</v>
+        <v>135022</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="1"/>
-        <v>0.82122959394691386</v>
+        <v>0.8212417585091113</v>
       </c>
       <c r="H40" s="5">
         <v>169073</v>
@@ -7444,14 +7444,14 @@
       </c>
       <c r="J40" s="11">
         <f t="shared" si="2"/>
-        <v>29026</v>
+        <v>29027</v>
       </c>
       <c r="K40" s="6">
-        <v>136943</v>
+        <v>136944</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="3"/>
-        <v>0.80996374347175482</v>
+        <v>0.80996965807668875</v>
       </c>
       <c r="M40" s="5">
         <v>263762</v>
@@ -7461,14 +7461,14 @@
       </c>
       <c r="O40" s="11">
         <f t="shared" si="4"/>
-        <v>67953</v>
+        <v>67954</v>
       </c>
       <c r="P40" s="6">
-        <v>241230</v>
+        <v>241231</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>0.91457450277143792</v>
+        <v>0.91457829406813718</v>
       </c>
       <c r="R40" s="5">
         <v>173127</v>
@@ -7512,14 +7512,14 @@
       </c>
       <c r="AD40" s="11">
         <f t="shared" si="10"/>
-        <v>145548</v>
+        <v>145550</v>
       </c>
       <c r="AE40" s="6">
-        <v>249069</v>
+        <v>249071</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="11"/>
-        <v>0.91173617491699643</v>
+        <v>0.91174349607037097</v>
       </c>
       <c r="AG40" s="5">
         <v>172895</v>
@@ -7563,14 +7563,14 @@
       </c>
       <c r="AS40" s="11">
         <f t="shared" si="16"/>
-        <v>206376</v>
+        <v>206377</v>
       </c>
       <c r="AT40" s="6">
-        <v>255763</v>
+        <v>255764</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="17"/>
-        <v>0.90725375919179596</v>
+        <v>0.90725730643576474</v>
       </c>
       <c r="AV40" s="5">
         <v>172382</v>
@@ -7614,14 +7614,14 @@
       </c>
       <c r="BH40" s="11">
         <f t="shared" si="22"/>
-        <v>208596</v>
+        <v>208597</v>
       </c>
       <c r="BI40" s="6">
-        <v>260558</v>
+        <v>260559</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="23"/>
-        <v>0.89479178829234118</v>
+        <v>0.89479522242903353</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7639,14 +7639,14 @@
       </c>
       <c r="E41" s="11">
         <f t="shared" si="0"/>
-        <v>77307</v>
+        <v>77320</v>
       </c>
       <c r="F41" s="6">
-        <v>452059</v>
+        <v>452072</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="1"/>
-        <v>0.73708196031690387</v>
+        <v>0.73710315681002558</v>
       </c>
       <c r="H41" s="5">
         <v>630477</v>
@@ -7656,14 +7656,14 @@
       </c>
       <c r="J41" s="11">
         <f t="shared" si="2"/>
-        <v>82452</v>
+        <v>82461</v>
       </c>
       <c r="K41" s="6">
-        <v>458521</v>
+        <v>458530</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="3"/>
-        <v>0.72726047104018066</v>
+        <v>0.72727474594632313</v>
       </c>
       <c r="M41" s="5">
         <v>852643</v>
@@ -7673,14 +7673,14 @@
       </c>
       <c r="O41" s="11">
         <f t="shared" si="4"/>
-        <v>165674</v>
+        <v>165693</v>
       </c>
       <c r="P41" s="6">
-        <v>685192</v>
+        <v>685211</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>0.80360948251495645</v>
+        <v>0.80363176616708287</v>
       </c>
       <c r="R41" s="5">
         <v>651946</v>
@@ -7690,14 +7690,14 @@
       </c>
       <c r="T41" s="11">
         <f t="shared" si="6"/>
-        <v>104714</v>
+        <v>104722</v>
       </c>
       <c r="U41" s="6">
-        <v>468836</v>
+        <v>468844</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="7"/>
-        <v>0.71913317974188051</v>
+        <v>0.71914545069683689</v>
       </c>
       <c r="W41" s="5">
         <v>654087</v>
@@ -7707,14 +7707,14 @@
       </c>
       <c r="Y41" s="11">
         <f t="shared" si="8"/>
-        <v>129248</v>
+        <v>129260</v>
       </c>
       <c r="Z41" s="6">
-        <v>472875</v>
+        <v>472887</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="9"/>
-        <v>0.72295428589774757</v>
+        <v>0.72297263208105345</v>
       </c>
       <c r="AB41" s="5">
         <v>882248</v>
@@ -7724,14 +7724,14 @@
       </c>
       <c r="AD41" s="11">
         <f t="shared" si="10"/>
-        <v>296867</v>
+        <v>296884</v>
       </c>
       <c r="AE41" s="6">
-        <v>708715</v>
+        <v>708732</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="11"/>
-        <v>0.80330587317851665</v>
+        <v>0.80332514213690487</v>
       </c>
       <c r="AG41" s="5">
         <v>638043</v>
@@ -7741,14 +7741,14 @@
       </c>
       <c r="AI41" s="11">
         <f t="shared" si="12"/>
-        <v>359863</v>
+        <v>359876</v>
       </c>
       <c r="AJ41" s="6">
-        <v>481390</v>
+        <v>481403</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="13"/>
-        <v>0.75447893010345701</v>
+        <v>0.75449930490578221</v>
       </c>
       <c r="AL41" s="5">
         <v>632207</v>
@@ -7758,14 +7758,14 @@
       </c>
       <c r="AN41" s="11">
         <f t="shared" si="14"/>
-        <v>319909</v>
+        <v>319926</v>
       </c>
       <c r="AO41" s="6">
-        <v>483014</v>
+        <v>483031</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="15"/>
-        <v>0.76401241998269553</v>
+        <v>0.76403930990957081</v>
       </c>
       <c r="AQ41" s="5">
         <v>865402</v>
@@ -7775,14 +7775,14 @@
       </c>
       <c r="AS41" s="11">
         <f t="shared" si="16"/>
-        <v>516817</v>
+        <v>516839</v>
       </c>
       <c r="AT41" s="6">
-        <v>724190</v>
+        <v>724212</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="17"/>
-        <v>0.83682496689399843</v>
+        <v>0.83685038860552663</v>
       </c>
       <c r="AV41" s="5">
         <v>609881</v>
@@ -7792,14 +7792,14 @@
       </c>
       <c r="AX41" s="11">
         <f t="shared" si="18"/>
-        <v>321754</v>
+        <v>321771</v>
       </c>
       <c r="AY41" s="6">
-        <v>489949</v>
+        <v>489966</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="19"/>
-        <v>0.80335180141699769</v>
+        <v>0.80337967570722812</v>
       </c>
       <c r="BA41" s="5">
         <v>594974</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="20"/>
-        <v>336313</v>
+        <v>336331</v>
       </c>
       <c r="BD41" s="6">
-        <v>492322</v>
+        <v>492340</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="21"/>
-        <v>0.82746809104263375</v>
+        <v>0.82749834446547244</v>
       </c>
       <c r="BF41" s="5">
         <v>867754</v>
@@ -7826,14 +7826,14 @@
       </c>
       <c r="BH41" s="11">
         <f t="shared" si="22"/>
-        <v>556540</v>
+        <v>556565</v>
       </c>
       <c r="BI41" s="6">
-        <v>737652</v>
+        <v>737677</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="23"/>
-        <v>0.8500704116604475</v>
+        <v>0.85009922166881402</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7885,14 +7885,14 @@
       </c>
       <c r="O42" s="11">
         <f t="shared" si="4"/>
-        <v>4464</v>
+        <v>4466</v>
       </c>
       <c r="P42" s="6">
-        <v>15935</v>
+        <v>15937</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="5"/>
-        <v>0.80793996856462003</v>
+        <v>0.80804137301627543</v>
       </c>
       <c r="R42" s="5">
         <v>14633</v>
@@ -7936,14 +7936,14 @@
       </c>
       <c r="AD42" s="11">
         <f t="shared" si="10"/>
-        <v>7505</v>
+        <v>7507</v>
       </c>
       <c r="AE42" s="6">
-        <v>16417</v>
+        <v>16419</v>
       </c>
       <c r="AF42" s="12">
         <f t="shared" si="11"/>
-        <v>0.81103645884793996</v>
+        <v>0.81113526331390173</v>
       </c>
       <c r="AG42" s="5">
         <v>14593</v>
@@ -7987,14 +7987,14 @@
       </c>
       <c r="AS42" s="11">
         <f t="shared" si="16"/>
-        <v>12257</v>
+        <v>12259</v>
       </c>
       <c r="AT42" s="6">
-        <v>16647</v>
+        <v>16649</v>
       </c>
       <c r="AU42" s="12">
         <f t="shared" si="17"/>
-        <v>0.81411384976525825</v>
+        <v>0.81421165884194058</v>
       </c>
       <c r="AV42" s="5">
         <v>14203</v>
@@ -8038,14 +8038,14 @@
       </c>
       <c r="BH42" s="11">
         <f t="shared" si="22"/>
-        <v>12529</v>
+        <v>12531</v>
       </c>
       <c r="BI42" s="6">
-        <v>16741</v>
+        <v>16743</v>
       </c>
       <c r="BJ42" s="12">
         <f t="shared" si="23"/>
-        <v>0.80334948893900859</v>
+        <v>0.80344546283410911</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8394,14 +8394,14 @@
       </c>
       <c r="AN44" s="11">
         <f t="shared" si="14"/>
-        <v>115547</v>
+        <v>115548</v>
       </c>
       <c r="AO44" s="6">
-        <v>158899</v>
+        <v>158900</v>
       </c>
       <c r="AP44" s="12">
         <f t="shared" si="15"/>
-        <v>0.75160823415889355</v>
+        <v>0.75161296425936086</v>
       </c>
       <c r="AQ44" s="5">
         <v>305678</v>
@@ -8411,14 +8411,14 @@
       </c>
       <c r="AS44" s="11">
         <f t="shared" si="16"/>
-        <v>186778</v>
+        <v>186779</v>
       </c>
       <c r="AT44" s="6">
-        <v>252328</v>
+        <v>252329</v>
       </c>
       <c r="AU44" s="12">
         <f t="shared" si="17"/>
-        <v>0.82546993895537135</v>
+        <v>0.8254732103716983</v>
       </c>
       <c r="AV44" s="5">
         <v>207845</v>
@@ -8428,14 +8428,14 @@
       </c>
       <c r="AX44" s="11">
         <f t="shared" si="18"/>
-        <v>111102</v>
+        <v>111103</v>
       </c>
       <c r="AY44" s="6">
-        <v>161565</v>
+        <v>161566</v>
       </c>
       <c r="AZ44" s="12">
         <f t="shared" si="19"/>
-        <v>0.77733407106257069</v>
+        <v>0.77733888234020543</v>
       </c>
       <c r="BA44" s="5">
         <v>209739</v>
@@ -8521,14 +8521,14 @@
       </c>
       <c r="O45" s="11">
         <f t="shared" si="4"/>
-        <v>53663</v>
+        <v>53664</v>
       </c>
       <c r="P45" s="6">
-        <v>209802</v>
+        <v>209803</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="5"/>
-        <v>0.8306489927784112</v>
+        <v>0.83065295198276956</v>
       </c>
       <c r="R45" s="5">
         <v>182214</v>
@@ -8572,14 +8572,14 @@
       </c>
       <c r="AD45" s="11">
         <f t="shared" si="10"/>
-        <v>108357</v>
+        <v>108358</v>
       </c>
       <c r="AE45" s="6">
-        <v>218423</v>
+        <v>218424</v>
       </c>
       <c r="AF45" s="12">
         <f t="shared" si="11"/>
-        <v>0.84993462729777269</v>
+        <v>0.84993851853004809</v>
       </c>
       <c r="AG45" s="5">
         <v>177277</v>
@@ -8674,14 +8674,14 @@
       </c>
       <c r="BH45" s="11">
         <f t="shared" si="22"/>
-        <v>189804</v>
+        <v>189805</v>
       </c>
       <c r="BI45" s="6">
-        <v>233082</v>
+        <v>233083</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="23"/>
-        <v>0.83515294404293972</v>
+        <v>0.83515652712933863</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9099,15 +9099,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" si="0"/>
-        <v>546873</v>
+        <v>546900</v>
       </c>
       <c r="F48" s="15">
         <f>SUM(F10:F47)</f>
-        <v>3051576</v>
+        <v>3051603</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" si="1"/>
-        <v>0.67868361565334823</v>
+        <v>0.67868962056937276</v>
       </c>
       <c r="H48" s="15">
         <f>SUM(H10:H47)</f>
@@ -9119,15 +9119,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" si="2"/>
-        <v>589275</v>
+        <v>589298</v>
       </c>
       <c r="K48" s="15">
         <f>SUM(K10:K47)</f>
-        <v>3089592</v>
+        <v>3089615</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" si="3"/>
-        <v>0.65983860651019943</v>
+        <v>0.65984351857883172</v>
       </c>
       <c r="M48" s="15">
         <f>SUM(M10:M47)</f>
@@ -9139,15 +9139,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2192283</v>
+        <v>2192326</v>
       </c>
       <c r="P48" s="15">
         <f>SUM(P10:P47)</f>
-        <v>8044934</v>
+        <v>8044977</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.86349516084540567</v>
+        <v>0.86349977620855434</v>
       </c>
       <c r="R48" s="15">
         <f>SUM(R10:R47)</f>
@@ -9159,15 +9159,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>772906</v>
+        <v>772920</v>
       </c>
       <c r="U48" s="15">
         <f>SUM(U10:U47)</f>
-        <v>3153546</v>
+        <v>3153560</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.6603419111965636</v>
+        <v>0.6603448427494113</v>
       </c>
       <c r="W48" s="15">
         <f>SUM(W10:W47)</f>
@@ -9179,15 +9179,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" si="8"/>
-        <v>978248</v>
+        <v>978269</v>
       </c>
       <c r="Z48" s="15">
         <f>SUM(Z10:Z47)</f>
-        <v>3178201</v>
+        <v>3178222</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" si="9"/>
-        <v>0.67236604355801732</v>
+        <v>0.67237048622445494</v>
       </c>
       <c r="AB48" s="15">
         <f>SUM(AB10:AB47)</f>
@@ -9199,15 +9199,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>3987982</v>
+        <v>3988029</v>
       </c>
       <c r="AE48" s="15">
         <f>SUM(AE10:AE47)</f>
-        <v>8342162</v>
+        <v>8342209</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.8638247432832511</v>
+        <v>0.86382961009870418</v>
       </c>
       <c r="AG48" s="15">
         <f>SUM(AG10:AG47)</f>
@@ -9219,15 +9219,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>2361833</v>
+        <v>2361856</v>
       </c>
       <c r="AJ48" s="15">
         <f>SUM(AJ10:AJ47)</f>
-        <v>3233175</v>
+        <v>3233198</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.70142407630942039</v>
+        <v>0.70142906606523481</v>
       </c>
       <c r="AL48" s="15">
         <f>SUM(AL10:AL47)</f>
@@ -9239,15 +9239,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>2046791</v>
+        <v>2046823</v>
       </c>
       <c r="AO48" s="15">
         <f>SUM(AO10:AO47)</f>
-        <v>3245101</v>
+        <v>3245133</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.70975880325048479</v>
+        <v>0.70976580219495644</v>
       </c>
       <c r="AQ48" s="15">
         <f>SUM(AQ10:AQ47)</f>
@@ -9259,15 +9259,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>6759956</v>
+        <v>6760011</v>
       </c>
       <c r="AT48" s="15">
         <f>SUM(AT10:AT47)</f>
-        <v>8562889</v>
+        <v>8562944</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.86476384511124371</v>
+        <v>0.86476939954637433</v>
       </c>
       <c r="AV48" s="15">
         <f>SUM(AV10:AV47)</f>
@@ -9279,15 +9279,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>2013199</v>
+        <v>2013228</v>
       </c>
       <c r="AY48" s="15">
         <f>SUM(AY10:AY47)</f>
-        <v>3290736</v>
+        <v>3290765</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.74411326624545859</v>
+        <v>0.74411982383157949</v>
       </c>
       <c r="BA48" s="15">
         <f>SUM(BA10:BA47)</f>
@@ -9299,15 +9299,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>2072223</v>
+        <v>2072250</v>
       </c>
       <c r="BD48" s="15">
         <f>SUM(BD10:BD47)</f>
-        <v>3302220</v>
+        <v>3302247</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.75710443126490834</v>
+        <v>0.75711062159130826</v>
       </c>
       <c r="BF48" s="15">
         <f>SUM(BF10:BF47)</f>
@@ -9319,15 +9319,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>7183607</v>
+        <v>7183672</v>
       </c>
       <c r="BI48" s="15">
         <f>SUM(BI10:BI47)</f>
-        <v>8731077</v>
+        <v>8731142</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.85809296098723753</v>
+        <v>0.85809934920743813</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">

--- a/gstdatabase/GSTR-1-2018-2019.xlsx
+++ b/gstdatabase/GSTR-1-2018-2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA037FF-BAFB-4934-9FE7-E72588326D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85820234-A21C-4390-8FAC-FEBF03B04F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -684,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ103"/>
+  <dimension ref="A1:BJ101"/>
   <sheetFormatPr defaultColWidth="12.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.44140625" bestFit="1" customWidth="1"/>
@@ -1169,14 +1169,14 @@
       </c>
       <c r="AI10" s="11">
         <f>AJ10-AH10</f>
-        <v>19241</v>
+        <v>19242</v>
       </c>
       <c r="AJ10" s="6">
-        <v>25880</v>
+        <v>25881</v>
       </c>
       <c r="AK10" s="12">
         <f>AJ10/AG10</f>
-        <v>0.65698619008935821</v>
+        <v>0.65701157595450854</v>
       </c>
       <c r="AL10" s="5">
         <v>39302</v>
@@ -1203,14 +1203,14 @@
       </c>
       <c r="AS10" s="11">
         <f>AT10-AR10</f>
-        <v>57144</v>
+        <v>57145</v>
       </c>
       <c r="AT10" s="6">
-        <v>70787</v>
+        <v>70788</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/AQ10</f>
-        <v>0.83581684220469465</v>
+        <v>0.83582864969536674</v>
       </c>
       <c r="AV10" s="5">
         <v>38866</v>
@@ -1254,14 +1254,14 @@
       </c>
       <c r="BH10" s="11">
         <f>BI10-BG10</f>
-        <v>60957</v>
+        <v>60958</v>
       </c>
       <c r="BI10" s="6">
-        <v>72079</v>
+        <v>72080</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/BF10</f>
-        <v>0.81098809604176514</v>
+        <v>0.81099934742005897</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="E12" s="11">
         <f t="shared" si="0"/>
-        <v>4908</v>
+        <v>4909</v>
       </c>
       <c r="F12" s="6">
-        <v>75145</v>
+        <v>75146</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" si="1"/>
-        <v>0.75648821148851353</v>
+        <v>0.75649827853504337</v>
       </c>
       <c r="H12" s="5">
         <v>103832</v>
@@ -1915,14 +1915,14 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" si="0"/>
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="F14" s="6">
-        <v>28301</v>
+        <v>28302</v>
       </c>
       <c r="G14" s="12">
         <f t="shared" si="1"/>
-        <v>0.54050802139037435</v>
+        <v>0.54052711993888469</v>
       </c>
       <c r="H14" s="5">
         <v>53901</v>
@@ -1949,14 +1949,14 @@
       </c>
       <c r="O14" s="11">
         <f t="shared" si="4"/>
-        <v>35305</v>
+        <v>35306</v>
       </c>
       <c r="P14" s="6">
-        <v>98341</v>
+        <v>98342</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="5"/>
-        <v>0.82774439001397238</v>
+        <v>0.8277528070972846</v>
       </c>
       <c r="R14" s="5">
         <v>54910</v>
@@ -2000,14 +2000,14 @@
       </c>
       <c r="AD14" s="11">
         <f t="shared" si="10"/>
-        <v>55164</v>
+        <v>55166</v>
       </c>
       <c r="AE14" s="6">
-        <v>102364</v>
+        <v>102366</v>
       </c>
       <c r="AF14" s="12">
         <f t="shared" si="11"/>
-        <v>0.83578141202021605</v>
+        <v>0.83579774161679332</v>
       </c>
       <c r="AG14" s="5">
         <v>49944</v>
@@ -2051,14 +2051,14 @@
       </c>
       <c r="AS14" s="11">
         <f t="shared" si="16"/>
-        <v>87220</v>
+        <v>87221</v>
       </c>
       <c r="AT14" s="6">
-        <v>105110</v>
+        <v>105111</v>
       </c>
       <c r="AU14" s="12">
         <f t="shared" si="17"/>
-        <v>0.85000566077407047</v>
+        <v>0.85001374759417103</v>
       </c>
       <c r="AV14" s="5">
         <v>44859</v>
@@ -2068,14 +2068,14 @@
       </c>
       <c r="AX14" s="11">
         <f t="shared" si="18"/>
-        <v>19903</v>
+        <v>19904</v>
       </c>
       <c r="AY14" s="6">
-        <v>30196</v>
+        <v>30197</v>
       </c>
       <c r="AZ14" s="12">
         <f t="shared" si="19"/>
-        <v>0.67313136717269673</v>
+        <v>0.67315365924340709</v>
       </c>
       <c r="BA14" s="5">
         <v>44209</v>
@@ -2102,14 +2102,14 @@
       </c>
       <c r="BH14" s="11">
         <f t="shared" si="22"/>
-        <v>92377</v>
+        <v>92378</v>
       </c>
       <c r="BI14" s="6">
-        <v>108328</v>
+        <v>108329</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="23"/>
-        <v>0.84446523230433423</v>
+        <v>0.844473027751793</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="O15" s="11">
         <f t="shared" si="4"/>
-        <v>75272</v>
+        <v>75273</v>
       </c>
       <c r="P15" s="6">
-        <v>338519</v>
+        <v>338520</v>
       </c>
       <c r="Q15" s="12">
         <f t="shared" si="5"/>
-        <v>0.88633781059356431</v>
+        <v>0.88634042887440112</v>
       </c>
       <c r="R15" s="5">
         <v>166252</v>
@@ -2212,14 +2212,14 @@
       </c>
       <c r="AD15" s="11">
         <f t="shared" si="10"/>
-        <v>156789</v>
+        <v>156790</v>
       </c>
       <c r="AE15" s="6">
-        <v>351558</v>
+        <v>351559</v>
       </c>
       <c r="AF15" s="12">
         <f t="shared" si="11"/>
-        <v>0.88091449648318776</v>
+        <v>0.88091700222760683</v>
       </c>
       <c r="AG15" s="5">
         <v>161513</v>
@@ -2526,14 +2526,14 @@
       </c>
       <c r="BH16" s="11">
         <f t="shared" si="22"/>
-        <v>501856</v>
+        <v>501857</v>
       </c>
       <c r="BI16" s="6">
-        <v>605898</v>
+        <v>605899</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="23"/>
-        <v>0.829583604887426</v>
+        <v>0.82958497406772513</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2585,14 +2585,14 @@
       </c>
       <c r="O17" s="11">
         <f t="shared" si="4"/>
-        <v>111628</v>
+        <v>111631</v>
       </c>
       <c r="P17" s="6">
-        <v>448817</v>
+        <v>448820</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="5"/>
-        <v>0.89688599707843664</v>
+        <v>0.89689199207860648</v>
       </c>
       <c r="R17" s="5">
         <v>195360</v>
@@ -2602,14 +2602,14 @@
       </c>
       <c r="T17" s="11">
         <f t="shared" si="6"/>
-        <v>20975</v>
+        <v>20976</v>
       </c>
       <c r="U17" s="6">
-        <v>114635</v>
+        <v>114636</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="7"/>
-        <v>0.58678849303849301</v>
+        <v>0.58679361179361178</v>
       </c>
       <c r="W17" s="5">
         <v>193037</v>
@@ -2636,14 +2636,14 @@
       </c>
       <c r="AD17" s="11">
         <f t="shared" si="10"/>
-        <v>217806</v>
+        <v>217807</v>
       </c>
       <c r="AE17" s="6">
-        <v>464514</v>
+        <v>464515</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="11"/>
-        <v>0.90825440524327583</v>
+        <v>0.90825636052213765</v>
       </c>
       <c r="AG17" s="5">
         <v>180725</v>
@@ -2687,14 +2687,14 @@
       </c>
       <c r="AS17" s="11">
         <f t="shared" si="16"/>
-        <v>374714</v>
+        <v>374716</v>
       </c>
       <c r="AT17" s="6">
-        <v>475240</v>
+        <v>475242</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="17"/>
-        <v>0.89567541283919527</v>
+        <v>0.89567918219957254</v>
       </c>
       <c r="AV17" s="5">
         <v>171569</v>
@@ -2721,14 +2721,14 @@
       </c>
       <c r="BC17" s="11">
         <f t="shared" si="20"/>
-        <v>57285</v>
+        <v>57286</v>
       </c>
       <c r="BD17" s="6">
-        <v>117357</v>
+        <v>117358</v>
       </c>
       <c r="BE17" s="12">
         <f t="shared" si="21"/>
-        <v>0.69584887313003618</v>
+        <v>0.69585480246423126</v>
       </c>
       <c r="BF17" s="5">
         <v>551432</v>
@@ -2738,14 +2738,14 @@
       </c>
       <c r="BH17" s="11">
         <f t="shared" si="22"/>
-        <v>407039</v>
+        <v>407042</v>
       </c>
       <c r="BI17" s="6">
-        <v>486579</v>
+        <v>486582</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="23"/>
-        <v>0.88239166388602763</v>
+        <v>0.88239710426670925</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2797,14 +2797,14 @@
       </c>
       <c r="O18" s="11">
         <f t="shared" si="4"/>
-        <v>254410</v>
+        <v>254413</v>
       </c>
       <c r="P18" s="6">
-        <v>869032</v>
+        <v>869035</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="5"/>
-        <v>0.86347124518103413</v>
+        <v>0.86347422598465884</v>
       </c>
       <c r="R18" s="5">
         <v>418258</v>
@@ -2831,14 +2831,14 @@
       </c>
       <c r="Y18" s="11">
         <f t="shared" si="8"/>
-        <v>80971</v>
+        <v>80972</v>
       </c>
       <c r="Z18" s="6">
-        <v>269024</v>
+        <v>269025</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="9"/>
-        <v>0.64956068021527757</v>
+        <v>0.64956309472357499</v>
       </c>
       <c r="AB18" s="5">
         <v>1050898</v>
@@ -2848,14 +2848,14 @@
       </c>
       <c r="AD18" s="11">
         <f t="shared" si="10"/>
-        <v>436539</v>
+        <v>436543</v>
       </c>
       <c r="AE18" s="6">
-        <v>905334</v>
+        <v>905338</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="11"/>
-        <v>0.86148608142750294</v>
+        <v>0.86148988769604662</v>
       </c>
       <c r="AG18" s="5">
         <v>403018</v>
@@ -2899,14 +2899,14 @@
       </c>
       <c r="AS18" s="11">
         <f t="shared" si="16"/>
-        <v>781416</v>
+        <v>781421</v>
       </c>
       <c r="AT18" s="6">
-        <v>931162</v>
+        <v>931167</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="17"/>
-        <v>0.86140937579499988</v>
+        <v>0.86141400124887257</v>
       </c>
       <c r="AV18" s="5">
         <v>383854</v>
@@ -2950,14 +2950,14 @@
       </c>
       <c r="BH18" s="11">
         <f t="shared" si="22"/>
-        <v>810031</v>
+        <v>810037</v>
       </c>
       <c r="BI18" s="6">
-        <v>946544</v>
+        <v>946550</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="23"/>
-        <v>0.85394401851975488</v>
+        <v>0.85394943154240477</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3162,14 +3162,14 @@
       </c>
       <c r="BH19" s="11">
         <f t="shared" si="22"/>
-        <v>219834</v>
+        <v>219835</v>
       </c>
       <c r="BI19" s="6">
-        <v>245315</v>
+        <v>245316</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="23"/>
-        <v>0.80628091567928217</v>
+        <v>0.8062842023960165</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3399,14 +3399,14 @@
       </c>
       <c r="E21" s="11">
         <f t="shared" si="0"/>
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="F21" s="6">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="G21" s="12">
         <f t="shared" si="1"/>
-        <v>0.46148814390842191</v>
+        <v>0.46165167620605069</v>
       </c>
       <c r="H21" s="5">
         <v>6221</v>
@@ -3416,14 +3416,14 @@
       </c>
       <c r="J21" s="11">
         <f t="shared" si="2"/>
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="K21" s="6">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="L21" s="12">
         <f t="shared" si="3"/>
-        <v>0.46439479183411025</v>
+        <v>0.46455553769490437</v>
       </c>
       <c r="M21" s="5">
         <v>9000</v>
@@ -3433,14 +3433,14 @@
       </c>
       <c r="O21" s="11">
         <f t="shared" si="4"/>
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="P21" s="6">
-        <v>6710</v>
+        <v>6711</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="5"/>
-        <v>0.74555555555555553</v>
+        <v>0.7456666666666667</v>
       </c>
       <c r="R21" s="5">
         <v>6296</v>
@@ -3450,14 +3450,14 @@
       </c>
       <c r="T21" s="11">
         <f t="shared" si="6"/>
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="U21" s="6">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="7"/>
-        <v>0.46998094027954257</v>
+        <v>0.47013977128335449</v>
       </c>
       <c r="W21" s="5">
         <v>6159</v>
@@ -3467,14 +3467,14 @@
       </c>
       <c r="Y21" s="11">
         <f t="shared" si="8"/>
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="Z21" s="6">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="AA21" s="12">
         <f t="shared" si="9"/>
-        <v>0.48611787627861663</v>
+        <v>0.48628024029874978</v>
       </c>
       <c r="AB21" s="5">
         <v>9574</v>
@@ -3484,14 +3484,14 @@
       </c>
       <c r="AD21" s="11">
         <f t="shared" si="10"/>
-        <v>4947</v>
+        <v>4948</v>
       </c>
       <c r="AE21" s="6">
-        <v>7056</v>
+        <v>7057</v>
       </c>
       <c r="AF21" s="12">
         <f t="shared" si="11"/>
-        <v>0.736996030917067</v>
+        <v>0.73710048046793397</v>
       </c>
       <c r="AG21" s="5">
         <v>6075</v>
@@ -3501,14 +3501,14 @@
       </c>
       <c r="AI21" s="11">
         <f t="shared" si="12"/>
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="AJ21" s="6">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="AK21" s="12">
         <f t="shared" si="13"/>
-        <v>0.50748971193415637</v>
+        <v>0.50765432098765428</v>
       </c>
       <c r="AL21" s="5">
         <v>6088</v>
@@ -3518,14 +3518,14 @@
       </c>
       <c r="AN21" s="11">
         <f t="shared" si="14"/>
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="AO21" s="6">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="AP21" s="12">
         <f t="shared" si="15"/>
-        <v>0.51018396846254932</v>
+        <v>0.5103482260183968</v>
       </c>
       <c r="AQ21" s="5">
         <v>10144</v>
@@ -3535,14 +3535,14 @@
       </c>
       <c r="AS21" s="11">
         <f t="shared" si="16"/>
-        <v>6454</v>
+        <v>6455</v>
       </c>
       <c r="AT21" s="6">
-        <v>7248</v>
+        <v>7249</v>
       </c>
       <c r="AU21" s="12">
         <f t="shared" si="17"/>
-        <v>0.71451104100946372</v>
+        <v>0.71460962145110407</v>
       </c>
       <c r="AV21" s="5">
         <v>6030</v>
@@ -3552,14 +3552,14 @@
       </c>
       <c r="AX21" s="11">
         <f t="shared" si="18"/>
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="AY21" s="6">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="AZ21" s="12">
         <f t="shared" si="19"/>
-        <v>0.52819237147595355</v>
+        <v>0.5283582089552239</v>
       </c>
       <c r="BA21" s="5">
         <v>6065</v>
@@ -3569,14 +3569,14 @@
       </c>
       <c r="BC21" s="11">
         <f t="shared" si="20"/>
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="BD21" s="6">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="BE21" s="12">
         <f t="shared" si="21"/>
-        <v>0.52613355317394894</v>
+        <v>0.52629843363561413</v>
       </c>
       <c r="BF21" s="5">
         <v>10737</v>
@@ -3586,14 +3586,14 @@
       </c>
       <c r="BH21" s="11">
         <f t="shared" si="22"/>
-        <v>6852</v>
+        <v>6853</v>
       </c>
       <c r="BI21" s="6">
-        <v>7509</v>
+        <v>7510</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="23"/>
-        <v>0.69935736239172952</v>
+        <v>0.69945049827698613</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="E22" s="11">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F22" s="6">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="G22" s="12">
         <f t="shared" si="1"/>
-        <v>0.60133683456672238</v>
+        <v>0.60157555502506566</v>
       </c>
       <c r="H22" s="5">
         <v>4295</v>
@@ -3959,14 +3959,14 @@
       </c>
       <c r="AS23" s="11">
         <f t="shared" si="16"/>
-        <v>5865</v>
+        <v>5866</v>
       </c>
       <c r="AT23" s="6">
-        <v>6624</v>
+        <v>6625</v>
       </c>
       <c r="AU23" s="12">
         <f t="shared" si="17"/>
-        <v>0.63784304285026483</v>
+        <v>0.63793933558016369</v>
       </c>
       <c r="AV23" s="5">
         <v>7292</v>
@@ -4010,14 +4010,14 @@
       </c>
       <c r="BH23" s="11">
         <f t="shared" si="22"/>
-        <v>5928</v>
+        <v>5929</v>
       </c>
       <c r="BI23" s="6">
-        <v>6715</v>
+        <v>6716</v>
       </c>
       <c r="BJ23" s="12">
         <f t="shared" si="23"/>
-        <v>0.61442034952877667</v>
+        <v>0.61451184920852775</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4035,14 +4035,14 @@
       </c>
       <c r="E24" s="11">
         <f t="shared" si="0"/>
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F24" s="6">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="G24" s="12">
         <f t="shared" si="1"/>
-        <v>0.61141858432857554</v>
+        <v>0.61200116516166614</v>
       </c>
       <c r="H24" s="5">
         <v>3586</v>
@@ -4052,14 +4052,14 @@
       </c>
       <c r="J24" s="11">
         <f t="shared" si="2"/>
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K24" s="6">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="3"/>
-        <v>0.6006692693809258</v>
+        <v>0.60094813162297822</v>
       </c>
       <c r="M24" s="5">
         <v>4577</v>
@@ -4069,14 +4069,14 @@
       </c>
       <c r="O24" s="11">
         <f t="shared" si="4"/>
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="P24" s="6">
-        <v>3285</v>
+        <v>3287</v>
       </c>
       <c r="Q24" s="12">
         <f t="shared" si="5"/>
-        <v>0.71771902993226999</v>
+        <v>0.71815599737819535</v>
       </c>
       <c r="R24" s="5">
         <v>3714</v>
@@ -4086,14 +4086,14 @@
       </c>
       <c r="T24" s="11">
         <f t="shared" si="6"/>
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="U24" s="6">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="7"/>
-        <v>0.60150780829294559</v>
+        <v>0.60204631125471186</v>
       </c>
       <c r="W24" s="5">
         <v>3697</v>
@@ -4103,14 +4103,14 @@
       </c>
       <c r="Y24" s="11">
         <f t="shared" si="8"/>
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="Z24" s="6">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="AA24" s="12">
         <f t="shared" si="9"/>
-        <v>0.60481471463348657</v>
+        <v>0.60535569380578846</v>
       </c>
       <c r="AB24" s="5">
         <v>4810</v>
@@ -4120,14 +4120,14 @@
       </c>
       <c r="AD24" s="11">
         <f t="shared" si="10"/>
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="AE24" s="6">
-        <v>3439</v>
+        <v>3442</v>
       </c>
       <c r="AF24" s="12">
         <f t="shared" si="11"/>
-        <v>0.71496881496881493</v>
+        <v>0.71559251559251558</v>
       </c>
       <c r="AG24" s="5">
         <v>3785</v>
@@ -4137,14 +4137,14 @@
       </c>
       <c r="AI24" s="11">
         <f t="shared" si="12"/>
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="AJ24" s="6">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="AK24" s="12">
         <f t="shared" si="13"/>
-        <v>0.6068692206076618</v>
+        <v>0.60739762219286653</v>
       </c>
       <c r="AL24" s="5">
         <v>3841</v>
@@ -4154,14 +4154,14 @@
       </c>
       <c r="AN24" s="11">
         <f t="shared" si="14"/>
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="AO24" s="6">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="AP24" s="12">
         <f t="shared" si="15"/>
-        <v>0.61129914084873727</v>
+        <v>0.61181983858370215</v>
       </c>
       <c r="AQ24" s="5">
         <v>5062</v>
@@ -4171,14 +4171,14 @@
       </c>
       <c r="AS24" s="11">
         <f t="shared" si="16"/>
-        <v>3158</v>
+        <v>3161</v>
       </c>
       <c r="AT24" s="6">
-        <v>3638</v>
+        <v>3641</v>
       </c>
       <c r="AU24" s="12">
         <f t="shared" si="17"/>
-        <v>0.71868826550770448</v>
+        <v>0.71928091663374161</v>
       </c>
       <c r="AV24" s="5">
         <v>3750</v>
@@ -4188,14 +4188,14 @@
       </c>
       <c r="AX24" s="11">
         <f t="shared" si="18"/>
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="AY24" s="6">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="AZ24" s="12">
         <f t="shared" si="19"/>
-        <v>0.63919999999999999</v>
+        <v>0.63946666666666663</v>
       </c>
       <c r="BA24" s="5">
         <v>3712</v>
@@ -4205,14 +4205,14 @@
       </c>
       <c r="BC24" s="11">
         <f t="shared" si="20"/>
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="BD24" s="6">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="BE24" s="12">
         <f t="shared" si="21"/>
-        <v>0.65517241379310343</v>
+        <v>0.65544181034482762</v>
       </c>
       <c r="BF24" s="5">
         <v>5225</v>
@@ -4222,14 +4222,14 @@
       </c>
       <c r="BH24" s="11">
         <f t="shared" si="22"/>
-        <v>3111</v>
+        <v>3114</v>
       </c>
       <c r="BI24" s="6">
-        <v>3821</v>
+        <v>3824</v>
       </c>
       <c r="BJ24" s="12">
         <f t="shared" si="23"/>
-        <v>0.7312918660287081</v>
+        <v>0.731866028708134</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4459,14 +4459,14 @@
       </c>
       <c r="E26" s="11">
         <f t="shared" si="0"/>
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="F26" s="6">
-        <v>6135</v>
+        <v>6136</v>
       </c>
       <c r="G26" s="12">
         <f t="shared" si="1"/>
-        <v>0.54062389848431447</v>
+        <v>0.54071201973916105</v>
       </c>
       <c r="H26" s="5">
         <v>12288</v>
@@ -4476,14 +4476,14 @@
       </c>
       <c r="J26" s="11">
         <f t="shared" si="2"/>
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="K26" s="6">
-        <v>6585</v>
+        <v>6586</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="3"/>
-        <v>0.535888671875</v>
+        <v>0.53597005208333337</v>
       </c>
       <c r="M26" s="5">
         <v>20216</v>
@@ -4493,14 +4493,14 @@
       </c>
       <c r="O26" s="11">
         <f t="shared" si="4"/>
-        <v>6000</v>
+        <v>6003</v>
       </c>
       <c r="P26" s="6">
-        <v>15204</v>
+        <v>15207</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="5"/>
-        <v>0.75207756232686984</v>
+        <v>0.75222595963593197</v>
       </c>
       <c r="R26" s="5">
         <v>13942</v>
@@ -4510,14 +4510,14 @@
       </c>
       <c r="T26" s="11">
         <f t="shared" si="6"/>
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="U26" s="6">
-        <v>7343</v>
+        <v>7344</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="7"/>
-        <v>0.52668196815377999</v>
+        <v>0.52675369387462345</v>
       </c>
       <c r="W26" s="5">
         <v>13671</v>
@@ -4544,14 +4544,14 @@
       </c>
       <c r="AD26" s="11">
         <f t="shared" si="10"/>
-        <v>8965</v>
+        <v>8967</v>
       </c>
       <c r="AE26" s="6">
-        <v>16710</v>
+        <v>16712</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="11"/>
-        <v>0.74571581578007851</v>
+        <v>0.74580506961799353</v>
       </c>
       <c r="AG26" s="5">
         <v>13544</v>
@@ -4561,14 +4561,14 @@
       </c>
       <c r="AI26" s="11">
         <f t="shared" si="12"/>
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="AJ26" s="6">
-        <v>7610</v>
+        <v>7612</v>
       </c>
       <c r="AK26" s="12">
         <f t="shared" si="13"/>
-        <v>0.56187241582988778</v>
+        <v>0.56202008269344361</v>
       </c>
       <c r="AL26" s="5">
         <v>13664</v>
@@ -4595,14 +4595,14 @@
       </c>
       <c r="AS26" s="11">
         <f t="shared" si="16"/>
-        <v>14317</v>
+        <v>14319</v>
       </c>
       <c r="AT26" s="6">
-        <v>16812</v>
+        <v>16814</v>
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="17"/>
-        <v>0.72521784142869472</v>
+        <v>0.72530411526184113</v>
       </c>
       <c r="AV26" s="5">
         <v>13582</v>
@@ -4629,14 +4629,14 @@
       </c>
       <c r="BC26" s="11">
         <f t="shared" si="20"/>
-        <v>6135</v>
+        <v>6137</v>
       </c>
       <c r="BD26" s="6">
-        <v>7644</v>
+        <v>7646</v>
       </c>
       <c r="BE26" s="12">
         <f t="shared" si="21"/>
-        <v>0.56714646089924325</v>
+        <v>0.56729485086808129</v>
       </c>
       <c r="BF26" s="5">
         <v>23703</v>
@@ -4646,14 +4646,14 @@
       </c>
       <c r="BH26" s="11">
         <f t="shared" si="22"/>
-        <v>14210</v>
+        <v>14216</v>
       </c>
       <c r="BI26" s="6">
-        <v>16854</v>
+        <v>16860</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="23"/>
-        <v>0.71104923427414246</v>
+        <v>0.71130236678901404</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4671,14 +4671,14 @@
       </c>
       <c r="E27" s="11">
         <f t="shared" si="0"/>
-        <v>14851</v>
+        <v>14852</v>
       </c>
       <c r="F27" s="6">
-        <v>42023</v>
+        <v>42024</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="1"/>
-        <v>0.50653921722255035</v>
+        <v>0.50655127107918174</v>
       </c>
       <c r="H27" s="5">
         <v>85929</v>
@@ -4688,14 +4688,14 @@
       </c>
       <c r="J27" s="11">
         <f t="shared" si="2"/>
-        <v>15875</v>
+        <v>15876</v>
       </c>
       <c r="K27" s="6">
-        <v>42826</v>
+        <v>42827</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="3"/>
-        <v>0.49838820421510782</v>
+        <v>0.49839984172980017</v>
       </c>
       <c r="M27" s="5">
         <v>136177</v>
@@ -4756,14 +4756,14 @@
       </c>
       <c r="AD27" s="11">
         <f t="shared" si="10"/>
-        <v>68771</v>
+        <v>68772</v>
       </c>
       <c r="AE27" s="6">
-        <v>108187</v>
+        <v>108188</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="11"/>
-        <v>0.75122035899038297</v>
+        <v>0.75122730271152316</v>
       </c>
       <c r="AG27" s="5">
         <v>86986</v>
@@ -4807,14 +4807,14 @@
       </c>
       <c r="AS27" s="11">
         <f t="shared" si="16"/>
-        <v>94458</v>
+        <v>94459</v>
       </c>
       <c r="AT27" s="6">
-        <v>110500</v>
+        <v>110501</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="17"/>
-        <v>0.73360021775644468</v>
+        <v>0.73360685667244252</v>
       </c>
       <c r="AV27" s="5">
         <v>85745</v>
@@ -4858,14 +4858,14 @@
       </c>
       <c r="BH27" s="11">
         <f t="shared" si="22"/>
-        <v>99076</v>
+        <v>99078</v>
       </c>
       <c r="BI27" s="6">
-        <v>112444</v>
+        <v>112446</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="23"/>
-        <v>0.71509246775711632</v>
+        <v>0.71510518684337721</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5324,14 +5324,14 @@
       </c>
       <c r="J30" s="11">
         <f t="shared" si="2"/>
-        <v>15760</v>
+        <v>15761</v>
       </c>
       <c r="K30" s="6">
-        <v>54314</v>
+        <v>54315</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="3"/>
-        <v>0.53930553762746869</v>
+        <v>0.53931546702942079</v>
       </c>
       <c r="M30" s="5">
         <v>200801</v>
@@ -5341,14 +5341,14 @@
       </c>
       <c r="O30" s="11">
         <f t="shared" si="4"/>
-        <v>62193</v>
+        <v>62194</v>
       </c>
       <c r="P30" s="6">
-        <v>161709</v>
+        <v>161710</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="5"/>
-        <v>0.80531969462303477</v>
+        <v>0.80532467467791491</v>
       </c>
       <c r="R30" s="5">
         <v>104405</v>
@@ -5358,14 +5358,14 @@
       </c>
       <c r="T30" s="11">
         <f t="shared" si="6"/>
-        <v>19552</v>
+        <v>19553</v>
       </c>
       <c r="U30" s="6">
-        <v>55993</v>
+        <v>55994</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="7"/>
-        <v>0.53630573248407643</v>
+        <v>0.53631531056941717</v>
       </c>
       <c r="W30" s="5">
         <v>103393</v>
@@ -5375,14 +5375,14 @@
       </c>
       <c r="Y30" s="11">
         <f t="shared" si="8"/>
-        <v>23196</v>
+        <v>23197</v>
       </c>
       <c r="Z30" s="6">
-        <v>56649</v>
+        <v>56650</v>
       </c>
       <c r="AA30" s="12">
         <f t="shared" si="9"/>
-        <v>0.54789976110568417</v>
+        <v>0.54790943294033445</v>
       </c>
       <c r="AB30" s="5">
         <v>214949</v>
@@ -5392,14 +5392,14 @@
       </c>
       <c r="AD30" s="11">
         <f t="shared" si="10"/>
-        <v>93518</v>
+        <v>93519</v>
       </c>
       <c r="AE30" s="6">
-        <v>170809</v>
+        <v>170810</v>
       </c>
       <c r="AF30" s="12">
         <f t="shared" si="11"/>
-        <v>0.79464896324244361</v>
+        <v>0.7946536155087951</v>
       </c>
       <c r="AG30" s="5">
         <v>102459</v>
@@ -5409,14 +5409,14 @@
       </c>
       <c r="AI30" s="11">
         <f t="shared" si="12"/>
-        <v>44355</v>
+        <v>44356</v>
       </c>
       <c r="AJ30" s="6">
-        <v>57988</v>
+        <v>57989</v>
       </c>
       <c r="AK30" s="12">
         <f t="shared" si="13"/>
-        <v>0.5659629705540753</v>
+        <v>0.5659727305556369</v>
       </c>
       <c r="AL30" s="5">
         <v>101956</v>
@@ -5426,14 +5426,14 @@
       </c>
       <c r="AN30" s="11">
         <f t="shared" si="14"/>
-        <v>42725</v>
+        <v>42726</v>
       </c>
       <c r="AO30" s="6">
-        <v>58394</v>
+        <v>58395</v>
       </c>
       <c r="AP30" s="12">
         <f t="shared" si="15"/>
-        <v>0.57273725920985519</v>
+        <v>0.57274706736239167</v>
       </c>
       <c r="AQ30" s="5">
         <v>223141</v>
@@ -5443,14 +5443,14 @@
       </c>
       <c r="AS30" s="11">
         <f t="shared" si="16"/>
-        <v>150093</v>
+        <v>150094</v>
       </c>
       <c r="AT30" s="6">
-        <v>176546</v>
+        <v>176547</v>
       </c>
       <c r="AU30" s="12">
         <f t="shared" si="17"/>
-        <v>0.79118584213568999</v>
+        <v>0.79119032360704666</v>
       </c>
       <c r="AV30" s="5">
         <v>91341</v>
@@ -5477,14 +5477,14 @@
       </c>
       <c r="BC30" s="11">
         <f t="shared" si="20"/>
-        <v>44790</v>
+        <v>44791</v>
       </c>
       <c r="BD30" s="6">
-        <v>60067</v>
+        <v>60068</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="21"/>
-        <v>0.70578213307953519</v>
+        <v>0.70579388299434831</v>
       </c>
       <c r="BF30" s="5">
         <v>218115</v>
@@ -5494,14 +5494,14 @@
       </c>
       <c r="BH30" s="11">
         <f t="shared" si="22"/>
-        <v>155293</v>
+        <v>155294</v>
       </c>
       <c r="BI30" s="6">
-        <v>180143</v>
+        <v>180144</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="23"/>
-        <v>0.82590835109919081</v>
+        <v>0.82591293583659997</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="E31" s="11">
         <f t="shared" si="0"/>
-        <v>9392</v>
+        <v>9393</v>
       </c>
       <c r="F31" s="6">
-        <v>32555</v>
+        <v>32556</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="1"/>
-        <v>0.64481945847445876</v>
+        <v>0.64483926555350879</v>
       </c>
       <c r="H31" s="5">
         <v>53177</v>
@@ -5536,14 +5536,14 @@
       </c>
       <c r="J31" s="11">
         <f t="shared" si="2"/>
-        <v>9914</v>
+        <v>9915</v>
       </c>
       <c r="K31" s="6">
-        <v>32873</v>
+        <v>32874</v>
       </c>
       <c r="L31" s="12">
         <f t="shared" si="3"/>
-        <v>0.61818079244786284</v>
+        <v>0.61819959757037812</v>
       </c>
       <c r="M31" s="5">
         <v>98284</v>
@@ -5553,14 +5553,14 @@
       </c>
       <c r="O31" s="11">
         <f t="shared" si="4"/>
-        <v>34889</v>
+        <v>34890</v>
       </c>
       <c r="P31" s="6">
-        <v>85287</v>
+        <v>85288</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="5"/>
-        <v>0.86776077489723658</v>
+        <v>0.86777094949330513</v>
       </c>
       <c r="R31" s="5">
         <v>50949</v>
@@ -5570,14 +5570,14 @@
       </c>
       <c r="T31" s="11">
         <f t="shared" si="6"/>
-        <v>12248</v>
+        <v>12249</v>
       </c>
       <c r="U31" s="6">
-        <v>33429</v>
+        <v>33430</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="7"/>
-        <v>0.65612671495024433</v>
+        <v>0.65614634242085224</v>
       </c>
       <c r="W31" s="5">
         <v>49380</v>
@@ -5587,14 +5587,14 @@
       </c>
       <c r="Y31" s="11">
         <f t="shared" si="8"/>
-        <v>14456</v>
+        <v>14457</v>
       </c>
       <c r="Z31" s="6">
-        <v>33559</v>
+        <v>33560</v>
       </c>
       <c r="AA31" s="12">
         <f t="shared" si="9"/>
-        <v>0.67960712839206161</v>
+        <v>0.67962737950587282</v>
       </c>
       <c r="AB31" s="5">
         <v>101382</v>
@@ -5604,14 +5604,14 @@
       </c>
       <c r="AD31" s="11">
         <f t="shared" si="10"/>
-        <v>52668</v>
+        <v>52669</v>
       </c>
       <c r="AE31" s="6">
-        <v>88434</v>
+        <v>88435</v>
       </c>
       <c r="AF31" s="12">
         <f t="shared" si="11"/>
-        <v>0.87228502100964667</v>
+        <v>0.87229488469353533</v>
       </c>
       <c r="AG31" s="5">
         <v>47462</v>
@@ -5621,14 +5621,14 @@
       </c>
       <c r="AI31" s="11">
         <f t="shared" si="12"/>
-        <v>28047</v>
+        <v>28048</v>
       </c>
       <c r="AJ31" s="6">
-        <v>34092</v>
+        <v>34093</v>
       </c>
       <c r="AK31" s="12">
         <f t="shared" si="13"/>
-        <v>0.71830095655471748</v>
+        <v>0.71832202604188611</v>
       </c>
       <c r="AL31" s="5">
         <v>45806</v>
@@ -5638,14 +5638,14 @@
       </c>
       <c r="AN31" s="11">
         <f t="shared" si="14"/>
-        <v>24274</v>
+        <v>24275</v>
       </c>
       <c r="AO31" s="6">
-        <v>34139</v>
+        <v>34140</v>
       </c>
       <c r="AP31" s="12">
         <f t="shared" si="15"/>
-        <v>0.74529537615159591</v>
+        <v>0.74531720735274853</v>
       </c>
       <c r="AQ31" s="5">
         <v>101564</v>
@@ -5655,14 +5655,14 @@
       </c>
       <c r="AS31" s="11">
         <f t="shared" si="16"/>
-        <v>75030</v>
+        <v>75031</v>
       </c>
       <c r="AT31" s="6">
-        <v>90042</v>
+        <v>90043</v>
       </c>
       <c r="AU31" s="12">
         <f t="shared" si="17"/>
-        <v>0.886554290890473</v>
+        <v>0.88656413689890123</v>
       </c>
       <c r="AV31" s="5">
         <v>42627</v>
@@ -5672,14 +5672,14 @@
       </c>
       <c r="AX31" s="11">
         <f t="shared" si="18"/>
-        <v>24339</v>
+        <v>24340</v>
       </c>
       <c r="AY31" s="6">
-        <v>34448</v>
+        <v>34449</v>
       </c>
       <c r="AZ31" s="12">
         <f t="shared" si="19"/>
-        <v>0.80812630492410908</v>
+        <v>0.80814976423393625</v>
       </c>
       <c r="BA31" s="5">
         <v>42175</v>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="BC31" s="11">
         <f t="shared" si="20"/>
-        <v>24981</v>
+        <v>24982</v>
       </c>
       <c r="BD31" s="6">
-        <v>34502</v>
+        <v>34503</v>
       </c>
       <c r="BE31" s="12">
         <f t="shared" si="21"/>
-        <v>0.81806757557794907</v>
+        <v>0.81809128630705397</v>
       </c>
       <c r="BF31" s="5">
         <v>102281</v>
@@ -5706,14 +5706,14 @@
       </c>
       <c r="BH31" s="11">
         <f t="shared" si="22"/>
-        <v>79949</v>
+        <v>79950</v>
       </c>
       <c r="BI31" s="6">
-        <v>91430</v>
+        <v>91431</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="23"/>
-        <v>0.89390991484244386</v>
+        <v>0.89391969182937203</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5765,14 +5765,14 @@
       </c>
       <c r="O32" s="11">
         <f t="shared" si="4"/>
-        <v>92602</v>
+        <v>92603</v>
       </c>
       <c r="P32" s="6">
-        <v>287433</v>
+        <v>287434</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="5"/>
-        <v>0.89208389715832204</v>
+        <v>0.89208700078211323</v>
       </c>
       <c r="R32" s="5">
         <v>141043</v>
@@ -5782,14 +5782,14 @@
       </c>
       <c r="T32" s="11">
         <f t="shared" si="6"/>
-        <v>26771</v>
+        <v>26772</v>
       </c>
       <c r="U32" s="6">
-        <v>93844</v>
+        <v>93845</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="7"/>
-        <v>0.66535737328332489</v>
+        <v>0.66536446331969679</v>
       </c>
       <c r="W32" s="5">
         <v>135990</v>
@@ -5799,14 +5799,14 @@
       </c>
       <c r="Y32" s="11">
         <f t="shared" si="8"/>
-        <v>33867</v>
+        <v>33868</v>
       </c>
       <c r="Z32" s="6">
-        <v>94381</v>
+        <v>94382</v>
       </c>
       <c r="AA32" s="12">
         <f t="shared" si="9"/>
-        <v>0.69402897271858222</v>
+        <v>0.69403632620045597</v>
       </c>
       <c r="AB32" s="5">
         <v>328946</v>
@@ -5833,14 +5833,14 @@
       </c>
       <c r="AI32" s="11">
         <f t="shared" si="12"/>
-        <v>75317</v>
+        <v>75318</v>
       </c>
       <c r="AJ32" s="6">
-        <v>95693</v>
+        <v>95694</v>
       </c>
       <c r="AK32" s="12">
         <f t="shared" si="13"/>
-        <v>0.72744895321788572</v>
+        <v>0.72745655512140239</v>
       </c>
       <c r="AL32" s="5">
         <v>128868</v>
@@ -5850,14 +5850,14 @@
       </c>
       <c r="AN32" s="11">
         <f t="shared" si="14"/>
-        <v>63819</v>
+        <v>63820</v>
       </c>
       <c r="AO32" s="6">
-        <v>95810</v>
+        <v>95811</v>
       </c>
       <c r="AP32" s="12">
         <f t="shared" si="15"/>
-        <v>0.74347394232858433</v>
+        <v>0.74348170220690935</v>
       </c>
       <c r="AQ32" s="5">
         <v>335747</v>
@@ -5867,14 +5867,14 @@
       </c>
       <c r="AS32" s="11">
         <f t="shared" si="16"/>
-        <v>253841</v>
+        <v>253842</v>
       </c>
       <c r="AT32" s="6">
-        <v>306061</v>
+        <v>306062</v>
       </c>
       <c r="AU32" s="12">
         <f t="shared" si="17"/>
-        <v>0.91158223305048147</v>
+        <v>0.91158521148364691</v>
       </c>
       <c r="AV32" s="5">
         <v>125246</v>
@@ -5884,14 +5884,14 @@
       </c>
       <c r="AX32" s="11">
         <f t="shared" si="18"/>
-        <v>63833</v>
+        <v>63834</v>
       </c>
       <c r="AY32" s="6">
-        <v>96809</v>
+        <v>96810</v>
       </c>
       <c r="AZ32" s="12">
         <f t="shared" si="19"/>
-        <v>0.77295083276112608</v>
+        <v>0.77295881704804947</v>
       </c>
       <c r="BA32" s="5">
         <v>123206</v>
@@ -5901,14 +5901,14 @@
       </c>
       <c r="BC32" s="11">
         <f t="shared" si="20"/>
-        <v>65718</v>
+        <v>65719</v>
       </c>
       <c r="BD32" s="6">
-        <v>96991</v>
+        <v>96992</v>
       </c>
       <c r="BE32" s="12">
         <f t="shared" si="21"/>
-        <v>0.78722627144781909</v>
+        <v>0.78723438793565248</v>
       </c>
       <c r="BF32" s="5">
         <v>346732</v>
@@ -5943,14 +5943,14 @@
       </c>
       <c r="E33" s="11">
         <f t="shared" si="0"/>
-        <v>22117</v>
+        <v>22120</v>
       </c>
       <c r="F33" s="6">
-        <v>227290</v>
+        <v>227293</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="1"/>
-        <v>0.72392727921316824</v>
+        <v>0.72393683432706513</v>
       </c>
       <c r="H33" s="5">
         <v>329706</v>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J33" s="11">
         <f t="shared" si="2"/>
-        <v>23705</v>
+        <v>23708</v>
       </c>
       <c r="K33" s="6">
-        <v>229003</v>
+        <v>229006</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="3"/>
-        <v>0.69456728115351252</v>
+        <v>0.69457638016899903</v>
       </c>
       <c r="M33" s="5">
         <v>801034</v>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="O33" s="11">
         <f t="shared" si="4"/>
-        <v>145326</v>
+        <v>145330</v>
       </c>
       <c r="P33" s="6">
-        <v>736137</v>
+        <v>736141</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="5"/>
-        <v>0.91898346387294427</v>
+        <v>0.91898845741878621</v>
       </c>
       <c r="R33" s="5">
         <v>331018</v>
@@ -5994,14 +5994,14 @@
       </c>
       <c r="T33" s="11">
         <f t="shared" si="6"/>
-        <v>34432</v>
+        <v>34435</v>
       </c>
       <c r="U33" s="6">
-        <v>231864</v>
+        <v>231867</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="7"/>
-        <v>0.70045737694022681</v>
+        <v>0.70046643989148627</v>
       </c>
       <c r="W33" s="5">
         <v>322207</v>
@@ -6011,14 +6011,14 @@
       </c>
       <c r="Y33" s="11">
         <f t="shared" si="8"/>
-        <v>46982</v>
+        <v>46985</v>
       </c>
       <c r="Z33" s="6">
-        <v>233026</v>
+        <v>233029</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="9"/>
-        <v>0.72321830376124663</v>
+        <v>0.72322761454592854</v>
       </c>
       <c r="AB33" s="5">
         <v>823883</v>
@@ -6028,14 +6028,14 @@
       </c>
       <c r="AD33" s="11">
         <f t="shared" si="10"/>
-        <v>298880</v>
+        <v>298885</v>
       </c>
       <c r="AE33" s="6">
-        <v>758705</v>
+        <v>758710</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="11"/>
-        <v>0.9208892524788107</v>
+        <v>0.92089532130168972</v>
       </c>
       <c r="AG33" s="5">
         <v>309633</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="AI33" s="11">
         <f t="shared" si="12"/>
-        <v>165951</v>
+        <v>165956</v>
       </c>
       <c r="AJ33" s="6">
-        <v>235464</v>
+        <v>235469</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="13"/>
-        <v>0.76046157870769593</v>
+        <v>0.76047772685727943</v>
       </c>
       <c r="AL33" s="5">
         <v>305879</v>
@@ -6062,14 +6062,14 @@
       </c>
       <c r="AN33" s="11">
         <f t="shared" si="14"/>
-        <v>116953</v>
+        <v>116957</v>
       </c>
       <c r="AO33" s="6">
-        <v>235820</v>
+        <v>235824</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="15"/>
-        <v>0.77095845089071169</v>
+        <v>0.77097152795713342</v>
       </c>
       <c r="AQ33" s="5">
         <v>838229</v>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="AS33" s="11">
         <f t="shared" si="16"/>
-        <v>575961</v>
+        <v>575966</v>
       </c>
       <c r="AT33" s="6">
-        <v>775906</v>
+        <v>775911</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="17"/>
-        <v>0.92564919610273566</v>
+        <v>0.92565516105980583</v>
       </c>
       <c r="AV33" s="5">
         <v>298136</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="AX33" s="11">
         <f t="shared" si="18"/>
-        <v>108170</v>
+        <v>108174</v>
       </c>
       <c r="AY33" s="6">
-        <v>237502</v>
+        <v>237506</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="19"/>
-        <v>0.79662301768320498</v>
+        <v>0.79663643437894116</v>
       </c>
       <c r="BA33" s="5">
         <v>294597</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="BC33" s="11">
         <f t="shared" si="20"/>
-        <v>112365</v>
+        <v>112369</v>
       </c>
       <c r="BD33" s="6">
-        <v>237893</v>
+        <v>237897</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="21"/>
-        <v>0.80752010373493277</v>
+        <v>0.80753368160571903</v>
       </c>
       <c r="BF33" s="5">
         <v>864165</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="BH33" s="11">
         <f t="shared" si="22"/>
-        <v>636696</v>
+        <v>636703</v>
       </c>
       <c r="BI33" s="6">
-        <v>791661</v>
+        <v>791668</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="23"/>
-        <v>0.91609935602575898</v>
+        <v>0.91610745633067758</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6503,14 +6503,14 @@
       </c>
       <c r="AS35" s="11">
         <f t="shared" si="16"/>
-        <v>4954</v>
+        <v>4955</v>
       </c>
       <c r="AT35" s="6">
-        <v>7249</v>
+        <v>7250</v>
       </c>
       <c r="AU35" s="12">
         <f t="shared" si="17"/>
-        <v>0.91033530076604297</v>
+        <v>0.91046088157729499</v>
       </c>
       <c r="AV35" s="5">
         <v>4015</v>
@@ -6579,14 +6579,14 @@
       </c>
       <c r="E36" s="11">
         <f t="shared" si="0"/>
-        <v>57014</v>
+        <v>57015</v>
       </c>
       <c r="F36" s="6">
-        <v>323161</v>
+        <v>323162</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="1"/>
-        <v>0.58150511397580129</v>
+        <v>0.58150691340430283</v>
       </c>
       <c r="H36" s="5">
         <v>576385</v>
@@ -6596,14 +6596,14 @@
       </c>
       <c r="J36" s="11">
         <f t="shared" si="2"/>
-        <v>61332</v>
+        <v>61334</v>
       </c>
       <c r="K36" s="6">
-        <v>325771</v>
+        <v>325773</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="3"/>
-        <v>0.56519687361746052</v>
+        <v>0.56520034352039006</v>
       </c>
       <c r="M36" s="5">
         <v>1291465</v>
@@ -6613,14 +6613,14 @@
       </c>
       <c r="O36" s="11">
         <f t="shared" si="4"/>
-        <v>325475</v>
+        <v>325476</v>
       </c>
       <c r="P36" s="6">
-        <v>1125067</v>
+        <v>1125068</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>0.87115562558799498</v>
+        <v>0.87115639990243643</v>
       </c>
       <c r="R36" s="5">
         <v>567427</v>
@@ -6630,14 +6630,14 @@
       </c>
       <c r="T36" s="11">
         <f t="shared" si="6"/>
-        <v>80874</v>
+        <v>80875</v>
       </c>
       <c r="U36" s="6">
-        <v>330319</v>
+        <v>330320</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="7"/>
-        <v>0.58213479443170668</v>
+        <v>0.58213655677294174</v>
       </c>
       <c r="W36" s="5">
         <v>554725</v>
@@ -6647,14 +6647,14 @@
       </c>
       <c r="Y36" s="11">
         <f t="shared" si="8"/>
-        <v>102842</v>
+        <v>102843</v>
       </c>
       <c r="Z36" s="6">
-        <v>331910</v>
+        <v>331911</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="9"/>
-        <v>0.5983325070981117</v>
+        <v>0.59833430979314073</v>
       </c>
       <c r="AB36" s="5">
         <v>1322160</v>
@@ -6664,14 +6664,14 @@
       </c>
       <c r="AD36" s="11">
         <f t="shared" si="10"/>
-        <v>585410</v>
+        <v>585411</v>
       </c>
       <c r="AE36" s="6">
-        <v>1156226</v>
+        <v>1156227</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="11"/>
-        <v>0.8744977914927089</v>
+        <v>0.87449854783082226</v>
       </c>
       <c r="AG36" s="5">
         <v>528657</v>
@@ -6681,14 +6681,14 @@
       </c>
       <c r="AI36" s="11">
         <f t="shared" si="12"/>
-        <v>239157</v>
+        <v>239158</v>
       </c>
       <c r="AJ36" s="6">
-        <v>336437</v>
+        <v>336438</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="13"/>
-        <v>0.63639940452883437</v>
+        <v>0.63640129611449392</v>
       </c>
       <c r="AL36" s="5">
         <v>520551</v>
@@ -6698,14 +6698,14 @@
       </c>
       <c r="AN36" s="11">
         <f t="shared" si="14"/>
-        <v>188253</v>
+        <v>188254</v>
       </c>
       <c r="AO36" s="6">
-        <v>336829</v>
+        <v>336830</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="15"/>
-        <v>0.64706243960726229</v>
+        <v>0.64706436064862038</v>
       </c>
       <c r="AQ36" s="5">
         <v>1349417</v>
@@ -6715,14 +6715,14 @@
       </c>
       <c r="AS36" s="11">
         <f t="shared" si="16"/>
-        <v>963176</v>
+        <v>963179</v>
       </c>
       <c r="AT36" s="6">
-        <v>1181473</v>
+        <v>1181476</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="17"/>
-        <v>0.87554329017642429</v>
+        <v>0.87554551335873199</v>
       </c>
       <c r="AV36" s="5">
         <v>479560</v>
@@ -6732,14 +6732,14 @@
       </c>
       <c r="AX36" s="11">
         <f t="shared" si="18"/>
-        <v>182774</v>
+        <v>182776</v>
       </c>
       <c r="AY36" s="6">
-        <v>340653</v>
+        <v>340655</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="19"/>
-        <v>0.71034489949120028</v>
+        <v>0.71034906998081571</v>
       </c>
       <c r="BA36" s="5">
         <v>474262</v>
@@ -6749,14 +6749,14 @@
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="20"/>
-        <v>186135</v>
+        <v>186137</v>
       </c>
       <c r="BD36" s="6">
-        <v>341579</v>
+        <v>341581</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="21"/>
-        <v>0.72023269838190707</v>
+        <v>0.72023691546023083</v>
       </c>
       <c r="BF36" s="5">
         <v>1384075</v>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="BH36" s="11">
         <f t="shared" si="22"/>
-        <v>1004962</v>
+        <v>1004969</v>
       </c>
       <c r="BI36" s="6">
-        <v>1200541</v>
+        <v>1200548</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="23"/>
-        <v>0.86739591423875151</v>
+        <v>0.86740097176814845</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6791,14 +6791,14 @@
       </c>
       <c r="E37" s="11">
         <f t="shared" si="0"/>
-        <v>66179</v>
+        <v>66185</v>
       </c>
       <c r="F37" s="6">
-        <v>318003</v>
+        <v>318009</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="1"/>
-        <v>0.74981785257022404</v>
+        <v>0.74983199994341054</v>
       </c>
       <c r="H37" s="5">
         <v>438161</v>
@@ -6808,14 +6808,14 @@
       </c>
       <c r="J37" s="11">
         <f t="shared" si="2"/>
-        <v>71258</v>
+        <v>71265</v>
       </c>
       <c r="K37" s="6">
-        <v>321977</v>
+        <v>321984</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="3"/>
-        <v>0.73483719454720986</v>
+        <v>0.73485317040996345</v>
       </c>
       <c r="M37" s="5">
         <v>650458</v>
@@ -6825,14 +6825,14 @@
       </c>
       <c r="O37" s="11">
         <f t="shared" si="4"/>
-        <v>156074</v>
+        <v>156084</v>
       </c>
       <c r="P37" s="6">
-        <v>542389</v>
+        <v>542399</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>0.83385706686673078</v>
+        <v>0.8338724406495116</v>
       </c>
       <c r="R37" s="5">
         <v>451955</v>
@@ -6842,14 +6842,14 @@
       </c>
       <c r="T37" s="11">
         <f t="shared" si="6"/>
-        <v>89267</v>
+        <v>89274</v>
       </c>
       <c r="U37" s="6">
-        <v>330060</v>
+        <v>330067</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="7"/>
-        <v>0.73029394519365864</v>
+        <v>0.73030943346129595</v>
       </c>
       <c r="W37" s="5">
         <v>454656</v>
@@ -6859,14 +6859,14 @@
       </c>
       <c r="Y37" s="11">
         <f t="shared" si="8"/>
-        <v>110089</v>
+        <v>110097</v>
       </c>
       <c r="Z37" s="6">
-        <v>333654</v>
+        <v>333662</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="9"/>
-        <v>0.73386032516891897</v>
+        <v>0.73387792088963966</v>
       </c>
       <c r="AB37" s="5">
         <v>682420</v>
@@ -6876,14 +6876,14 @@
       </c>
       <c r="AD37" s="11">
         <f t="shared" si="10"/>
-        <v>263204</v>
+        <v>263214</v>
       </c>
       <c r="AE37" s="6">
-        <v>566110</v>
+        <v>566120</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="11"/>
-        <v>0.82956243955335429</v>
+        <v>0.82957709328565987</v>
       </c>
       <c r="AG37" s="5">
         <v>455096</v>
@@ -6893,14 +6893,14 @@
       </c>
       <c r="AI37" s="11">
         <f t="shared" si="12"/>
-        <v>253291</v>
+        <v>253297</v>
       </c>
       <c r="AJ37" s="6">
-        <v>341043</v>
+        <v>341049</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="13"/>
-        <v>0.74938694253520133</v>
+        <v>0.74940012656670241</v>
       </c>
       <c r="AL37" s="5">
         <v>455153</v>
@@ -6910,14 +6910,14 @@
       </c>
       <c r="AN37" s="11">
         <f t="shared" si="14"/>
-        <v>230814</v>
+        <v>230820</v>
       </c>
       <c r="AO37" s="6">
-        <v>342554</v>
+        <v>342560</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="15"/>
-        <v>0.75261285765445907</v>
+        <v>0.75262604003488942</v>
       </c>
       <c r="AQ37" s="5">
         <v>700400</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="AS37" s="11">
         <f t="shared" si="16"/>
-        <v>433741</v>
+        <v>433751</v>
       </c>
       <c r="AT37" s="6">
-        <v>584986</v>
+        <v>584996</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="17"/>
-        <v>0.83521701884637345</v>
+        <v>0.83523129640205596</v>
       </c>
       <c r="AV37" s="5">
         <v>439004</v>
@@ -6944,14 +6944,14 @@
       </c>
       <c r="AX37" s="11">
         <f t="shared" si="18"/>
-        <v>227679</v>
+        <v>227687</v>
       </c>
       <c r="AY37" s="6">
-        <v>349509</v>
+        <v>349517</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="19"/>
-        <v>0.79614080965093714</v>
+        <v>0.7961590327195196</v>
       </c>
       <c r="BA37" s="5">
         <v>433985</v>
@@ -6961,14 +6961,14 @@
       </c>
       <c r="BC37" s="11">
         <f t="shared" si="20"/>
-        <v>235056</v>
+        <v>235066</v>
       </c>
       <c r="BD37" s="6">
-        <v>351510</v>
+        <v>351520</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="21"/>
-        <v>0.80995886954618246</v>
+        <v>0.80998191181722867</v>
       </c>
       <c r="BF37" s="5">
         <v>706472</v>
@@ -6978,14 +6978,14 @@
       </c>
       <c r="BH37" s="11">
         <f t="shared" si="22"/>
-        <v>460594</v>
+        <v>460605</v>
       </c>
       <c r="BI37" s="6">
-        <v>599326</v>
+        <v>599337</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="23"/>
-        <v>0.84833652289121153</v>
+        <v>0.84835209321813176</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7427,14 +7427,14 @@
       </c>
       <c r="E40" s="11">
         <f t="shared" si="0"/>
-        <v>26503</v>
+        <v>26504</v>
       </c>
       <c r="F40" s="6">
-        <v>135022</v>
+        <v>135023</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="1"/>
-        <v>0.8212417585091113</v>
+        <v>0.82124784079020996</v>
       </c>
       <c r="H40" s="5">
         <v>169073</v>
@@ -7461,14 +7461,14 @@
       </c>
       <c r="O40" s="11">
         <f t="shared" si="4"/>
-        <v>67954</v>
+        <v>67955</v>
       </c>
       <c r="P40" s="6">
-        <v>241231</v>
+        <v>241232</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>0.91457829406813718</v>
+        <v>0.91458208536483643</v>
       </c>
       <c r="R40" s="5">
         <v>173127</v>
@@ -7512,14 +7512,14 @@
       </c>
       <c r="AD40" s="11">
         <f t="shared" si="10"/>
-        <v>145550</v>
+        <v>145551</v>
       </c>
       <c r="AE40" s="6">
-        <v>249071</v>
+        <v>249072</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="11"/>
-        <v>0.91174349607037097</v>
+        <v>0.91174715664705819</v>
       </c>
       <c r="AG40" s="5">
         <v>172895</v>
@@ -7546,14 +7546,14 @@
       </c>
       <c r="AN40" s="11">
         <f t="shared" si="14"/>
-        <v>107534</v>
+        <v>107535</v>
       </c>
       <c r="AO40" s="6">
-        <v>144480</v>
+        <v>144481</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="15"/>
-        <v>0.83356410966491279</v>
+        <v>0.83356987907320224</v>
       </c>
       <c r="AQ40" s="5">
         <v>281909</v>
@@ -7563,14 +7563,14 @@
       </c>
       <c r="AS40" s="11">
         <f t="shared" si="16"/>
-        <v>206377</v>
+        <v>206382</v>
       </c>
       <c r="AT40" s="6">
-        <v>255764</v>
+        <v>255769</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="17"/>
-        <v>0.90725730643576474</v>
+        <v>0.90727504265560877</v>
       </c>
       <c r="AV40" s="5">
         <v>172382</v>
@@ -7580,14 +7580,14 @@
       </c>
       <c r="AX40" s="11">
         <f t="shared" si="18"/>
-        <v>103190</v>
+        <v>103191</v>
       </c>
       <c r="AY40" s="6">
-        <v>146399</v>
+        <v>146400</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="19"/>
-        <v>0.84927080553654088</v>
+        <v>0.84927660660625814</v>
       </c>
       <c r="BA40" s="5">
         <v>172548</v>
@@ -7597,14 +7597,14 @@
       </c>
       <c r="BC40" s="11">
         <f t="shared" si="20"/>
-        <v>105621</v>
+        <v>105622</v>
       </c>
       <c r="BD40" s="6">
-        <v>146857</v>
+        <v>146858</v>
       </c>
       <c r="BE40" s="12">
         <f t="shared" si="21"/>
-        <v>0.85110809745693949</v>
+        <v>0.85111389294573103</v>
       </c>
       <c r="BF40" s="5">
         <v>291194</v>
@@ -7614,14 +7614,14 @@
       </c>
       <c r="BH40" s="11">
         <f t="shared" si="22"/>
-        <v>208597</v>
+        <v>208601</v>
       </c>
       <c r="BI40" s="6">
-        <v>260559</v>
+        <v>260563</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="23"/>
-        <v>0.89479522242903353</v>
+        <v>0.89480895897580304</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7639,14 +7639,14 @@
       </c>
       <c r="E41" s="11">
         <f t="shared" si="0"/>
-        <v>77320</v>
+        <v>77334</v>
       </c>
       <c r="F41" s="6">
-        <v>452072</v>
+        <v>452086</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="1"/>
-        <v>0.73710315681002558</v>
+        <v>0.73712598380261829</v>
       </c>
       <c r="H41" s="5">
         <v>630477</v>
@@ -7656,14 +7656,14 @@
       </c>
       <c r="J41" s="11">
         <f t="shared" si="2"/>
-        <v>82461</v>
+        <v>82477</v>
       </c>
       <c r="K41" s="6">
-        <v>458530</v>
+        <v>458546</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="3"/>
-        <v>0.72727474594632313</v>
+        <v>0.72730012355724316</v>
       </c>
       <c r="M41" s="5">
         <v>852643</v>
@@ -7673,14 +7673,14 @@
       </c>
       <c r="O41" s="11">
         <f t="shared" si="4"/>
-        <v>165693</v>
+        <v>165711</v>
       </c>
       <c r="P41" s="6">
-        <v>685211</v>
+        <v>685229</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>0.80363176616708287</v>
+        <v>0.8036528769954131</v>
       </c>
       <c r="R41" s="5">
         <v>651946</v>
@@ -7690,14 +7690,14 @@
       </c>
       <c r="T41" s="11">
         <f t="shared" si="6"/>
-        <v>104722</v>
+        <v>104734</v>
       </c>
       <c r="U41" s="6">
-        <v>468844</v>
+        <v>468856</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="7"/>
-        <v>0.71914545069683689</v>
+        <v>0.71916385712927144</v>
       </c>
       <c r="W41" s="5">
         <v>654087</v>
@@ -7707,14 +7707,14 @@
       </c>
       <c r="Y41" s="11">
         <f t="shared" si="8"/>
-        <v>129260</v>
+        <v>129275</v>
       </c>
       <c r="Z41" s="6">
-        <v>472887</v>
+        <v>472902</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="9"/>
-        <v>0.72297263208105345</v>
+        <v>0.72299556481018579</v>
       </c>
       <c r="AB41" s="5">
         <v>882248</v>
@@ -7724,14 +7724,14 @@
       </c>
       <c r="AD41" s="11">
         <f t="shared" si="10"/>
-        <v>296884</v>
+        <v>296903</v>
       </c>
       <c r="AE41" s="6">
-        <v>708732</v>
+        <v>708751</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="11"/>
-        <v>0.80332514213690487</v>
+        <v>0.80334667803157389</v>
       </c>
       <c r="AG41" s="5">
         <v>638043</v>
@@ -7741,14 +7741,14 @@
       </c>
       <c r="AI41" s="11">
         <f t="shared" si="12"/>
-        <v>359876</v>
+        <v>359889</v>
       </c>
       <c r="AJ41" s="6">
-        <v>481403</v>
+        <v>481416</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="13"/>
-        <v>0.75449930490578221</v>
+        <v>0.7545196797081074</v>
       </c>
       <c r="AL41" s="5">
         <v>632207</v>
@@ -7758,14 +7758,14 @@
       </c>
       <c r="AN41" s="11">
         <f t="shared" si="14"/>
-        <v>319926</v>
+        <v>319939</v>
       </c>
       <c r="AO41" s="6">
-        <v>483031</v>
+        <v>483044</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="15"/>
-        <v>0.76403930990957081</v>
+        <v>0.76405987279482823</v>
       </c>
       <c r="AQ41" s="5">
         <v>865402</v>
@@ -7775,14 +7775,14 @@
       </c>
       <c r="AS41" s="11">
         <f t="shared" si="16"/>
-        <v>516839</v>
+        <v>516860</v>
       </c>
       <c r="AT41" s="6">
-        <v>724212</v>
+        <v>724233</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="17"/>
-        <v>0.83685038860552663</v>
+        <v>0.83687465478471279</v>
       </c>
       <c r="AV41" s="5">
         <v>609881</v>
@@ -7792,14 +7792,14 @@
       </c>
       <c r="AX41" s="11">
         <f t="shared" si="18"/>
-        <v>321771</v>
+        <v>321790</v>
       </c>
       <c r="AY41" s="6">
-        <v>489966</v>
+        <v>489985</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="19"/>
-        <v>0.80337967570722812</v>
+        <v>0.80341082932572094</v>
       </c>
       <c r="BA41" s="5">
         <v>594974</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="20"/>
-        <v>336331</v>
+        <v>336348</v>
       </c>
       <c r="BD41" s="6">
-        <v>492340</v>
+        <v>492357</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="21"/>
-        <v>0.82749834446547244</v>
+        <v>0.82752691714259785</v>
       </c>
       <c r="BF41" s="5">
         <v>867754</v>
@@ -7826,14 +7826,14 @@
       </c>
       <c r="BH41" s="11">
         <f t="shared" si="22"/>
-        <v>556565</v>
+        <v>556594</v>
       </c>
       <c r="BI41" s="6">
-        <v>737677</v>
+        <v>737706</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="23"/>
-        <v>0.85009922166881402</v>
+        <v>0.85013264127851906</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8038,14 +8038,14 @@
       </c>
       <c r="BH42" s="11">
         <f t="shared" si="22"/>
-        <v>12531</v>
+        <v>12532</v>
       </c>
       <c r="BI42" s="6">
-        <v>16743</v>
+        <v>16744</v>
       </c>
       <c r="BJ42" s="12">
         <f t="shared" si="23"/>
-        <v>0.80344546283410911</v>
+        <v>0.80349344978165937</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8309,14 +8309,14 @@
       </c>
       <c r="O44" s="11">
         <f t="shared" si="4"/>
-        <v>72461</v>
+        <v>72462</v>
       </c>
       <c r="P44" s="6">
-        <v>233292</v>
+        <v>233293</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="5"/>
-        <v>0.82686609484653006</v>
+        <v>0.82686963918621958</v>
       </c>
       <c r="R44" s="5">
         <v>209233</v>
@@ -8360,14 +8360,14 @@
       </c>
       <c r="AD44" s="11">
         <f t="shared" si="10"/>
-        <v>127294</v>
+        <v>127295</v>
       </c>
       <c r="AE44" s="6">
-        <v>244439</v>
+        <v>244440</v>
       </c>
       <c r="AF44" s="12">
         <f t="shared" si="11"/>
-        <v>0.81976993762157091</v>
+        <v>0.81977329130055676</v>
       </c>
       <c r="AG44" s="5">
         <v>213000</v>
@@ -8487,14 +8487,14 @@
       </c>
       <c r="E45" s="11">
         <f t="shared" si="0"/>
-        <v>22310</v>
+        <v>22311</v>
       </c>
       <c r="F45" s="6">
-        <v>132668</v>
+        <v>132669</v>
       </c>
       <c r="G45" s="12">
         <f t="shared" si="1"/>
-        <v>0.7730739870987291</v>
+        <v>0.77307981423102246</v>
       </c>
       <c r="H45" s="5">
         <v>177364</v>
@@ -8504,14 +8504,14 @@
       </c>
       <c r="J45" s="11">
         <f t="shared" si="2"/>
-        <v>23859</v>
+        <v>23860</v>
       </c>
       <c r="K45" s="6">
-        <v>134615</v>
+        <v>134616</v>
       </c>
       <c r="L45" s="12">
         <f t="shared" si="3"/>
-        <v>0.75897589138720367</v>
+        <v>0.75898152950993436</v>
       </c>
       <c r="M45" s="5">
         <v>252576</v>
@@ -8555,14 +8555,14 @@
       </c>
       <c r="Y45" s="11">
         <f t="shared" si="8"/>
-        <v>43451</v>
+        <v>43452</v>
       </c>
       <c r="Z45" s="6">
-        <v>139030</v>
+        <v>139031</v>
       </c>
       <c r="AA45" s="12">
         <f t="shared" si="9"/>
-        <v>0.77283971205425384</v>
+        <v>0.7728452708524417</v>
       </c>
       <c r="AB45" s="5">
         <v>256988</v>
@@ -9099,15 +9099,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" si="0"/>
-        <v>546900</v>
+        <v>546935</v>
       </c>
       <c r="F48" s="15">
         <f>SUM(F10:F47)</f>
-        <v>3051603</v>
+        <v>3051638</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" si="1"/>
-        <v>0.67868962056937276</v>
+        <v>0.67869740471977502</v>
       </c>
       <c r="H48" s="15">
         <f>SUM(H10:H47)</f>
@@ -9119,15 +9119,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" si="2"/>
-        <v>589298</v>
+        <v>589333</v>
       </c>
       <c r="K48" s="15">
         <f>SUM(K10:K47)</f>
-        <v>3089615</v>
+        <v>3089650</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" si="3"/>
-        <v>0.65984351857883172</v>
+        <v>0.65985099346588083</v>
       </c>
       <c r="M48" s="15">
         <f>SUM(M10:M47)</f>
@@ -9139,15 +9139,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2192326</v>
+        <v>2192378</v>
       </c>
       <c r="P48" s="15">
         <f>SUM(P10:P47)</f>
-        <v>8044977</v>
+        <v>8045029</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.86349977620855434</v>
+        <v>0.86350535757794333</v>
       </c>
       <c r="R48" s="15">
         <f>SUM(R10:R47)</f>
@@ -9159,15 +9159,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>772920</v>
+        <v>772951</v>
       </c>
       <c r="U48" s="15">
         <f>SUM(U10:U47)</f>
-        <v>3153560</v>
+        <v>3153591</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.6603448427494113</v>
+        <v>0.66035133404500268</v>
       </c>
       <c r="W48" s="15">
         <f>SUM(W10:W47)</f>
@@ -9179,15 +9179,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" si="8"/>
-        <v>978269</v>
+        <v>978304</v>
       </c>
       <c r="Z48" s="15">
         <f>SUM(Z10:Z47)</f>
-        <v>3178222</v>
+        <v>3178257</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" si="9"/>
-        <v>0.67237048622445494</v>
+        <v>0.67237789066851761</v>
       </c>
       <c r="AB48" s="15">
         <f>SUM(AB10:AB47)</f>
@@ -9199,15 +9199,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>3988029</v>
+        <v>3988083</v>
       </c>
       <c r="AE48" s="15">
         <f>SUM(AE10:AE47)</f>
-        <v>8342209</v>
+        <v>8342263</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.86382961009870418</v>
+        <v>0.86383520175901207</v>
       </c>
       <c r="AG48" s="15">
         <f>SUM(AG10:AG47)</f>
@@ -9219,15 +9219,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>2361856</v>
+        <v>2361890</v>
       </c>
       <c r="AJ48" s="15">
         <f>SUM(AJ10:AJ47)</f>
-        <v>3233198</v>
+        <v>3233232</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.70142906606523481</v>
+        <v>0.70143644222600388</v>
       </c>
       <c r="AL48" s="15">
         <f>SUM(AL10:AL47)</f>
@@ -9239,15 +9239,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>2046823</v>
+        <v>2046854</v>
       </c>
       <c r="AO48" s="15">
         <f>SUM(AO10:AO47)</f>
-        <v>3245133</v>
+        <v>3245164</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.70976580219495644</v>
+        <v>0.70977258242241337</v>
       </c>
       <c r="AQ48" s="15">
         <f>SUM(AQ10:AQ47)</f>
@@ -9259,15 +9259,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>6760011</v>
+        <v>6760076</v>
       </c>
       <c r="AT48" s="15">
         <f>SUM(AT10:AT47)</f>
-        <v>8562944</v>
+        <v>8563009</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.86476939954637433</v>
+        <v>0.8647759638788014</v>
       </c>
       <c r="AV48" s="15">
         <f>SUM(AV10:AV47)</f>
@@ -9279,15 +9279,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>2013228</v>
+        <v>2013267</v>
       </c>
       <c r="AY48" s="15">
         <f>SUM(AY10:AY47)</f>
-        <v>3290765</v>
+        <v>3290804</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.74411982383157949</v>
+        <v>0.74412864265429379</v>
       </c>
       <c r="BA48" s="15">
         <f>SUM(BA10:BA47)</f>
@@ -9299,15 +9299,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>2072250</v>
+        <v>2072292</v>
       </c>
       <c r="BD48" s="15">
         <f>SUM(BD10:BD47)</f>
-        <v>3302247</v>
+        <v>3302289</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.75711062159130826</v>
+        <v>0.75712025098793023</v>
       </c>
       <c r="BF48" s="15">
         <f>SUM(BF10:BF47)</f>
@@ -9319,15 +9319,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>7183672</v>
+        <v>7183759</v>
       </c>
       <c r="BI48" s="15">
         <f>SUM(BI10:BI47)</f>
-        <v>8731142</v>
+        <v>8731229</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.85809934920743813</v>
+        <v>0.85810789959447575</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
@@ -9443,71 +9443,43 @@
       <c r="BJ56"/>
     </row>
     <row r="57" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="G57"/>
-      <c r="L57"/>
-      <c r="Q57"/>
-      <c r="V57"/>
-      <c r="AA57"/>
-      <c r="AF57"/>
-      <c r="AK57"/>
-      <c r="AP57"/>
-      <c r="AU57"/>
-      <c r="AZ57"/>
-      <c r="BE57"/>
-      <c r="BJ57"/>
+      <c r="A57" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B57" s="21"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="G58"/>
-      <c r="L58"/>
-      <c r="Q58"/>
-      <c r="V58"/>
-      <c r="AA58"/>
-      <c r="AF58"/>
-      <c r="AK58"/>
-      <c r="AP58"/>
-      <c r="AU58"/>
-      <c r="AZ58"/>
-      <c r="BE58"/>
-      <c r="BJ58"/>
+    <row r="60" spans="1:62" x14ac:dyDescent="0.3">
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="9"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="9"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="9"/>
+      <c r="AB60" s="3"/>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A59" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-    </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="9"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
-      <c r="Q62" s="9"/>
-      <c r="R62" s="3"/>
-      <c r="S62" s="3"/>
-      <c r="T62" s="3"/>
-      <c r="U62" s="3"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="3"/>
-    </row>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A1:E1"/>
@@ -9521,7 +9493,7 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="H8:L8"/>
-    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="A3:B3"/>
